--- a/artfynd/A 12479-2025 artfynd.xlsx
+++ b/artfynd/A 12479-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124244069</v>
+        <v>124244491</v>
       </c>
       <c r="B2" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461842</v>
+        <v>461860</v>
       </c>
       <c r="R2" t="n">
-        <v>7050570</v>
+        <v>7050631</v>
       </c>
       <c r="S2" t="n">
         <v>8</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På en grov sälglåga.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,22 +784,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -969,10 +964,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124243366</v>
+        <v>124244069</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>79920</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,46 +976,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461694</v>
+        <v>461842</v>
       </c>
       <c r="R4" t="n">
-        <v>7050529</v>
+        <v>7050570</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1049,7 +1044,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1059,12 +1054,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i en murken granhögstubbe.</t>
+          <t>På en grov sälglåga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1083,22 +1078,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1116,10 +1111,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124244322</v>
+        <v>124241982</v>
       </c>
       <c r="B5" t="n">
-        <v>100279</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1128,46 +1123,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461935</v>
+        <v>461758</v>
       </c>
       <c r="R5" t="n">
-        <v>7050570</v>
+        <v>7050534</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1196,7 +1186,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1206,7 +1196,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1221,6 +1216,26 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1238,7 +1253,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124244491</v>
+        <v>124242253</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1278,13 +1293,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461860</v>
+        <v>461780</v>
       </c>
       <c r="R6" t="n">
-        <v>7050631</v>
+        <v>7050582</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1313,7 +1328,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1323,12 +1338,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:46</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1380,10 +1390,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124244822</v>
+        <v>124244357</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1392,43 +1402,52 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461680</v>
+        <v>461909</v>
       </c>
       <c r="R7" t="n">
-        <v>7050615</v>
+        <v>7050579</v>
       </c>
       <c r="S7" t="n">
         <v>9</v>
@@ -1460,7 +1479,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1470,7 +1489,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>18:37</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>I flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1485,26 +1509,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1522,10 +1526,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124244357</v>
+        <v>124241219</v>
       </c>
       <c r="B8" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1534,55 +1538,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461909</v>
+        <v>461671</v>
       </c>
       <c r="R8" t="n">
-        <v>7050579</v>
+        <v>7050487</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1611,7 +1601,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1621,12 +1611,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:37</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>I flerskiktad äldre granskog.</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1641,6 +1626,26 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1658,10 +1663,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124242253</v>
+        <v>124244006</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1674,21 +1679,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1698,13 +1703,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461780</v>
+        <v>461840</v>
       </c>
       <c r="R9" t="n">
-        <v>7050582</v>
+        <v>7050563</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1733,7 +1738,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1743,7 +1748,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Enstaka på en grov sälglåga.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1762,22 +1772,22 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1795,7 +1805,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124242084</v>
+        <v>124244443</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1835,13 +1845,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461835</v>
+        <v>461867</v>
       </c>
       <c r="R10" t="n">
-        <v>7050524</v>
+        <v>7050617</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1870,7 +1880,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1880,7 +1890,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1909,12 +1924,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1932,7 +1947,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124241219</v>
+        <v>124244822</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1966,19 +1981,24 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461671</v>
+        <v>461680</v>
       </c>
       <c r="R11" t="n">
-        <v>7050487</v>
+        <v>7050615</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2007,7 +2027,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2017,7 +2037,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2069,10 +2089,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124241982</v>
+        <v>124244983</v>
       </c>
       <c r="B12" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2085,37 +2105,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461758</v>
+        <v>461652</v>
       </c>
       <c r="R12" t="n">
-        <v>7050534</v>
+        <v>7050519</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2144,7 +2164,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2154,12 +2174,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:13</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På en sälglåga.</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2178,22 +2193,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2211,7 +2226,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124244443</v>
+        <v>124242084</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -2251,13 +2266,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461867</v>
+        <v>461835</v>
       </c>
       <c r="R13" t="n">
-        <v>7050617</v>
+        <v>7050524</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2286,7 +2301,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2296,12 +2311,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:43</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2330,12 +2340,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2353,10 +2363,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124244006</v>
+        <v>124243366</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>57529</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2369,37 +2379,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461840</v>
+        <v>461694</v>
       </c>
       <c r="R14" t="n">
-        <v>7050563</v>
+        <v>7050529</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2428,7 +2443,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2438,12 +2453,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Enstaka på en grov sälglåga.</t>
+          <t>Rejäla hackspår i en murken granhögstubbe.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2462,22 +2477,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2495,10 +2510,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124244983</v>
+        <v>124244322</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>100279</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2507,41 +2522,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461652</v>
+        <v>461935</v>
       </c>
       <c r="R15" t="n">
-        <v>7050519</v>
+        <v>7050570</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2570,7 +2590,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2580,7 +2600,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2595,26 +2615,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2754,10 +2754,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124262725</v>
+        <v>124260479</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2770,37 +2770,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461642</v>
+        <v>461666</v>
       </c>
       <c r="R17" t="n">
-        <v>7050696</v>
+        <v>7050837</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2829,7 +2834,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2839,12 +2844,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal fuktig granskog nära bäck</t>
+          <t>Fyndplatsen finns intill en bäck i gammal högväxt granskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2855,26 +2860,51 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124263649</v>
+        <v>124262454</v>
       </c>
       <c r="B18" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2883,25 +2913,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2911,10 +2941,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461556</v>
+        <v>461608</v>
       </c>
       <c r="R18" t="n">
-        <v>7050632</v>
+        <v>7050779</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2946,7 +2976,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2956,12 +2986,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal grov sälg i gammal granskog</t>
+          <t>Enstaka bålar på en skadad rönn.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2972,26 +3002,51 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124264084</v>
+        <v>124261248</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3004,37 +3059,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461561</v>
+        <v>461756</v>
       </c>
       <c r="R19" t="n">
-        <v>7050657</v>
+        <v>7050765</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3063,7 +3118,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3073,7 +3128,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3084,51 +3139,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Emil Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124263132</v>
+        <v>124264003</v>
       </c>
       <c r="B20" t="n">
-        <v>91030</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3137,40 +3167,45 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3179,10 +3214,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461570</v>
+        <v>461546</v>
       </c>
       <c r="R20" t="n">
-        <v>7050652</v>
+        <v>7050666</v>
       </c>
       <c r="S20" t="n">
         <v>8</v>
@@ -3214,7 +3249,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3224,12 +3259,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i en grov gran.</t>
+          <t>Minst 51 plantor inom ca 2 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3244,26 +3279,6 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3281,10 +3296,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124259184</v>
+        <v>124262686</v>
       </c>
       <c r="B21" t="n">
-        <v>74901</v>
+        <v>79920</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3293,41 +3308,46 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461677</v>
+        <v>461617</v>
       </c>
       <c r="R21" t="n">
-        <v>7050616</v>
+        <v>7050728</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3356,7 +3376,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3366,12 +3386,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På död gran i sumpgranskog</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3382,26 +3397,51 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124261626</v>
+        <v>124262760</v>
       </c>
       <c r="B22" t="n">
-        <v>56714</v>
+        <v>57883</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3410,20 +3450,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3431,22 +3471,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461768</v>
+        <v>461558</v>
       </c>
       <c r="R22" t="n">
-        <v>7050794</v>
+        <v>7050692</v>
       </c>
       <c r="S22" t="n">
         <v>8</v>
@@ -3478,7 +3522,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3488,7 +3532,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3499,31 +3543,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124262760</v>
+        <v>124260090</v>
       </c>
       <c r="B23" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3532,50 +3571,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461558</v>
+        <v>461642</v>
       </c>
       <c r="R23" t="n">
-        <v>7050692</v>
+        <v>7050845</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3604,7 +3634,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3614,7 +3644,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3625,26 +3655,51 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124262353</v>
+        <v>124262595</v>
       </c>
       <c r="B24" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3657,21 +3712,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3681,13 +3736,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461655</v>
+        <v>461615</v>
       </c>
       <c r="R24" t="n">
-        <v>7050759</v>
+        <v>7050725</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3716,7 +3771,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3726,12 +3781,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På gran ca 40 cm i diameter intill bäck</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3742,26 +3792,51 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124263675</v>
+        <v>124262526</v>
       </c>
       <c r="B25" t="n">
-        <v>79892</v>
+        <v>79927</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3770,25 +3845,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3798,10 +3873,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461551</v>
+        <v>461665</v>
       </c>
       <c r="R25" t="n">
-        <v>7050634</v>
+        <v>7050738</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3833,7 +3908,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3843,12 +3918,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På sälg ca 60 cm i diameter</t>
+          <t>På död rönn intill bäck</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3868,17 +3943,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124261471</v>
+        <v>124260468</v>
       </c>
       <c r="B26" t="n">
-        <v>78547</v>
+        <v>74901</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3891,37 +3966,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461800</v>
+        <v>461783</v>
       </c>
       <c r="R26" t="n">
-        <v>7050827</v>
+        <v>7050722</v>
       </c>
       <c r="S26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3950,7 +4025,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3960,12 +4035,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På kolade tallstubbe.</t>
+          <t>På bark på stam av levande gammal gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3976,51 +4051,26 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Stump # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124262526</v>
+        <v>124260842</v>
       </c>
       <c r="B27" t="n">
-        <v>79927</v>
+        <v>91012</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4029,25 +4079,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -4057,10 +4107,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461665</v>
+        <v>461785</v>
       </c>
       <c r="R27" t="n">
-        <v>7050738</v>
+        <v>7050704</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4092,7 +4142,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4102,12 +4152,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På död rönn intill bäck</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4122,22 +4172,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124260993</v>
+        <v>124259895</v>
       </c>
       <c r="B28" t="n">
-        <v>57529</v>
+        <v>74893</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4150,42 +4200,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Småfloarna, Småfloarna, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461776</v>
+        <v>461797</v>
       </c>
       <c r="R28" t="n">
-        <v>7050859</v>
+        <v>7050670</v>
       </c>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4214,7 +4259,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4224,12 +4269,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rejäla hackspår.</t>
+          <t>Rikligt på ved på basen av granhögstubbe i fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4240,51 +4285,26 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124262198</v>
+        <v>124263001</v>
       </c>
       <c r="B29" t="n">
-        <v>105102</v>
+        <v>79920</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4297,37 +4317,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461687</v>
+        <v>461597</v>
       </c>
       <c r="R29" t="n">
-        <v>7050752</v>
+        <v>7050664</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4356,7 +4381,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4366,12 +4391,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På marken i fuktig gammal granskog</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4382,26 +4402,51 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124260873</v>
+        <v>124263852</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4414,21 +4459,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4438,13 +4483,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461744</v>
+        <v>461549</v>
       </c>
       <c r="R30" t="n">
-        <v>7050919</v>
+        <v>7050671</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4473,7 +4518,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4483,7 +4528,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4494,51 +4544,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124262979</v>
+        <v>124260702</v>
       </c>
       <c r="B31" t="n">
-        <v>91012</v>
+        <v>100279</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4547,46 +4572,46 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461543</v>
+        <v>461678</v>
       </c>
       <c r="R31" t="n">
-        <v>7050645</v>
+        <v>7050823</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4615,7 +4640,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4625,12 +4650,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Både blåvioletta och vita blommor.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4641,26 +4666,31 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124260947</v>
+        <v>124260205</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4669,25 +4699,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4697,10 +4727,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461749</v>
+        <v>461793</v>
       </c>
       <c r="R32" t="n">
-        <v>7050709</v>
+        <v>7050683</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4732,7 +4762,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4742,7 +4772,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På bark på rönnhögststubbe i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4769,10 +4804,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124262878</v>
+        <v>124258944</v>
       </c>
       <c r="B33" t="n">
-        <v>74901</v>
+        <v>57883</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4781,41 +4816,60 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>103015</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461633</v>
+        <v>461559</v>
       </c>
       <c r="R33" t="n">
-        <v>7050666</v>
+        <v>7050789</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4844,7 +4898,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4854,12 +4908,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 170 år) i gammal granskog</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4870,26 +4924,31 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124261077</v>
+        <v>124259251</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4898,41 +4957,50 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461731</v>
+        <v>461721</v>
       </c>
       <c r="R34" t="n">
-        <v>7050711</v>
+        <v>7050576</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4961,7 +5029,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4971,12 +5039,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal fuktig granskog</t>
+          <t>Inom en yta på 3x7m</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4991,22 +5059,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124263250</v>
+        <v>124263066</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5019,21 +5087,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -5043,10 +5111,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461629</v>
+        <v>461654</v>
       </c>
       <c r="R35" t="n">
-        <v>7050621</v>
+        <v>7050616</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5078,7 +5146,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5088,12 +5156,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ett 100-tal bålar på ett 10-tal granar</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5108,22 +5176,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124263059</v>
+        <v>124259759</v>
       </c>
       <c r="B36" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5136,21 +5204,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5160,7 +5228,7 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461654</v>
+        <v>461789</v>
       </c>
       <c r="R36" t="n">
         <v>7050616</v>
@@ -5195,7 +5263,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5205,12 +5273,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran ca 5 m från bäck i äldre granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5225,22 +5293,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124261426</v>
+        <v>124263675</v>
       </c>
       <c r="B37" t="n">
-        <v>78891</v>
+        <v>79892</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5253,21 +5321,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>283</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5277,10 +5345,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461715</v>
+        <v>461551</v>
       </c>
       <c r="R37" t="n">
-        <v>7050700</v>
+        <v>7050634</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5312,7 +5380,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5322,12 +5390,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På kvist på klen gran i gransumpskog</t>
+          <t>På sälg ca 60 cm i diameter</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5347,7 +5415,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -5471,10 +5539,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124259289</v>
+        <v>124262970</v>
       </c>
       <c r="B39" t="n">
-        <v>95347</v>
+        <v>79892</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5483,41 +5551,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2813</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461716</v>
+        <v>461598</v>
       </c>
       <c r="R39" t="n">
-        <v>7050630</v>
+        <v>7050665</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5546,7 +5614,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5556,12 +5624,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På marken i gammal sumpgranskog</t>
+          <t>Enstaka på en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5572,26 +5640,51 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124262807</v>
+        <v>124259946</v>
       </c>
       <c r="B40" t="n">
-        <v>74901</v>
+        <v>78891</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5604,21 +5697,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5628,10 +5721,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461633</v>
+        <v>461815</v>
       </c>
       <c r="R40" t="n">
-        <v>7050701</v>
+        <v>7050652</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5663,7 +5756,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5673,12 +5766,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På gammal gran i gransumpskog</t>
+          <t>På tunn levande gren på gammal klen gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5693,22 +5786,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124259877</v>
+        <v>124260773</v>
       </c>
       <c r="B41" t="n">
-        <v>79891</v>
+        <v>91673</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5717,31 +5810,31 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>898</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5750,13 +5843,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461614</v>
+        <v>461785</v>
       </c>
       <c r="R41" t="n">
-        <v>7050862</v>
+        <v>7050704</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5785,7 +5878,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5795,12 +5888,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ymnig påväxt på en grov gammal sälg där vissa bålar är fertila med apothecier.</t>
+          <t>På gammal ullticka på granlåga i bördig, fuktig lågarik granskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5812,50 +5905,40 @@
       <c r="AG41" t="b">
         <v>0</v>
       </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>ullticka</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124261741</v>
+        <v>124262198</v>
       </c>
       <c r="B42" t="n">
-        <v>90977</v>
+        <v>105102</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5868,21 +5951,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>221725</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5892,13 +5975,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461728</v>
+        <v>461687</v>
       </c>
       <c r="R42" t="n">
-        <v>7050768</v>
+        <v>7050752</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5927,7 +6010,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5937,12 +6020,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På marken i fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5969,10 +6052,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124263103</v>
+        <v>124261444</v>
       </c>
       <c r="B43" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5985,21 +6068,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -6009,13 +6092,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461643</v>
+        <v>461810</v>
       </c>
       <c r="R43" t="n">
-        <v>7050590</v>
+        <v>7050829</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6044,7 +6127,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6054,12 +6137,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På gammal rönn I gammal granskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6086,10 +6169,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124260536</v>
+        <v>124259877</v>
       </c>
       <c r="B44" t="n">
-        <v>100279</v>
+        <v>79891</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6098,38 +6181,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461834</v>
+        <v>461614</v>
       </c>
       <c r="R44" t="n">
-        <v>7050707</v>
+        <v>7050862</v>
       </c>
       <c r="S44" t="n">
         <v>9</v>
@@ -6161,7 +6249,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6171,7 +6259,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ymnig påväxt på en grov gammal sälg där vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6182,26 +6275,51 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124259946</v>
+        <v>124262035</v>
       </c>
       <c r="B45" t="n">
-        <v>78891</v>
+        <v>79891</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6214,37 +6332,46 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>283</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461815</v>
+        <v>461712</v>
       </c>
       <c r="R45" t="n">
-        <v>7050652</v>
+        <v>7050901</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6273,7 +6400,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6283,12 +6410,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På tunn levande gren på gammal klen gran i gammal fuktig granskog</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6303,22 +6430,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124260115</v>
+        <v>124263257</v>
       </c>
       <c r="B46" t="n">
-        <v>100279</v>
+        <v>57529</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6327,31 +6454,35 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6360,13 +6491,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461636</v>
+        <v>461584</v>
       </c>
       <c r="R46" t="n">
-        <v>7050841</v>
+        <v>7050588</v>
       </c>
       <c r="S46" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6395,7 +6526,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6405,7 +6536,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6416,31 +6547,26 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124260054</v>
+        <v>124263802</v>
       </c>
       <c r="B47" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6449,41 +6575,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461843</v>
+        <v>461536</v>
       </c>
       <c r="R47" t="n">
-        <v>7050661</v>
+        <v>7050642</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6512,7 +6638,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6522,7 +6648,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ca 40 ex inom en kvadratmeter</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6537,22 +6668,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Emil Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124260842</v>
+        <v>124262908</v>
       </c>
       <c r="B48" t="n">
-        <v>91012</v>
+        <v>77743</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6565,21 +6696,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6589,10 +6720,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461785</v>
+        <v>461633</v>
       </c>
       <c r="R48" t="n">
-        <v>7050704</v>
+        <v>7050666</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6624,7 +6755,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6634,12 +6765,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran (ca 170 år gammal) i gammal granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6666,10 +6797,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124259169</v>
+        <v>124262348</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6678,25 +6809,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6706,13 +6837,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>461539</v>
+        <v>461656</v>
       </c>
       <c r="R49" t="n">
-        <v>7050804</v>
+        <v>7050743</v>
       </c>
       <c r="S49" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6741,7 +6872,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6751,7 +6882,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På rönn vid bäck</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6762,51 +6898,26 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124260205</v>
+        <v>124262979</v>
       </c>
       <c r="B50" t="n">
-        <v>79920</v>
+        <v>91012</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6815,38 +6926,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>461793</v>
+        <v>461543</v>
       </c>
       <c r="R50" t="n">
-        <v>7050683</v>
+        <v>7050645</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6878,7 +6994,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6888,12 +7004,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På bark på rönnhögststubbe i gammal fuktig granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6908,22 +7024,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124262035</v>
+        <v>124260947</v>
       </c>
       <c r="B51" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6936,46 +7052,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461712</v>
+        <v>461749</v>
       </c>
       <c r="R51" t="n">
-        <v>7050901</v>
+        <v>7050709</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7004,7 +7111,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7014,12 +7121,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7034,22 +7136,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124263683</v>
+        <v>124259378</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7058,57 +7160,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461584</v>
+        <v>461603</v>
       </c>
       <c r="R52" t="n">
-        <v>7050644</v>
+        <v>7050832</v>
       </c>
       <c r="S52" t="n">
         <v>9</v>
@@ -7140,7 +7228,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7150,12 +7238,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Minst 63 plantor inom ca 2 x 1 m2 i gammal granskog.</t>
+          <t>Ymnigt med lunglav på en gammal grov sälg. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7170,6 +7258,26 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7187,7 +7295,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124259759</v>
+        <v>124263837</v>
       </c>
       <c r="B53" t="n">
         <v>77743</v>
@@ -7227,10 +7335,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461789</v>
+        <v>461549</v>
       </c>
       <c r="R53" t="n">
-        <v>7050616</v>
+        <v>7050671</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7262,7 +7370,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7272,12 +7380,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På gammal gran ca 5 m från bäck i äldre granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7292,22 +7400,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124258944</v>
+        <v>124261626</v>
       </c>
       <c r="B54" t="n">
-        <v>57883</v>
+        <v>56714</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7316,20 +7424,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103015</v>
+        <v>102612</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -7337,36 +7445,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>461559</v>
+        <v>461768</v>
       </c>
       <c r="R54" t="n">
-        <v>7050789</v>
+        <v>7050794</v>
       </c>
       <c r="S54" t="n">
         <v>8</v>
@@ -7398,7 +7492,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7408,12 +7502,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7445,10 +7534,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124262348</v>
+        <v>124262353</v>
       </c>
       <c r="B55" t="n">
-        <v>79920</v>
+        <v>77743</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7457,25 +7546,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>228579</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7485,10 +7574,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>461656</v>
+        <v>461655</v>
       </c>
       <c r="R55" t="n">
-        <v>7050743</v>
+        <v>7050759</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7520,7 +7609,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7530,12 +7619,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På rönn vid bäck</t>
+          <t>På gran ca 40 cm i diameter intill bäck</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7550,22 +7639,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124262686</v>
+        <v>124262044</v>
       </c>
       <c r="B56" t="n">
-        <v>79920</v>
+        <v>77743</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7574,46 +7663,41 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>228579</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461617</v>
+        <v>461724</v>
       </c>
       <c r="R56" t="n">
-        <v>7050728</v>
+        <v>7050772</v>
       </c>
       <c r="S56" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7642,7 +7726,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7652,7 +7736,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran (28 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7663,48 +7752,23 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124260468</v>
+        <v>124260631</v>
       </c>
       <c r="B57" t="n">
         <v>74901</v>
@@ -7740,14 +7804,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461783</v>
+        <v>461864</v>
       </c>
       <c r="R57" t="n">
-        <v>7050722</v>
+        <v>7050679</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7779,7 +7843,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7789,12 +7853,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal fuktig granskog</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7809,22 +7868,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124260631</v>
+        <v>124262725</v>
       </c>
       <c r="B58" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7837,34 +7896,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461864</v>
+        <v>461642</v>
       </c>
       <c r="R58" t="n">
-        <v>7050679</v>
+        <v>7050696</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7896,7 +7955,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7906,7 +7965,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal fuktig granskog nära bäck</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7921,22 +7985,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124263170</v>
+        <v>124260175</v>
       </c>
       <c r="B59" t="n">
-        <v>77743</v>
+        <v>74885</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7945,25 +8009,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228579</v>
+        <v>6439</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7973,10 +8037,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461624</v>
+        <v>461793</v>
       </c>
       <c r="R59" t="n">
-        <v>7050624</v>
+        <v>7050683</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8008,7 +8072,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8018,12 +8082,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På gammal gran i fuktig äldre granskog</t>
+          <t>På ved på rönnhögstubbe i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8038,22 +8102,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124263257</v>
+        <v>124262878</v>
       </c>
       <c r="B60" t="n">
-        <v>57529</v>
+        <v>74901</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8066,46 +8130,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461584</v>
+        <v>461633</v>
       </c>
       <c r="R60" t="n">
-        <v>7050588</v>
+        <v>7050666</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8134,7 +8189,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8144,7 +8199,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 170 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8171,7 +8231,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124263802</v>
+        <v>124263683</v>
       </c>
       <c r="B61" t="n">
         <v>98101</v>
@@ -8204,20 +8264,39 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461536</v>
+        <v>461584</v>
       </c>
       <c r="R61" t="n">
-        <v>7050642</v>
+        <v>7050644</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8246,7 +8325,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8256,12 +8335,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ca 40 ex inom en kvadratmeter</t>
+          <t>Minst 63 plantor inom ca 2 x 1 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8272,26 +8351,31 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124241603</v>
+        <v>124261213</v>
       </c>
       <c r="B62" t="n">
-        <v>98101</v>
+        <v>77743</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8300,52 +8384,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461712</v>
+        <v>461731</v>
       </c>
       <c r="R62" t="n">
-        <v>7050513</v>
+        <v>7050704</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8372,27 +8442,27 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Minst 78 plantor och 3 vinterståndare inom ca 1 m2 i gammal granskog.</t>
+          <t>På gammal gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8403,31 +8473,26 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124261167</v>
+        <v>124261741</v>
       </c>
       <c r="B63" t="n">
-        <v>74901</v>
+        <v>90977</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8436,25 +8501,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8464,10 +8529,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461741</v>
+        <v>461728</v>
       </c>
       <c r="R63" t="n">
-        <v>7050704</v>
+        <v>7050768</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8499,7 +8564,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8509,12 +8574,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På gammal gran i gransumpskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8529,22 +8594,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Emil Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124262632</v>
+        <v>124263103</v>
       </c>
       <c r="B64" t="n">
-        <v>79857</v>
+        <v>79891</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8553,25 +8618,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229748</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8581,13 +8646,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461651</v>
+        <v>461643</v>
       </c>
       <c r="R64" t="n">
-        <v>7050724</v>
+        <v>7050590</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8616,7 +8681,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8626,12 +8691,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På rönn vid bäck i gammal granskog</t>
+          <t>På gammal rönn I gammal granskog</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8658,10 +8723,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124263373</v>
+        <v>124260993</v>
       </c>
       <c r="B65" t="n">
-        <v>77743</v>
+        <v>57529</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8674,37 +8739,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228579</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Småfloarna, Småfloarna, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>461587</v>
+        <v>461776</v>
       </c>
       <c r="R65" t="n">
-        <v>7050582</v>
+        <v>7050859</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8733,7 +8803,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8743,7 +8813,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8754,26 +8829,51 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124258793</v>
+        <v>124262632</v>
       </c>
       <c r="B66" t="n">
-        <v>95335</v>
+        <v>79857</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8786,21 +8886,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2809</v>
+        <v>229748</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8810,10 +8910,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>461641</v>
+        <v>461651</v>
       </c>
       <c r="R66" t="n">
-        <v>7050551</v>
+        <v>7050724</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8845,7 +8945,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8855,12 +8955,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På rönn vid bäck i gammal granskog</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8887,10 +8987,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124260158</v>
+        <v>124263373</v>
       </c>
       <c r="B67" t="n">
-        <v>79891</v>
+        <v>77743</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8903,21 +9003,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8927,10 +9027,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461793</v>
+        <v>461587</v>
       </c>
       <c r="R67" t="n">
-        <v>7050683</v>
+        <v>7050582</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8962,7 +9062,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8972,12 +9072,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På bark på död rönnstubbe</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8992,22 +9087,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124259426</v>
+        <v>124263059</v>
       </c>
       <c r="B68" t="n">
-        <v>77743</v>
+        <v>74901</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9020,37 +9115,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>461787</v>
+        <v>461654</v>
       </c>
       <c r="R68" t="n">
-        <v>7050628</v>
+        <v>7050616</v>
       </c>
       <c r="S68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9079,7 +9174,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9089,7 +9184,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9104,22 +9204,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124259895</v>
+        <v>124260158</v>
       </c>
       <c r="B69" t="n">
-        <v>74893</v>
+        <v>79891</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9132,21 +9232,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9156,10 +9256,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>461797</v>
+        <v>461793</v>
       </c>
       <c r="R69" t="n">
-        <v>7050670</v>
+        <v>7050683</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9191,7 +9291,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9201,12 +9301,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Rikligt på ved på basen av granhögstubbe i fuktig gammal granskog</t>
+          <t>På bark på död rönnstubbe</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9226,17 +9326,17 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124262595</v>
+        <v>124261167</v>
       </c>
       <c r="B70" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9249,21 +9349,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9273,13 +9373,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>461615</v>
+        <v>461741</v>
       </c>
       <c r="R70" t="n">
-        <v>7050725</v>
+        <v>7050704</v>
       </c>
       <c r="S70" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9308,7 +9408,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9318,7 +9418,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På gammal gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9329,51 +9434,26 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin, Emil Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124260479</v>
+        <v>124263649</v>
       </c>
       <c r="B71" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9382,46 +9462,41 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>461666</v>
+        <v>461556</v>
       </c>
       <c r="R71" t="n">
-        <v>7050837</v>
+        <v>7050632</v>
       </c>
       <c r="S71" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9450,7 +9525,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9460,12 +9535,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns intill en bäck i gammal högväxt granskog.</t>
+          <t>På gammal grov sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9476,51 +9551,26 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124261444</v>
+        <v>124263536</v>
       </c>
       <c r="B72" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9533,37 +9583,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>461810</v>
+        <v>461544</v>
       </c>
       <c r="R72" t="n">
-        <v>7050829</v>
+        <v>7050635</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9592,7 +9647,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9602,12 +9657,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>Äldre ringhack på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9634,7 +9689,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124259251</v>
+        <v>124241603</v>
       </c>
       <c r="B73" t="n">
         <v>98101</v>
@@ -9669,7 +9724,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>78</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -9677,19 +9732,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>461721</v>
+        <v>461712</v>
       </c>
       <c r="R73" t="n">
-        <v>7050576</v>
+        <v>7050513</v>
       </c>
       <c r="S73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9713,27 +9773,27 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Inom en yta på 3x7m</t>
+          <t>Minst 78 plantor och 3 vinterståndare inom ca 1 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9744,26 +9804,31 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124262970</v>
+        <v>124263170</v>
       </c>
       <c r="B74" t="n">
-        <v>79892</v>
+        <v>77743</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9776,37 +9841,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>461598</v>
+        <v>461624</v>
       </c>
       <c r="R74" t="n">
-        <v>7050665</v>
+        <v>7050624</v>
       </c>
       <c r="S74" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9835,7 +9900,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9845,12 +9910,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Enstaka på en flerstammig sälg.</t>
+          <t>På gammal gran i fuktig äldre granskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9861,51 +9926,26 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124260773</v>
+        <v>124259967</v>
       </c>
       <c r="B75" t="n">
-        <v>91673</v>
+        <v>79891</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9914,31 +9954,31 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>898</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -9947,10 +9987,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>461785</v>
+        <v>461623</v>
       </c>
       <c r="R75" t="n">
-        <v>7050704</v>
+        <v>7050871</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9982,7 +10022,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9992,12 +10032,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>På gammal ullticka på granlåga i bördig, fuktig lågarik granskog</t>
+          <t>Rikligt på en skadad rönn.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10009,37 +10049,47 @@
       <c r="AG75" t="b">
         <v>0</v>
       </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>ullticka</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124259784</v>
+        <v>124262807</v>
       </c>
       <c r="B76" t="n">
         <v>74901</v>
@@ -10079,10 +10129,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>461789</v>
+        <v>461633</v>
       </c>
       <c r="R76" t="n">
-        <v>7050616</v>
+        <v>7050701</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10114,7 +10164,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10124,12 +10174,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>På gammal gran ca 5m från bäck i äldre granskog</t>
+          <t>På gammal gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10156,10 +10206,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124263536</v>
+        <v>124258987</v>
       </c>
       <c r="B77" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10172,42 +10222,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>461544</v>
+        <v>461689</v>
       </c>
       <c r="R77" t="n">
-        <v>7050635</v>
+        <v>7050585</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10236,7 +10281,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10246,12 +10291,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10278,10 +10323,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124262044</v>
+        <v>124264084</v>
       </c>
       <c r="B78" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10294,37 +10339,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>461724</v>
+        <v>461561</v>
       </c>
       <c r="R78" t="n">
-        <v>7050772</v>
+        <v>7050657</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10353,7 +10398,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10363,12 +10408,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:16</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran (28 cm dbh) i gammal granskog</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10379,26 +10419,51 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124261248</v>
+        <v>124263250</v>
       </c>
       <c r="B79" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10411,37 +10476,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>461756</v>
+        <v>461629</v>
       </c>
       <c r="R79" t="n">
-        <v>7050765</v>
+        <v>7050621</v>
       </c>
       <c r="S79" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10470,7 +10535,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10480,7 +10545,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ett 100-tal bålar på ett 10-tal granar</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10495,22 +10565,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Emil Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124263852</v>
+        <v>124261793</v>
       </c>
       <c r="B80" t="n">
-        <v>74901</v>
+        <v>57529</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10523,37 +10593,42 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>461549</v>
+        <v>461776</v>
       </c>
       <c r="R80" t="n">
-        <v>7050671</v>
+        <v>7050867</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10582,7 +10657,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10592,12 +10667,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>Letade efter hästmyra</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10612,22 +10687,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Emil Nordin, Ludvig Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124261793</v>
+        <v>124263225</v>
       </c>
       <c r="B81" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10640,42 +10715,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>461776</v>
+        <v>461603</v>
       </c>
       <c r="R81" t="n">
-        <v>7050867</v>
+        <v>7050578</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10704,7 +10774,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10714,12 +10784,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Letade efter hästmyra</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10734,22 +10804,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>August Nordin, Ludvig Nordin, Emil Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124263066</v>
+        <v>124259784</v>
       </c>
       <c r="B82" t="n">
-        <v>77743</v>
+        <v>74901</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10762,21 +10832,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10786,7 +10856,7 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>461654</v>
+        <v>461789</v>
       </c>
       <c r="R82" t="n">
         <v>7050616</v>
@@ -10821,7 +10891,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10831,12 +10901,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran ca 5m från bäck i äldre granskog</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10851,19 +10921,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124258987</v>
+        <v>124261077</v>
       </c>
       <c r="B83" t="n">
         <v>78810</v>
@@ -10903,10 +10973,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>461689</v>
+        <v>461731</v>
       </c>
       <c r="R83" t="n">
-        <v>7050585</v>
+        <v>7050711</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10938,7 +11008,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10948,12 +11018,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10980,10 +11050,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124263001</v>
+        <v>124260536</v>
       </c>
       <c r="B84" t="n">
-        <v>79920</v>
+        <v>100279</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10996,42 +11066,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6462</v>
+        <v>222498</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>461597</v>
+        <v>461834</v>
       </c>
       <c r="R84" t="n">
-        <v>7050664</v>
+        <v>7050707</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11060,7 +11125,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11070,7 +11135,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11081,51 +11146,26 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124259967</v>
+        <v>124259426</v>
       </c>
       <c r="B85" t="n">
-        <v>79891</v>
+        <v>77743</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11138,42 +11178,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>461623</v>
+        <v>461787</v>
       </c>
       <c r="R85" t="n">
-        <v>7050871</v>
+        <v>7050628</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -11202,7 +11237,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11212,12 +11247,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Rikligt på en skadad rönn.</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11228,51 +11258,26 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124260175</v>
+        <v>124260054</v>
       </c>
       <c r="B86" t="n">
-        <v>74885</v>
+        <v>96979</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11285,37 +11290,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6439</v>
+        <v>221945</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>461793</v>
+        <v>461843</v>
       </c>
       <c r="R86" t="n">
-        <v>7050683</v>
+        <v>7050661</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -11344,7 +11349,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11354,12 +11359,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>På ved på rönnhögstubbe i gammal fuktig granskog</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11374,22 +11374,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124259378</v>
+        <v>124259289</v>
       </c>
       <c r="B87" t="n">
-        <v>79891</v>
+        <v>95347</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11398,46 +11398,41 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>2813</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>461603</v>
+        <v>461716</v>
       </c>
       <c r="R87" t="n">
-        <v>7050832</v>
+        <v>7050630</v>
       </c>
       <c r="S87" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11481,7 +11476,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglav på en gammal grov sälg. Vissa bålar är fertila med apothecier.</t>
+          <t>På marken i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11492,51 +11487,26 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124262454</v>
+        <v>124263132</v>
       </c>
       <c r="B88" t="n">
-        <v>79891</v>
+        <v>91030</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11549,37 +11519,51 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>461608</v>
+        <v>461570</v>
       </c>
       <c r="R88" t="n">
-        <v>7050779</v>
+        <v>7050652</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11608,7 +11592,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11618,12 +11602,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en skadad rönn.</t>
+          <t>Rikligt med fruktkroppar i en grov gran.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11642,12 +11626,12 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM88" t="inlineStr">
@@ -11657,7 +11641,7 @@
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>Stem on living tree # Sorbus aucuparia</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -11675,10 +11659,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124264003</v>
+        <v>124258793</v>
       </c>
       <c r="B89" t="n">
-        <v>98101</v>
+        <v>95335</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11687,60 +11671,41 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>461546</v>
+        <v>461641</v>
       </c>
       <c r="R89" t="n">
-        <v>7050666</v>
+        <v>7050551</v>
       </c>
       <c r="S89" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11769,7 +11734,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11779,12 +11744,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Minst 51 plantor inom ca 2 m2 i gammal granskog.</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11795,31 +11760,26 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
-      </c>
-      <c r="AH89" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124263225</v>
+        <v>124261471</v>
       </c>
       <c r="B90" t="n">
-        <v>91012</v>
+        <v>78547</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11832,37 +11792,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>461603</v>
+        <v>461800</v>
       </c>
       <c r="R90" t="n">
-        <v>7050578</v>
+        <v>7050827</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11891,7 +11851,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11901,12 +11861,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På kolade tallstubbe.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11917,23 +11877,48 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Stump # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124260090</v>
+        <v>124262932</v>
       </c>
       <c r="B91" t="n">
         <v>78810</v>
@@ -11966,20 +11951,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>461642</v>
+        <v>461633</v>
       </c>
       <c r="R91" t="n">
-        <v>7050845</v>
+        <v>7050666</v>
       </c>
       <c r="S91" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -12008,7 +12002,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -12018,7 +12012,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12029,51 +12028,26 @@
       </c>
       <c r="AG91" t="b">
         <v>0</v>
-      </c>
-      <c r="AH91" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124262932</v>
+        <v>124259184</v>
       </c>
       <c r="B92" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12086,43 +12060,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>461633</v>
+        <v>461677</v>
       </c>
       <c r="R92" t="n">
-        <v>7050666</v>
+        <v>7050616</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12154,7 +12119,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -12164,12 +12129,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På död gran i sumpgranskog</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12184,22 +12149,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124260702</v>
+        <v>124260873</v>
       </c>
       <c r="B93" t="n">
-        <v>100279</v>
+        <v>78810</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -12208,46 +12173,41 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>461678</v>
+        <v>461744</v>
       </c>
       <c r="R93" t="n">
-        <v>7050823</v>
+        <v>7050919</v>
       </c>
       <c r="S93" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -12276,7 +12236,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -12286,12 +12246,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Både blåvioletta och vita blommor.</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12306,6 +12261,26 @@
       <c r="AH93" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM93" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -12323,10 +12298,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124261213</v>
+        <v>124260115</v>
       </c>
       <c r="B94" t="n">
-        <v>77743</v>
+        <v>100279</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12335,41 +12310,46 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228579</v>
+        <v>222498</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>461731</v>
+        <v>461636</v>
       </c>
       <c r="R94" t="n">
-        <v>7050704</v>
+        <v>7050841</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -12398,7 +12378,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12408,12 +12388,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:48</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>På gammal gran i gransumpskog</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12424,26 +12399,31 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124262908</v>
+        <v>124261426</v>
       </c>
       <c r="B95" t="n">
-        <v>77743</v>
+        <v>78891</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12456,21 +12436,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228579</v>
+        <v>283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -12480,10 +12460,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>461633</v>
+        <v>461715</v>
       </c>
       <c r="R95" t="n">
-        <v>7050666</v>
+        <v>7050700</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12515,7 +12495,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12525,12 +12505,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (ca 170 år gammal) i gammal granskog</t>
+          <t>På kvist på klen gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12545,22 +12525,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124263837</v>
+        <v>124259169</v>
       </c>
       <c r="B96" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12573,21 +12553,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -12597,13 +12577,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>461549</v>
+        <v>461539</v>
       </c>
       <c r="R96" t="n">
-        <v>7050671</v>
+        <v>7050804</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12632,7 +12612,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12642,12 +12622,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:16</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12658,16 +12633,41 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM96" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>

--- a/artfynd/A 12479-2025 artfynd.xlsx
+++ b/artfynd/A 12479-2025 artfynd.xlsx
@@ -817,10 +817,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124243996</v>
+        <v>124243366</v>
       </c>
       <c r="B3" t="n">
-        <v>79927</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,43 +829,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461837</v>
+        <v>461694</v>
       </c>
       <c r="R3" t="n">
-        <v>7050572</v>
+        <v>7050529</v>
       </c>
       <c r="S3" t="n">
         <v>7</v>
@@ -897,7 +897,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -907,12 +907,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På en grov sälglåga.</t>
+          <t>Rejäla hackspår i en murken granhögstubbe.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,22 +931,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -964,10 +964,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124244069</v>
+        <v>124241982</v>
       </c>
       <c r="B4" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -976,46 +976,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461842</v>
+        <v>461758</v>
       </c>
       <c r="R4" t="n">
-        <v>7050570</v>
+        <v>7050534</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1044,7 +1039,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1054,12 +1049,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På en grov sälglåga.</t>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1111,10 +1106,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124241982</v>
+        <v>124243782</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>95335</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1123,25 +1118,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1151,13 +1146,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461758</v>
+        <v>461757</v>
       </c>
       <c r="R5" t="n">
-        <v>7050534</v>
+        <v>7050561</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1186,7 +1181,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1196,12 +1191,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På en sälglåga.</t>
+          <t>Vid en bäck i gammal granskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1216,26 +1211,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1253,10 +1228,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124242253</v>
+        <v>124244322</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>100279</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1265,41 +1240,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461780</v>
+        <v>461935</v>
       </c>
       <c r="R6" t="n">
-        <v>7050582</v>
+        <v>7050570</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1328,7 +1308,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1338,7 +1318,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1353,26 +1333,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1390,10 +1350,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124244357</v>
+        <v>124242084</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1402,55 +1362,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461909</v>
+        <v>461835</v>
       </c>
       <c r="R7" t="n">
-        <v>7050579</v>
+        <v>7050524</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1479,7 +1425,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1489,12 +1435,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:37</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>I flerskiktad äldre granskog.</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1509,6 +1450,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1526,10 +1487,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124241219</v>
+        <v>124244069</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1538,41 +1499,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461671</v>
+        <v>461842</v>
       </c>
       <c r="R8" t="n">
-        <v>7050487</v>
+        <v>7050570</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1601,7 +1567,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1611,7 +1577,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På en grov sälglåga.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1630,22 +1601,22 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1663,10 +1634,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124244006</v>
+        <v>124244357</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>57883</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1675,41 +1646,55 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461840</v>
+        <v>461909</v>
       </c>
       <c r="R9" t="n">
-        <v>7050563</v>
+        <v>7050579</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1738,7 +1723,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1748,12 +1733,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Enstaka på en grov sälglåga.</t>
+          <t>I flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1768,26 +1753,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1805,10 +1770,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124244443</v>
+        <v>124244006</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1821,21 +1786,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1845,13 +1810,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461867</v>
+        <v>461840</v>
       </c>
       <c r="R10" t="n">
-        <v>7050617</v>
+        <v>7050563</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1880,7 +1845,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1890,12 +1855,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>Enstaka på en grov sälglåga.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1914,22 +1879,22 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1947,7 +1912,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124244822</v>
+        <v>124241219</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1981,24 +1946,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461680</v>
+        <v>461671</v>
       </c>
       <c r="R11" t="n">
-        <v>7050615</v>
+        <v>7050487</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2027,7 +1987,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2037,7 +1997,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2089,7 +2049,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124244983</v>
+        <v>124244822</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -2123,19 +2083,24 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461652</v>
+        <v>461680</v>
       </c>
       <c r="R12" t="n">
-        <v>7050519</v>
+        <v>7050615</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2164,7 +2129,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2174,7 +2139,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2226,7 +2191,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124242084</v>
+        <v>124244983</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -2262,14 +2227,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461835</v>
+        <v>461652</v>
       </c>
       <c r="R13" t="n">
-        <v>7050524</v>
+        <v>7050519</v>
       </c>
       <c r="S13" t="n">
         <v>7</v>
@@ -2301,7 +2266,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2311,7 +2276,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2363,10 +2328,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124243366</v>
+        <v>124243996</v>
       </c>
       <c r="B14" t="n">
-        <v>57529</v>
+        <v>79927</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2375,43 +2340,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461694</v>
+        <v>461837</v>
       </c>
       <c r="R14" t="n">
-        <v>7050529</v>
+        <v>7050572</v>
       </c>
       <c r="S14" t="n">
         <v>7</v>
@@ -2443,7 +2408,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2453,12 +2418,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i en murken granhögstubbe.</t>
+          <t>På en grov sälglåga.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2477,22 +2442,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2510,10 +2475,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124244322</v>
+        <v>124244443</v>
       </c>
       <c r="B15" t="n">
-        <v>100279</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2522,46 +2487,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461935</v>
+        <v>461867</v>
       </c>
       <c r="R15" t="n">
-        <v>7050570</v>
+        <v>7050617</v>
       </c>
       <c r="S15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2590,7 +2550,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2600,7 +2560,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2615,6 +2580,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2632,10 +2617,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124243782</v>
+        <v>124242253</v>
       </c>
       <c r="B16" t="n">
-        <v>95335</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2644,25 +2629,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2672,13 +2657,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461757</v>
+        <v>461780</v>
       </c>
       <c r="R16" t="n">
-        <v>7050561</v>
+        <v>7050582</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2707,7 +2692,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2717,12 +2702,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:12</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Vid en bäck i gammal granskog.</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2737,6 +2717,26 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2754,10 +2754,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124260479</v>
+        <v>124261626</v>
       </c>
       <c r="B17" t="n">
-        <v>79891</v>
+        <v>56714</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2770,42 +2770,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461666</v>
+        <v>461768</v>
       </c>
       <c r="R17" t="n">
-        <v>7050837</v>
+        <v>7050794</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2844,12 +2844,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:23</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Fyndplatsen finns intill en bäck i gammal högväxt granskog.</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2864,26 +2859,6 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2901,10 +2876,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124262454</v>
+        <v>124263250</v>
       </c>
       <c r="B18" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2917,21 +2892,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2941,10 +2916,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461608</v>
+        <v>461629</v>
       </c>
       <c r="R18" t="n">
-        <v>7050779</v>
+        <v>7050621</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2976,7 +2951,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2986,12 +2961,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en skadad rönn.</t>
+          <t>Ett 100-tal bålar på ett 10-tal granar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3002,51 +2977,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124261248</v>
+        <v>124260993</v>
       </c>
       <c r="B19" t="n">
-        <v>91030</v>
+        <v>57529</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3059,37 +3009,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Småfloarna, Småfloarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461756</v>
+        <v>461776</v>
       </c>
       <c r="R19" t="n">
-        <v>7050765</v>
+        <v>7050859</v>
       </c>
       <c r="S19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3118,7 +3073,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3128,7 +3083,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3139,26 +3099,51 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Emil Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124264003</v>
+        <v>124262526</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3167,60 +3152,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461546</v>
+        <v>461665</v>
       </c>
       <c r="R20" t="n">
-        <v>7050666</v>
+        <v>7050738</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3249,7 +3215,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3259,12 +3225,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Minst 51 plantor inom ca 2 m2 i gammal granskog.</t>
+          <t>På död rönn intill bäck</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3275,31 +3241,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124262686</v>
+        <v>124263225</v>
       </c>
       <c r="B21" t="n">
-        <v>79920</v>
+        <v>91012</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3308,46 +3269,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461617</v>
+        <v>461603</v>
       </c>
       <c r="R21" t="n">
-        <v>7050728</v>
+        <v>7050578</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3376,7 +3332,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3386,7 +3342,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3397,51 +3358,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124262760</v>
+        <v>124260773</v>
       </c>
       <c r="B22" t="n">
-        <v>57883</v>
+        <v>91673</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3450,35 +3386,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>898</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3487,13 +3419,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461558</v>
+        <v>461785</v>
       </c>
       <c r="R22" t="n">
-        <v>7050692</v>
+        <v>7050704</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3522,7 +3454,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3532,7 +3464,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På gammal ullticka på granlåga i bördig, fuktig lågarik granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3543,26 +3480,41 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124260090</v>
+        <v>124259967</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3575,37 +3527,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461642</v>
+        <v>461623</v>
       </c>
       <c r="R23" t="n">
-        <v>7050845</v>
+        <v>7050871</v>
       </c>
       <c r="S23" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3634,7 +3591,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3644,7 +3601,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt på en skadad rönn.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3663,22 +3625,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3696,10 +3658,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124262595</v>
+        <v>124263675</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3712,21 +3674,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3736,13 +3698,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461615</v>
+        <v>461551</v>
       </c>
       <c r="R24" t="n">
-        <v>7050725</v>
+        <v>7050634</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3771,7 +3733,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3781,7 +3743,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På sälg ca 60 cm i diameter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3792,51 +3759,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124262526</v>
+        <v>124259895</v>
       </c>
       <c r="B25" t="n">
-        <v>79927</v>
+        <v>74893</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3845,25 +3787,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3873,10 +3815,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461665</v>
+        <v>461797</v>
       </c>
       <c r="R25" t="n">
-        <v>7050738</v>
+        <v>7050670</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3908,7 +3850,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3918,12 +3860,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På död rönn intill bäck</t>
+          <t>Rikligt på ved på basen av granhögstubbe i fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3938,22 +3880,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124260468</v>
+        <v>124260115</v>
       </c>
       <c r="B26" t="n">
-        <v>74901</v>
+        <v>100279</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3962,41 +3904,46 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461783</v>
+        <v>461636</v>
       </c>
       <c r="R26" t="n">
-        <v>7050722</v>
+        <v>7050841</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4025,7 +3972,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4035,12 +3982,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal fuktig granskog</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4051,26 +3993,31 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124260842</v>
+        <v>124263837</v>
       </c>
       <c r="B27" t="n">
-        <v>91012</v>
+        <v>77743</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4083,21 +4030,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -4107,10 +4054,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461785</v>
+        <v>461549</v>
       </c>
       <c r="R27" t="n">
-        <v>7050704</v>
+        <v>7050671</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4142,7 +4089,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4152,12 +4099,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4177,17 +4124,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124259895</v>
+        <v>124263373</v>
       </c>
       <c r="B28" t="n">
-        <v>74893</v>
+        <v>77743</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4200,21 +4147,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>308</v>
+        <v>228579</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4224,10 +4171,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461797</v>
+        <v>461587</v>
       </c>
       <c r="R28" t="n">
-        <v>7050670</v>
+        <v>7050582</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4259,7 +4206,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4269,12 +4216,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt på ved på basen av granhögstubbe i fuktig gammal granskog</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4289,22 +4231,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124263001</v>
+        <v>124260090</v>
       </c>
       <c r="B29" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4313,46 +4255,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461597</v>
+        <v>461642</v>
       </c>
       <c r="R29" t="n">
-        <v>7050664</v>
+        <v>7050845</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4381,7 +4318,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4391,7 +4328,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4410,22 +4347,22 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4443,7 +4380,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124263852</v>
+        <v>124263059</v>
       </c>
       <c r="B30" t="n">
         <v>74901</v>
@@ -4483,10 +4420,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461549</v>
+        <v>461654</v>
       </c>
       <c r="R30" t="n">
-        <v>7050671</v>
+        <v>7050616</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4518,7 +4455,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4528,12 +4465,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4553,17 +4490,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124260702</v>
+        <v>124262725</v>
       </c>
       <c r="B31" t="n">
-        <v>100279</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4572,46 +4509,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461678</v>
+        <v>461642</v>
       </c>
       <c r="R31" t="n">
-        <v>7050823</v>
+        <v>7050696</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4640,7 +4572,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4650,12 +4582,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Både blåvioletta och vita blommor.</t>
+          <t>På gammal gran i gammal fuktig granskog nära bäck</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4666,31 +4598,26 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124260205</v>
+        <v>124264084</v>
       </c>
       <c r="B32" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4699,41 +4626,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461793</v>
+        <v>461561</v>
       </c>
       <c r="R32" t="n">
-        <v>7050683</v>
+        <v>7050657</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4762,7 +4689,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4772,12 +4699,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På bark på rönnhögststubbe i gammal fuktig granskog</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4788,26 +4710,51 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124258944</v>
+        <v>124262454</v>
       </c>
       <c r="B33" t="n">
-        <v>57883</v>
+        <v>79891</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4816,60 +4763,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461559</v>
+        <v>461608</v>
       </c>
       <c r="R33" t="n">
-        <v>7050789</v>
+        <v>7050779</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4898,7 +4826,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4908,12 +4836,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>Enstaka bålar på en skadad rönn.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4928,6 +4856,26 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4945,10 +4893,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124259251</v>
+        <v>124260873</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4957,50 +4905,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461721</v>
+        <v>461744</v>
       </c>
       <c r="R34" t="n">
-        <v>7050576</v>
+        <v>7050919</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5029,7 +4968,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5039,12 +4978,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Inom en yta på 3x7m</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5055,26 +4989,51 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124263066</v>
+        <v>124262348</v>
       </c>
       <c r="B35" t="n">
-        <v>77743</v>
+        <v>79920</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5083,25 +5042,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228579</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -5111,10 +5070,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461654</v>
+        <v>461656</v>
       </c>
       <c r="R35" t="n">
-        <v>7050616</v>
+        <v>7050743</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5146,7 +5105,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5156,12 +5115,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På rönn vid bäck</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5188,10 +5147,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124259759</v>
+        <v>124262198</v>
       </c>
       <c r="B36" t="n">
-        <v>77743</v>
+        <v>105102</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5200,25 +5159,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228579</v>
+        <v>221725</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5228,13 +5187,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461789</v>
+        <v>461687</v>
       </c>
       <c r="R36" t="n">
-        <v>7050616</v>
+        <v>7050752</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5263,7 +5222,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5273,12 +5232,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På gammal gran ca 5 m från bäck i äldre granskog</t>
+          <t>På marken i fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5293,19 +5252,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124263675</v>
+        <v>124262970</v>
       </c>
       <c r="B37" t="n">
         <v>79892</v>
@@ -5341,17 +5300,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461551</v>
+        <v>461598</v>
       </c>
       <c r="R37" t="n">
-        <v>7050634</v>
+        <v>7050665</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5380,7 +5339,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5390,12 +5349,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På sälg ca 60 cm i diameter</t>
+          <t>Enstaka på en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5406,26 +5365,51 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124261849</v>
+        <v>124263536</v>
       </c>
       <c r="B38" t="n">
-        <v>78891</v>
+        <v>57513</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5438,37 +5422,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>283</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461733</v>
+        <v>461544</v>
       </c>
       <c r="R38" t="n">
-        <v>7050778</v>
+        <v>7050635</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5497,7 +5486,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5507,12 +5496,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ett ex på klen gran som saknar topp i äldre granskog</t>
+          <t>Äldre ringhack på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5527,22 +5516,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124262970</v>
+        <v>124259784</v>
       </c>
       <c r="B39" t="n">
-        <v>79892</v>
+        <v>74901</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5555,37 +5544,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461598</v>
+        <v>461789</v>
       </c>
       <c r="R39" t="n">
-        <v>7050665</v>
+        <v>7050616</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5614,7 +5603,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5624,12 +5613,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Enstaka på en flerstammig sälg.</t>
+          <t>På gammal gran ca 5m från bäck i äldre granskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5640,51 +5629,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124259946</v>
+        <v>124260536</v>
       </c>
       <c r="B40" t="n">
-        <v>78891</v>
+        <v>100279</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5693,41 +5657,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>283</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461815</v>
+        <v>461834</v>
       </c>
       <c r="R40" t="n">
-        <v>7050652</v>
+        <v>7050707</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5756,7 +5720,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5766,12 +5730,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På tunn levande gren på gammal klen gran i gammal fuktig granskog</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5786,22 +5745,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124260773</v>
+        <v>124262908</v>
       </c>
       <c r="B41" t="n">
-        <v>91673</v>
+        <v>77743</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5810,43 +5769,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>898</v>
+        <v>228579</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461785</v>
+        <v>461633</v>
       </c>
       <c r="R41" t="n">
-        <v>7050704</v>
+        <v>7050666</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5878,7 +5832,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5888,12 +5842,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På gammal ullticka på granlåga i bördig, fuktig lågarik granskog</t>
+          <t>På bark på stam av levande gammal gran (ca 170 år gammal) i gammal granskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5904,21 +5858,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5928,17 +5867,17 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124262198</v>
+        <v>124261213</v>
       </c>
       <c r="B42" t="n">
-        <v>105102</v>
+        <v>77743</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5947,25 +5886,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221725</v>
+        <v>228579</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5975,13 +5914,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461687</v>
+        <v>461731</v>
       </c>
       <c r="R42" t="n">
-        <v>7050752</v>
+        <v>7050704</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6010,7 +5949,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6020,12 +5959,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På marken i fuktig gammal granskog</t>
+          <t>På gammal gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6040,22 +5979,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124261444</v>
+        <v>124262807</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6068,21 +6007,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -6092,10 +6031,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461810</v>
+        <v>461633</v>
       </c>
       <c r="R43" t="n">
-        <v>7050829</v>
+        <v>7050701</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6127,7 +6066,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6137,12 +6076,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På gammal gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6157,22 +6096,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124259877</v>
+        <v>124260205</v>
       </c>
       <c r="B44" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6181,46 +6120,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461614</v>
+        <v>461793</v>
       </c>
       <c r="R44" t="n">
-        <v>7050862</v>
+        <v>7050683</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6249,7 +6183,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6259,12 +6193,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ymnig påväxt på en grov gammal sälg där vissa bålar är fertila med apothecier.</t>
+          <t>På bark på rönnhögststubbe i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6275,51 +6209,26 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124262035</v>
+        <v>124260842</v>
       </c>
       <c r="B45" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6332,46 +6241,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461712</v>
+        <v>461785</v>
       </c>
       <c r="R45" t="n">
-        <v>7050901</v>
+        <v>7050704</v>
       </c>
       <c r="S45" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6400,7 +6300,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6410,12 +6310,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6430,22 +6330,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124263257</v>
+        <v>124262044</v>
       </c>
       <c r="B46" t="n">
-        <v>57529</v>
+        <v>77743</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6458,46 +6358,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>228579</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461584</v>
+        <v>461724</v>
       </c>
       <c r="R46" t="n">
-        <v>7050588</v>
+        <v>7050772</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6526,7 +6417,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6536,7 +6427,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran (28 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6563,10 +6459,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124263802</v>
+        <v>124263001</v>
       </c>
       <c r="B47" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6575,38 +6471,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461536</v>
+        <v>461597</v>
       </c>
       <c r="R47" t="n">
-        <v>7050642</v>
+        <v>7050664</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6638,7 +6539,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6648,12 +6549,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ca 40 ex inom en kvadratmeter</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6664,26 +6560,51 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124262908</v>
+        <v>124260175</v>
       </c>
       <c r="B48" t="n">
-        <v>77743</v>
+        <v>74885</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6692,25 +6613,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228579</v>
+        <v>6439</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6720,10 +6641,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461633</v>
+        <v>461793</v>
       </c>
       <c r="R48" t="n">
-        <v>7050666</v>
+        <v>7050683</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6755,7 +6676,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6765,12 +6686,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (ca 170 år gammal) i gammal granskog</t>
+          <t>På ved på rönnhögstubbe i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6797,10 +6718,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124262348</v>
+        <v>124260468</v>
       </c>
       <c r="B49" t="n">
-        <v>79920</v>
+        <v>74901</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6809,25 +6730,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6837,10 +6758,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>461656</v>
+        <v>461783</v>
       </c>
       <c r="R49" t="n">
-        <v>7050743</v>
+        <v>7050722</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6872,7 +6793,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6882,12 +6803,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På rönn vid bäck</t>
+          <t>På bark på stam av levande gammal gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6914,10 +6835,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124262979</v>
+        <v>124263132</v>
       </c>
       <c r="B50" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6930,24 +6851,33 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -6959,13 +6889,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>461543</v>
+        <v>461570</v>
       </c>
       <c r="R50" t="n">
-        <v>7050645</v>
+        <v>7050652</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6994,7 +6924,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7004,12 +6934,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Rikligt med fruktkroppar i en grov gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7020,26 +6950,51 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124260947</v>
+        <v>124261426</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>78891</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7052,21 +7007,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -7076,10 +7031,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461749</v>
+        <v>461715</v>
       </c>
       <c r="R51" t="n">
-        <v>7050709</v>
+        <v>7050700</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7111,7 +7066,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7121,7 +7076,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På kvist på klen gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7136,22 +7096,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124259378</v>
+        <v>124261167</v>
       </c>
       <c r="B52" t="n">
-        <v>79891</v>
+        <v>74901</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7164,42 +7124,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461603</v>
+        <v>461741</v>
       </c>
       <c r="R52" t="n">
-        <v>7050832</v>
+        <v>7050704</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7228,7 +7183,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7238,12 +7193,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglav på en gammal grov sälg. Vissa bålar är fertila med apothecier.</t>
+          <t>På gammal gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7254,51 +7209,26 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin, Emil Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124263837</v>
+        <v>124262932</v>
       </c>
       <c r="B53" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7311,34 +7241,43 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461549</v>
+        <v>461633</v>
       </c>
       <c r="R53" t="n">
-        <v>7050671</v>
+        <v>7050666</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7370,7 +7309,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7380,12 +7319,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7405,17 +7344,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124261626</v>
+        <v>124263649</v>
       </c>
       <c r="B54" t="n">
-        <v>56714</v>
+        <v>79920</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7424,46 +7363,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>102612</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>461768</v>
+        <v>461556</v>
       </c>
       <c r="R54" t="n">
-        <v>7050794</v>
+        <v>7050632</v>
       </c>
       <c r="S54" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7492,7 +7426,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7502,7 +7436,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På gammal grov sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7513,31 +7452,26 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124262353</v>
+        <v>124258793</v>
       </c>
       <c r="B55" t="n">
-        <v>77743</v>
+        <v>95335</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7546,25 +7480,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228579</v>
+        <v>2809</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7574,10 +7508,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>461655</v>
+        <v>461641</v>
       </c>
       <c r="R55" t="n">
-        <v>7050759</v>
+        <v>7050551</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7609,7 +7543,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7619,12 +7553,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På gran ca 40 cm i diameter intill bäck</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7639,22 +7573,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124262044</v>
+        <v>124262632</v>
       </c>
       <c r="B56" t="n">
-        <v>77743</v>
+        <v>79857</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7663,25 +7597,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228579</v>
+        <v>229748</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7691,10 +7625,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461724</v>
+        <v>461651</v>
       </c>
       <c r="R56" t="n">
-        <v>7050772</v>
+        <v>7050724</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7726,7 +7660,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7736,12 +7670,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (28 cm dbh) i gammal granskog</t>
+          <t>På rönn vid bäck i gammal granskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7768,10 +7702,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124260631</v>
+        <v>124261444</v>
       </c>
       <c r="B57" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7784,34 +7718,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461864</v>
+        <v>461810</v>
       </c>
       <c r="R57" t="n">
-        <v>7050679</v>
+        <v>7050829</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7843,7 +7777,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7853,7 +7787,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7868,22 +7807,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124262725</v>
+        <v>124263257</v>
       </c>
       <c r="B58" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7896,37 +7835,46 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461642</v>
+        <v>461584</v>
       </c>
       <c r="R58" t="n">
-        <v>7050696</v>
+        <v>7050588</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7955,7 +7903,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7965,12 +7913,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal fuktig granskog nära bäck</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7997,10 +7940,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124260175</v>
+        <v>124259378</v>
       </c>
       <c r="B59" t="n">
-        <v>74885</v>
+        <v>79891</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8009,41 +7952,46 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6439</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461793</v>
+        <v>461603</v>
       </c>
       <c r="R59" t="n">
-        <v>7050683</v>
+        <v>7050832</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8072,7 +8020,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8082,12 +8030,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På ved på rönnhögstubbe i gammal fuktig granskog</t>
+          <t>Ymnigt med lunglav på en gammal grov sälg. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8098,26 +8046,51 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124262878</v>
+        <v>124263066</v>
       </c>
       <c r="B60" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8130,21 +8103,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -8154,10 +8127,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461633</v>
+        <v>461654</v>
       </c>
       <c r="R60" t="n">
-        <v>7050666</v>
+        <v>7050616</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8189,7 +8162,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8199,12 +8172,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 170 år) i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8231,10 +8204,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124263683</v>
+        <v>124262353</v>
       </c>
       <c r="B61" t="n">
-        <v>98101</v>
+        <v>77743</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8243,60 +8216,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461584</v>
+        <v>461655</v>
       </c>
       <c r="R61" t="n">
-        <v>7050644</v>
+        <v>7050759</v>
       </c>
       <c r="S61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8325,7 +8279,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8335,12 +8289,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Minst 63 plantor inom ca 2 x 1 m2 i gammal granskog.</t>
+          <t>På gran ca 40 cm i diameter intill bäck</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8351,31 +8305,26 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124261213</v>
+        <v>124262760</v>
       </c>
       <c r="B62" t="n">
-        <v>77743</v>
+        <v>57883</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8384,41 +8333,50 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228579</v>
+        <v>103015</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461731</v>
+        <v>461558</v>
       </c>
       <c r="R62" t="n">
-        <v>7050704</v>
+        <v>7050692</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8447,7 +8405,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8457,12 +8415,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:48</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>På gammal gran i gransumpskog</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8477,22 +8430,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124261741</v>
+        <v>124259251</v>
       </c>
       <c r="B63" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8501,41 +8454,50 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461728</v>
+        <v>461721</v>
       </c>
       <c r="R63" t="n">
-        <v>7050768</v>
+        <v>7050576</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8564,7 +8526,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8574,12 +8536,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>Inom en yta på 3x7m</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8594,22 +8556,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>August Nordin, Emil Nordin, Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124263103</v>
+        <v>124263802</v>
       </c>
       <c r="B64" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8618,25 +8580,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8646,13 +8608,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461643</v>
+        <v>461536</v>
       </c>
       <c r="R64" t="n">
-        <v>7050590</v>
+        <v>7050642</v>
       </c>
       <c r="S64" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8681,7 +8643,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8691,12 +8653,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På gammal rönn I gammal granskog</t>
+          <t>Ca 40 ex inom en kvadratmeter</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8711,22 +8673,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124260993</v>
+        <v>124263683</v>
       </c>
       <c r="B65" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8735,46 +8697,60 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Småfloarna, Småfloarna, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>461776</v>
+        <v>461584</v>
       </c>
       <c r="R65" t="n">
-        <v>7050859</v>
+        <v>7050644</v>
       </c>
       <c r="S65" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8803,7 +8779,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8813,12 +8789,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Rejäla hackspår.</t>
+          <t>Minst 63 plantor inom ca 2 x 1 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8833,26 +8809,6 @@
       <c r="AH65" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8870,10 +8826,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124262632</v>
+        <v>124258987</v>
       </c>
       <c r="B66" t="n">
-        <v>79857</v>
+        <v>78810</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8882,25 +8838,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8910,10 +8866,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>461651</v>
+        <v>461689</v>
       </c>
       <c r="R66" t="n">
-        <v>7050724</v>
+        <v>7050585</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8945,7 +8901,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8955,12 +8911,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På rönn vid bäck i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8987,7 +8943,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124263373</v>
+        <v>124259426</v>
       </c>
       <c r="B67" t="n">
         <v>77743</v>
@@ -9023,17 +8979,17 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461587</v>
+        <v>461787</v>
       </c>
       <c r="R67" t="n">
-        <v>7050582</v>
+        <v>7050628</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9062,7 +9018,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9072,7 +9028,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9087,22 +9043,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124263059</v>
+        <v>124261793</v>
       </c>
       <c r="B68" t="n">
-        <v>74901</v>
+        <v>57529</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9115,37 +9071,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>461654</v>
+        <v>461776</v>
       </c>
       <c r="R68" t="n">
-        <v>7050616</v>
+        <v>7050867</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9174,7 +9135,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9184,12 +9145,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Letade efter hästmyra</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9204,22 +9165,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>August Nordin, Ludvig Nordin, Emil Nordin</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124260158</v>
+        <v>124259946</v>
       </c>
       <c r="B69" t="n">
-        <v>79891</v>
+        <v>78891</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9232,21 +9193,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9256,10 +9217,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>461793</v>
+        <v>461815</v>
       </c>
       <c r="R69" t="n">
-        <v>7050683</v>
+        <v>7050652</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9291,7 +9252,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9301,12 +9262,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På bark på död rönnstubbe</t>
+          <t>På tunn levande gren på gammal klen gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9326,17 +9287,17 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124261167</v>
+        <v>124264003</v>
       </c>
       <c r="B70" t="n">
-        <v>74901</v>
+        <v>98101</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9345,41 +9306,60 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>461741</v>
+        <v>461546</v>
       </c>
       <c r="R70" t="n">
-        <v>7050704</v>
+        <v>7050666</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9408,7 +9388,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9418,12 +9398,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På gammal gran i gransumpskog</t>
+          <t>Minst 51 plantor inom ca 2 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9434,26 +9414,31 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Emil Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124263649</v>
+        <v>124263103</v>
       </c>
       <c r="B71" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9462,25 +9447,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9490,13 +9475,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>461556</v>
+        <v>461643</v>
       </c>
       <c r="R71" t="n">
-        <v>7050632</v>
+        <v>7050590</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9525,7 +9510,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9535,12 +9520,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På gammal grov sälg i gammal granskog</t>
+          <t>På gammal rönn I gammal granskog</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9560,17 +9545,17 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124263536</v>
+        <v>124263852</v>
       </c>
       <c r="B72" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9583,42 +9568,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>461544</v>
+        <v>461549</v>
       </c>
       <c r="R72" t="n">
-        <v>7050635</v>
+        <v>7050671</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9647,7 +9627,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9657,12 +9637,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9682,17 +9662,17 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124241603</v>
+        <v>124262035</v>
       </c>
       <c r="B73" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9701,55 +9681,50 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
         <v>461712</v>
       </c>
       <c r="R73" t="n">
-        <v>7050513</v>
+        <v>7050901</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9773,27 +9748,27 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Minst 78 plantor och 3 vinterståndare inom ca 1 m2 i gammal granskog.</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9804,31 +9779,26 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124263170</v>
+        <v>124260631</v>
       </c>
       <c r="B74" t="n">
-        <v>77743</v>
+        <v>74901</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9841,34 +9811,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>461624</v>
+        <v>461864</v>
       </c>
       <c r="R74" t="n">
-        <v>7050624</v>
+        <v>7050679</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9900,7 +9870,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9910,12 +9880,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På gammal gran i fuktig äldre granskog</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9930,22 +9895,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124259967</v>
+        <v>124261077</v>
       </c>
       <c r="B75" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9958,39 +9923,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>461623</v>
+        <v>461731</v>
       </c>
       <c r="R75" t="n">
-        <v>7050871</v>
+        <v>7050711</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10022,7 +9982,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10032,12 +9992,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Rikligt på en skadad rönn.</t>
+          <t>På gammal gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10048,51 +10008,26 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124262807</v>
+        <v>124261471</v>
       </c>
       <c r="B76" t="n">
-        <v>74901</v>
+        <v>78547</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10105,37 +10040,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>461633</v>
+        <v>461800</v>
       </c>
       <c r="R76" t="n">
-        <v>7050701</v>
+        <v>7050827</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -10164,7 +10099,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10174,12 +10109,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>På gammal gran i gransumpskog</t>
+          <t>På kolade tallstubbe.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10190,26 +10125,51 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Stump # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124258987</v>
+        <v>124261248</v>
       </c>
       <c r="B77" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10222,37 +10182,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>461689</v>
+        <v>461756</v>
       </c>
       <c r="R77" t="n">
-        <v>7050585</v>
+        <v>7050765</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10281,7 +10241,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10291,12 +10251,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10311,19 +10266,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Emil Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124264084</v>
+        <v>124262595</v>
       </c>
       <c r="B78" t="n">
         <v>78810</v>
@@ -10359,17 +10314,17 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>461561</v>
+        <v>461615</v>
       </c>
       <c r="R78" t="n">
-        <v>7050657</v>
+        <v>7050725</v>
       </c>
       <c r="S78" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10398,7 +10353,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10408,7 +10363,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10437,12 +10392,12 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10460,10 +10415,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124263250</v>
+        <v>124260158</v>
       </c>
       <c r="B79" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10476,21 +10431,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10500,10 +10455,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>461629</v>
+        <v>461793</v>
       </c>
       <c r="R79" t="n">
-        <v>7050621</v>
+        <v>7050683</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10535,7 +10490,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10545,12 +10500,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ett 100-tal bålar på ett 10-tal granar</t>
+          <t>På bark på död rönnstubbe</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10565,22 +10520,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124261793</v>
+        <v>124259289</v>
       </c>
       <c r="B80" t="n">
-        <v>57529</v>
+        <v>95347</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10589,46 +10544,41 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>2813</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>461776</v>
+        <v>461716</v>
       </c>
       <c r="R80" t="n">
-        <v>7050867</v>
+        <v>7050630</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10657,7 +10607,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10667,12 +10617,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Letade efter hästmyra</t>
+          <t>På marken i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10687,22 +10637,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Emil Nordin, Ludvig Nordin, August Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124263225</v>
+        <v>124258944</v>
       </c>
       <c r="B81" t="n">
-        <v>91012</v>
+        <v>57883</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10711,41 +10661,60 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>461603</v>
+        <v>461559</v>
       </c>
       <c r="R81" t="n">
-        <v>7050578</v>
+        <v>7050789</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10774,7 +10743,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10784,12 +10753,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10800,26 +10769,31 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124259784</v>
+        <v>124259169</v>
       </c>
       <c r="B82" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10832,21 +10806,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10856,13 +10830,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>461789</v>
+        <v>461539</v>
       </c>
       <c r="R82" t="n">
-        <v>7050616</v>
+        <v>7050804</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10891,7 +10865,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10901,12 +10875,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>På gammal gran ca 5m från bäck i äldre granskog</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10917,23 +10886,48 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124261077</v>
+        <v>124260947</v>
       </c>
       <c r="B83" t="n">
         <v>78810</v>
@@ -10973,10 +10967,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>461731</v>
+        <v>461749</v>
       </c>
       <c r="R83" t="n">
-        <v>7050711</v>
+        <v>7050709</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11008,7 +11002,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11018,12 +11012,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:44</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal fuktig granskog</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11050,10 +11039,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124260536</v>
+        <v>124262686</v>
       </c>
       <c r="B84" t="n">
-        <v>100279</v>
+        <v>79920</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11066,37 +11055,42 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>222498</v>
+        <v>6462</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>461834</v>
+        <v>461617</v>
       </c>
       <c r="R84" t="n">
-        <v>7050707</v>
+        <v>7050728</v>
       </c>
       <c r="S84" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11125,7 +11119,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11135,7 +11129,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11146,26 +11140,51 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124259426</v>
+        <v>124259877</v>
       </c>
       <c r="B85" t="n">
-        <v>77743</v>
+        <v>79891</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11178,34 +11197,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>461787</v>
+        <v>461614</v>
       </c>
       <c r="R85" t="n">
-        <v>7050628</v>
+        <v>7050862</v>
       </c>
       <c r="S85" t="n">
         <v>9</v>
@@ -11237,7 +11261,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11247,7 +11271,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ymnig påväxt på en grov gammal sälg där vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11258,26 +11287,51 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124260054</v>
+        <v>124261741</v>
       </c>
       <c r="B86" t="n">
-        <v>96979</v>
+        <v>90977</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11290,37 +11344,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>461843</v>
+        <v>461728</v>
       </c>
       <c r="R86" t="n">
-        <v>7050661</v>
+        <v>7050768</v>
       </c>
       <c r="S86" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -11349,7 +11403,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11359,7 +11413,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11374,22 +11433,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Emil Nordin, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124259289</v>
+        <v>124241603</v>
       </c>
       <c r="B87" t="n">
-        <v>95347</v>
+        <v>98101</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11398,38 +11457,52 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2813</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>461716</v>
+        <v>461712</v>
       </c>
       <c r="R87" t="n">
-        <v>7050630</v>
+        <v>7050513</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11456,27 +11529,27 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>På marken i gammal sumpgranskog</t>
+          <t>Minst 78 plantor och 3 vinterståndare inom ca 1 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11487,26 +11560,31 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124263132</v>
+        <v>124260479</v>
       </c>
       <c r="B88" t="n">
-        <v>91030</v>
+        <v>79891</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11519,51 +11597,42 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>461570</v>
+        <v>461666</v>
       </c>
       <c r="R88" t="n">
-        <v>7050652</v>
+        <v>7050837</v>
       </c>
       <c r="S88" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11592,7 +11661,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11602,12 +11671,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i en grov gran.</t>
+          <t>Fyndplatsen finns intill en bäck i gammal högväxt granskog.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11626,22 +11695,22 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -11659,10 +11728,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124258793</v>
+        <v>124260054</v>
       </c>
       <c r="B89" t="n">
-        <v>95335</v>
+        <v>96979</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11675,37 +11744,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2809</v>
+        <v>221945</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>461641</v>
+        <v>461843</v>
       </c>
       <c r="R89" t="n">
-        <v>7050551</v>
+        <v>7050661</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11734,7 +11803,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11744,12 +11813,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:41</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11764,22 +11828,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Emil Nordin</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124261471</v>
+        <v>124259759</v>
       </c>
       <c r="B90" t="n">
-        <v>78547</v>
+        <v>77743</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11792,37 +11856,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>228579</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>461800</v>
+        <v>461789</v>
       </c>
       <c r="R90" t="n">
-        <v>7050827</v>
+        <v>7050616</v>
       </c>
       <c r="S90" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11851,7 +11915,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11861,12 +11925,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På kolade tallstubbe.</t>
+          <t>På gammal gran ca 5 m från bäck i äldre granskog</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11877,51 +11941,26 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Stump # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124262932</v>
+        <v>124263170</v>
       </c>
       <c r="B91" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11934,43 +11973,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>461633</v>
+        <v>461624</v>
       </c>
       <c r="R91" t="n">
-        <v>7050666</v>
+        <v>7050624</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12002,7 +12032,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -12012,12 +12042,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På gammal gran i fuktig äldre granskog</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12032,12 +12062,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -12161,10 +12191,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124260873</v>
+        <v>124262878</v>
       </c>
       <c r="B93" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -12177,21 +12207,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -12201,13 +12231,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>461744</v>
+        <v>461633</v>
       </c>
       <c r="R93" t="n">
-        <v>7050919</v>
+        <v>7050666</v>
       </c>
       <c r="S93" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -12236,7 +12266,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -12246,7 +12276,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 170 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12257,51 +12292,26 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AH93" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124260115</v>
+        <v>124262979</v>
       </c>
       <c r="B94" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12310,46 +12320,46 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>461636</v>
+        <v>461543</v>
       </c>
       <c r="R94" t="n">
-        <v>7050841</v>
+        <v>7050645</v>
       </c>
       <c r="S94" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -12378,7 +12388,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12388,7 +12398,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12399,28 +12414,23 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
-      </c>
-      <c r="AH94" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124261426</v>
+        <v>124261849</v>
       </c>
       <c r="B95" t="n">
         <v>78891</v>
@@ -12460,10 +12470,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>461715</v>
+        <v>461733</v>
       </c>
       <c r="R95" t="n">
-        <v>7050700</v>
+        <v>7050778</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12495,7 +12505,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12505,12 +12515,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>På kvist på klen gran i gransumpskog</t>
+          <t>Ett ex på klen gran som saknar topp i äldre granskog</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12537,10 +12547,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124259169</v>
+        <v>124260702</v>
       </c>
       <c r="B96" t="n">
-        <v>78810</v>
+        <v>100279</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12549,41 +12559,46 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>461539</v>
+        <v>461678</v>
       </c>
       <c r="R96" t="n">
-        <v>7050804</v>
+        <v>7050823</v>
       </c>
       <c r="S96" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12612,7 +12627,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12622,7 +12637,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Både blåvioletta och vita blommor.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12637,26 +12657,6 @@
       <c r="AH96" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>

--- a/artfynd/A 12479-2025 artfynd.xlsx
+++ b/artfynd/A 12479-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124244069</v>
+        <v>124242253</v>
       </c>
       <c r="B2" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461842</v>
+        <v>461780</v>
       </c>
       <c r="R2" t="n">
-        <v>7050570</v>
+        <v>7050582</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:26</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På en grov sälglåga.</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,22 +779,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -822,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124241219</v>
+        <v>124243782</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>95335</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -834,41 +824,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461671</v>
+        <v>461757</v>
       </c>
       <c r="R3" t="n">
-        <v>7050487</v>
+        <v>7050561</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -907,7 +897,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Vid en bäck i gammal granskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,26 +917,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -959,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124243366</v>
+        <v>124244822</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -975,42 +950,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461694</v>
+        <v>461680</v>
       </c>
       <c r="R4" t="n">
-        <v>7050529</v>
+        <v>7050615</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1039,7 +1014,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1049,12 +1024,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:57</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i en murken granhögstubbe.</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1083,12 +1053,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1106,10 +1076,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124244491</v>
+        <v>124244322</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>100279</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1118,41 +1088,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461860</v>
+        <v>461935</v>
       </c>
       <c r="R5" t="n">
-        <v>7050631</v>
+        <v>7050570</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1181,7 +1156,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1191,12 +1166,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:46</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1211,26 +1181,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1248,7 +1198,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124244822</v>
+        <v>124244983</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1282,24 +1232,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461680</v>
+        <v>461652</v>
       </c>
       <c r="R6" t="n">
-        <v>7050615</v>
+        <v>7050519</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1328,7 +1273,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1338,7 +1283,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1390,10 +1335,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124244322</v>
+        <v>124243996</v>
       </c>
       <c r="B7" t="n">
-        <v>100279</v>
+        <v>79927</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1406,27 +1351,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1435,13 +1380,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461935</v>
+        <v>461837</v>
       </c>
       <c r="R7" t="n">
-        <v>7050570</v>
+        <v>7050572</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1470,7 +1415,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1480,7 +1425,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På en grov sälglåga.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1495,6 +1445,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1512,10 +1482,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124244443</v>
+        <v>124244357</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1524,38 +1494,52 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461867</v>
+        <v>461909</v>
       </c>
       <c r="R8" t="n">
-        <v>7050617</v>
+        <v>7050579</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
@@ -1587,7 +1571,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1597,12 +1581,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>I flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1617,26 +1601,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1654,7 +1618,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124242253</v>
+        <v>124242084</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1694,13 +1658,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461780</v>
+        <v>461835</v>
       </c>
       <c r="R9" t="n">
-        <v>7050582</v>
+        <v>7050524</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1729,7 +1693,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1739,7 +1703,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1791,10 +1755,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124244357</v>
+        <v>124243366</v>
       </c>
       <c r="B10" t="n">
-        <v>57883</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1803,20 +1767,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1824,34 +1788,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461909</v>
+        <v>461694</v>
       </c>
       <c r="R10" t="n">
-        <v>7050579</v>
+        <v>7050529</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1880,7 +1835,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1890,12 +1845,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>I flerskiktad äldre granskog.</t>
+          <t>Rejäla hackspår i en murken granhögstubbe.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1910,6 +1865,26 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2069,10 +2044,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124243996</v>
+        <v>124244491</v>
       </c>
       <c r="B12" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2081,46 +2056,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461837</v>
+        <v>461860</v>
       </c>
       <c r="R12" t="n">
-        <v>7050572</v>
+        <v>7050631</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2149,7 +2119,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2159,12 +2129,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På en grov sälglåga.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2183,22 +2153,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2216,7 +2186,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124242084</v>
+        <v>124241219</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -2252,14 +2222,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461835</v>
+        <v>461671</v>
       </c>
       <c r="R13" t="n">
-        <v>7050524</v>
+        <v>7050487</v>
       </c>
       <c r="S13" t="n">
         <v>7</v>
@@ -2291,7 +2261,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2301,7 +2271,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2353,10 +2323,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124243782</v>
+        <v>124244443</v>
       </c>
       <c r="B14" t="n">
-        <v>95335</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2365,25 +2335,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2393,13 +2363,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461757</v>
+        <v>461867</v>
       </c>
       <c r="R14" t="n">
-        <v>7050561</v>
+        <v>7050617</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2428,7 +2398,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2438,12 +2408,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Vid en bäck i gammal granskog.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2458,6 +2428,26 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2475,10 +2465,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124244006</v>
+        <v>124244069</v>
       </c>
       <c r="B15" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2487,41 +2477,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461840</v>
+        <v>461842</v>
       </c>
       <c r="R15" t="n">
-        <v>7050563</v>
+        <v>7050570</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2550,7 +2545,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2560,12 +2555,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Enstaka på en grov sälglåga.</t>
+          <t>På en grov sälglåga.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2617,10 +2612,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124244983</v>
+        <v>124244006</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2633,37 +2628,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461652</v>
+        <v>461840</v>
       </c>
       <c r="R16" t="n">
-        <v>7050519</v>
+        <v>7050563</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2692,7 +2687,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2702,7 +2697,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Enstaka på en grov sälglåga.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2721,22 +2721,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2754,10 +2754,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124258793</v>
+        <v>124260158</v>
       </c>
       <c r="B17" t="n">
-        <v>95335</v>
+        <v>79891</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2766,25 +2766,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2809</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461641</v>
+        <v>461793</v>
       </c>
       <c r="R17" t="n">
-        <v>7050551</v>
+        <v>7050683</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På bark på död rönnstubbe</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2871,10 +2871,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124260873</v>
+        <v>124262970</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2887,37 +2887,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461744</v>
+        <v>461598</v>
       </c>
       <c r="R18" t="n">
-        <v>7050919</v>
+        <v>7050665</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2956,7 +2956,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Enstaka på en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2975,22 +2980,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3008,10 +3013,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124261793</v>
+        <v>124260115</v>
       </c>
       <c r="B19" t="n">
-        <v>57529</v>
+        <v>100279</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3020,46 +3025,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461776</v>
+        <v>461636</v>
       </c>
       <c r="R19" t="n">
-        <v>7050867</v>
+        <v>7050841</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3088,7 +3093,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3098,12 +3103,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:04</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Letade efter hästmyra</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3114,26 +3114,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Emil Nordin, Ludvig Nordin, August Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124259251</v>
+        <v>124259426</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>77743</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3142,47 +3147,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461721</v>
+        <v>461787</v>
       </c>
       <c r="R20" t="n">
-        <v>7050576</v>
+        <v>7050628</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -3214,7 +3210,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3224,12 +3220,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Inom en yta på 3x7m</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3249,17 +3240,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>August Nordin, Emil Nordin, Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124260115</v>
+        <v>124260479</v>
       </c>
       <c r="B21" t="n">
-        <v>100279</v>
+        <v>79891</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3268,31 +3259,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3301,13 +3292,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461636</v>
+        <v>461666</v>
       </c>
       <c r="R21" t="n">
-        <v>7050841</v>
+        <v>7050837</v>
       </c>
       <c r="S21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3336,7 +3327,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3346,7 +3337,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns intill en bäck i gammal högväxt granskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3361,6 +3357,26 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3378,10 +3394,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124260702</v>
+        <v>124263257</v>
       </c>
       <c r="B22" t="n">
-        <v>100279</v>
+        <v>57529</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3390,31 +3406,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3423,13 +3443,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461678</v>
+        <v>461584</v>
       </c>
       <c r="R22" t="n">
-        <v>7050823</v>
+        <v>7050588</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3458,7 +3478,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3468,12 +3488,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Både blåvioletta och vita blommor.</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3484,31 +3499,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124259426</v>
+        <v>124260842</v>
       </c>
       <c r="B23" t="n">
-        <v>77743</v>
+        <v>91012</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3521,37 +3531,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461787</v>
+        <v>461785</v>
       </c>
       <c r="R23" t="n">
-        <v>7050628</v>
+        <v>7050704</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3580,7 +3590,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3590,7 +3600,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3605,22 +3620,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124262632</v>
+        <v>124241603</v>
       </c>
       <c r="B24" t="n">
-        <v>79857</v>
+        <v>98101</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3629,38 +3644,52 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229748</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461651</v>
+        <v>461712</v>
       </c>
       <c r="R24" t="n">
-        <v>7050724</v>
+        <v>7050513</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3687,27 +3716,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På rönn vid bäck i gammal granskog</t>
+          <t>Minst 78 plantor och 3 vinterståndare inom ca 1 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3718,26 +3747,31 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124260631</v>
+        <v>124259895</v>
       </c>
       <c r="B25" t="n">
-        <v>74901</v>
+        <v>74893</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3750,34 +3784,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461864</v>
+        <v>461797</v>
       </c>
       <c r="R25" t="n">
-        <v>7050679</v>
+        <v>7050670</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3809,7 +3843,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3819,7 +3853,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt på ved på basen av granhögstubbe i fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3834,22 +3873,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124259184</v>
+        <v>124262348</v>
       </c>
       <c r="B26" t="n">
-        <v>74901</v>
+        <v>79920</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3858,25 +3897,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3886,10 +3925,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461677</v>
+        <v>461656</v>
       </c>
       <c r="R26" t="n">
-        <v>7050616</v>
+        <v>7050743</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3921,7 +3960,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3931,12 +3970,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På död gran i sumpgranskog</t>
+          <t>På rönn vid bäck</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3951,22 +3990,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124262760</v>
+        <v>124261077</v>
       </c>
       <c r="B27" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3975,50 +4014,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461558</v>
+        <v>461731</v>
       </c>
       <c r="R27" t="n">
-        <v>7050692</v>
+        <v>7050711</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4047,7 +4077,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4057,7 +4087,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4072,22 +4107,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124261741</v>
+        <v>124259289</v>
       </c>
       <c r="B28" t="n">
-        <v>90977</v>
+        <v>95347</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4100,21 +4135,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>2813</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4124,10 +4159,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461728</v>
+        <v>461716</v>
       </c>
       <c r="R28" t="n">
-        <v>7050768</v>
+        <v>7050630</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4159,7 +4194,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4169,12 +4204,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På marken i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4201,10 +4236,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124260054</v>
+        <v>124263536</v>
       </c>
       <c r="B29" t="n">
-        <v>96979</v>
+        <v>57513</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4213,41 +4248,46 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461843</v>
+        <v>461544</v>
       </c>
       <c r="R29" t="n">
-        <v>7050661</v>
+        <v>7050635</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4276,7 +4316,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4286,7 +4326,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4301,22 +4346,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Emil Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124259759</v>
+        <v>124262198</v>
       </c>
       <c r="B30" t="n">
-        <v>77743</v>
+        <v>105102</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4325,25 +4370,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228579</v>
+        <v>221725</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4353,13 +4398,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461789</v>
+        <v>461687</v>
       </c>
       <c r="R30" t="n">
-        <v>7050616</v>
+        <v>7050752</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4388,7 +4433,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4398,12 +4443,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gammal gran ca 5 m från bäck i äldre granskog</t>
+          <t>På marken i fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4418,22 +4463,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124262908</v>
+        <v>124258944</v>
       </c>
       <c r="B31" t="n">
-        <v>77743</v>
+        <v>57883</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4442,41 +4487,60 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228579</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461633</v>
+        <v>461559</v>
       </c>
       <c r="R31" t="n">
-        <v>7050666</v>
+        <v>7050789</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4505,7 +4569,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4515,12 +4579,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (ca 170 år gammal) i gammal granskog</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4531,23 +4595,28 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124262035</v>
+        <v>124259877</v>
       </c>
       <c r="B32" t="n">
         <v>79891</v>
@@ -4580,14 +4649,10 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bålar</t>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4596,13 +4661,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461712</v>
+        <v>461614</v>
       </c>
       <c r="R32" t="n">
-        <v>7050901</v>
+        <v>7050862</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4631,7 +4696,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4641,12 +4706,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>Ymnig påväxt på en grov gammal sälg där vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4657,26 +4722,51 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124263132</v>
+        <v>124263066</v>
       </c>
       <c r="B33" t="n">
-        <v>91030</v>
+        <v>77743</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4689,51 +4779,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461570</v>
+        <v>461654</v>
       </c>
       <c r="R33" t="n">
-        <v>7050652</v>
+        <v>7050616</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4762,7 +4838,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4772,12 +4848,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i en grov gran.</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4788,51 +4864,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124260536</v>
+        <v>124263001</v>
       </c>
       <c r="B34" t="n">
-        <v>100279</v>
+        <v>79920</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4845,37 +4896,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461834</v>
+        <v>461597</v>
       </c>
       <c r="R34" t="n">
-        <v>7050707</v>
+        <v>7050664</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4904,7 +4960,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4914,7 +4970,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4925,23 +4981,48 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124263001</v>
+        <v>124262686</v>
       </c>
       <c r="B35" t="n">
         <v>79920</v>
@@ -4982,17 +5063,17 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461597</v>
+        <v>461617</v>
       </c>
       <c r="R35" t="n">
-        <v>7050664</v>
+        <v>7050728</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5021,7 +5102,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5031,7 +5112,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5083,7 +5164,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124263649</v>
+        <v>124260205</v>
       </c>
       <c r="B36" t="n">
         <v>79920</v>
@@ -5123,10 +5204,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461556</v>
+        <v>461793</v>
       </c>
       <c r="R36" t="n">
-        <v>7050632</v>
+        <v>7050683</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5158,7 +5239,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5168,12 +5249,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På gammal grov sälg i gammal granskog</t>
+          <t>På bark på rönnhögststubbe i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5200,10 +5281,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124263802</v>
+        <v>124263649</v>
       </c>
       <c r="B37" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5212,25 +5293,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5240,10 +5321,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461536</v>
+        <v>461556</v>
       </c>
       <c r="R37" t="n">
-        <v>7050642</v>
+        <v>7050632</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5275,7 +5356,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5285,12 +5366,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ca 40 ex inom en kvadratmeter</t>
+          <t>På gammal grov sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5305,22 +5386,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124263103</v>
+        <v>124262760</v>
       </c>
       <c r="B38" t="n">
-        <v>79891</v>
+        <v>57883</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5329,38 +5410,47 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461643</v>
+        <v>461558</v>
       </c>
       <c r="R38" t="n">
-        <v>7050590</v>
+        <v>7050692</v>
       </c>
       <c r="S38" t="n">
         <v>8</v>
@@ -5392,7 +5482,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5402,12 +5492,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På gammal rönn I gammal granskog</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5422,22 +5507,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124262454</v>
+        <v>124260054</v>
       </c>
       <c r="B39" t="n">
-        <v>79891</v>
+        <v>96979</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5446,41 +5531,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461608</v>
+        <v>461843</v>
       </c>
       <c r="R39" t="n">
-        <v>7050779</v>
+        <v>7050661</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5509,7 +5594,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5519,12 +5604,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på en skadad rönn.</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5535,51 +5615,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124262979</v>
+        <v>124261167</v>
       </c>
       <c r="B40" t="n">
-        <v>91012</v>
+        <v>74901</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5592,39 +5647,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461543</v>
+        <v>461741</v>
       </c>
       <c r="R40" t="n">
-        <v>7050645</v>
+        <v>7050704</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5656,7 +5706,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5666,12 +5716,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gammal gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5686,22 +5736,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin, Emil Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124259895</v>
+        <v>124262932</v>
       </c>
       <c r="B41" t="n">
-        <v>74893</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5714,34 +5764,43 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461797</v>
+        <v>461633</v>
       </c>
       <c r="R41" t="n">
-        <v>7050670</v>
+        <v>7050666</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5773,7 +5832,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5783,12 +5842,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Rikligt på ved på basen av granhögstubbe i fuktig gammal granskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5815,7 +5874,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124262044</v>
+        <v>124262353</v>
       </c>
       <c r="B42" t="n">
         <v>77743</v>
@@ -5855,10 +5914,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461724</v>
+        <v>461655</v>
       </c>
       <c r="R42" t="n">
-        <v>7050772</v>
+        <v>7050759</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5890,7 +5949,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5900,12 +5959,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (28 cm dbh) i gammal granskog</t>
+          <t>På gran ca 40 cm i diameter intill bäck</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5920,22 +5979,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124260175</v>
+        <v>124263373</v>
       </c>
       <c r="B43" t="n">
-        <v>74885</v>
+        <v>77743</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5944,25 +6003,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6439</v>
+        <v>228579</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5972,10 +6031,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461793</v>
+        <v>461587</v>
       </c>
       <c r="R43" t="n">
-        <v>7050683</v>
+        <v>7050582</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6007,7 +6066,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6017,12 +6076,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På ved på rönnhögstubbe i gammal fuktig granskog</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6037,19 +6091,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124263852</v>
+        <v>124263059</v>
       </c>
       <c r="B44" t="n">
         <v>74901</v>
@@ -6089,10 +6143,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461549</v>
+        <v>461654</v>
       </c>
       <c r="R44" t="n">
-        <v>7050671</v>
+        <v>7050616</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6124,7 +6178,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6134,12 +6188,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6159,17 +6213,17 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124262970</v>
+        <v>124263103</v>
       </c>
       <c r="B45" t="n">
-        <v>79892</v>
+        <v>79891</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6182,37 +6236,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461598</v>
+        <v>461643</v>
       </c>
       <c r="R45" t="n">
-        <v>7050665</v>
+        <v>7050590</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6241,7 +6295,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6251,12 +6305,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Enstaka på en flerstammig sälg.</t>
+          <t>På gammal rönn I gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6267,51 +6321,26 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124263683</v>
+        <v>124263170</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
+        <v>77743</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6320,60 +6349,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461584</v>
+        <v>461624</v>
       </c>
       <c r="R46" t="n">
-        <v>7050644</v>
+        <v>7050624</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6402,7 +6412,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6412,12 +6422,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Minst 63 plantor inom ca 2 x 1 m2 i gammal granskog.</t>
+          <t>På gammal gran i fuktig äldre granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6428,31 +6438,26 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124262353</v>
+        <v>124261849</v>
       </c>
       <c r="B47" t="n">
-        <v>77743</v>
+        <v>78891</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6465,21 +6470,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228579</v>
+        <v>283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6489,10 +6494,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461655</v>
+        <v>461733</v>
       </c>
       <c r="R47" t="n">
-        <v>7050759</v>
+        <v>7050778</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6524,7 +6529,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6534,12 +6539,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gran ca 40 cm i diameter intill bäck</t>
+          <t>Ett ex på klen gran som saknar topp i äldre granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6566,10 +6571,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124262686</v>
+        <v>124259251</v>
       </c>
       <c r="B48" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6578,46 +6583,50 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461617</v>
+        <v>461721</v>
       </c>
       <c r="R48" t="n">
-        <v>7050728</v>
+        <v>7050576</v>
       </c>
       <c r="S48" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6646,7 +6655,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6656,7 +6665,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Inom en yta på 3x7m</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6667,51 +6681,26 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124259877</v>
+        <v>124261213</v>
       </c>
       <c r="B49" t="n">
-        <v>79891</v>
+        <v>77743</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6724,42 +6713,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>461614</v>
+        <v>461731</v>
       </c>
       <c r="R49" t="n">
-        <v>7050862</v>
+        <v>7050704</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6788,7 +6772,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6798,12 +6782,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ymnig påväxt på en grov gammal sälg där vissa bålar är fertila med apothecier.</t>
+          <t>På gammal gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6814,51 +6798,26 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124263257</v>
+        <v>124262454</v>
       </c>
       <c r="B50" t="n">
-        <v>57529</v>
+        <v>79891</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6871,46 +6830,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>461584</v>
+        <v>461608</v>
       </c>
       <c r="R50" t="n">
-        <v>7050588</v>
+        <v>7050779</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6939,7 +6889,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6949,7 +6899,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på en skadad rönn.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6960,26 +6915,51 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124264003</v>
+        <v>124262807</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
+        <v>74901</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6988,60 +6968,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461546</v>
+        <v>461633</v>
       </c>
       <c r="R51" t="n">
-        <v>7050666</v>
+        <v>7050701</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7070,7 +7031,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7080,12 +7041,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Minst 51 plantor inom ca 2 m2 i gammal granskog.</t>
+          <t>På gammal gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7096,31 +7057,26 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124259378</v>
+        <v>124261626</v>
       </c>
       <c r="B52" t="n">
-        <v>79891</v>
+        <v>56714</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7133,42 +7089,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461603</v>
+        <v>461768</v>
       </c>
       <c r="R52" t="n">
-        <v>7050832</v>
+        <v>7050794</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7197,7 +7153,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7207,12 +7163,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ymnigt med lunglav på en gammal grov sälg. Vissa bålar är fertila med apothecier.</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7227,26 +7178,6 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7264,10 +7195,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124262526</v>
+        <v>124260175</v>
       </c>
       <c r="B53" t="n">
-        <v>79927</v>
+        <v>74885</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7280,21 +7211,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>6439</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7304,10 +7235,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461665</v>
+        <v>461793</v>
       </c>
       <c r="R53" t="n">
-        <v>7050738</v>
+        <v>7050683</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7339,7 +7270,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7349,12 +7280,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På död rönn intill bäck</t>
+          <t>På ved på rönnhögstubbe i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7369,22 +7300,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124259784</v>
+        <v>124261426</v>
       </c>
       <c r="B54" t="n">
-        <v>74901</v>
+        <v>78891</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7397,21 +7328,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6440</v>
+        <v>283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7421,10 +7352,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>461789</v>
+        <v>461715</v>
       </c>
       <c r="R54" t="n">
-        <v>7050616</v>
+        <v>7050700</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7456,7 +7387,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7466,12 +7397,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På gammal gran ca 5m från bäck i äldre granskog</t>
+          <t>På kvist på klen gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7498,10 +7429,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124261849</v>
+        <v>124262526</v>
       </c>
       <c r="B55" t="n">
-        <v>78891</v>
+        <v>79927</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7510,25 +7441,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>283</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7538,10 +7469,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>461733</v>
+        <v>461665</v>
       </c>
       <c r="R55" t="n">
-        <v>7050778</v>
+        <v>7050738</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7573,7 +7504,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7583,12 +7514,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ett ex på klen gran som saknar topp i äldre granskog</t>
+          <t>På död rönn intill bäck</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7615,10 +7546,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124262932</v>
+        <v>124260468</v>
       </c>
       <c r="B56" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7631,43 +7562,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461633</v>
+        <v>461783</v>
       </c>
       <c r="R56" t="n">
-        <v>7050666</v>
+        <v>7050722</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7699,7 +7621,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7709,12 +7631,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7741,10 +7663,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124263225</v>
+        <v>124263250</v>
       </c>
       <c r="B57" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7757,21 +7679,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7781,10 +7703,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461603</v>
+        <v>461629</v>
       </c>
       <c r="R57" t="n">
-        <v>7050578</v>
+        <v>7050621</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7816,7 +7738,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7826,12 +7748,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>Ett 100-tal bålar på ett 10-tal granar</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7846,22 +7768,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124261426</v>
+        <v>124260536</v>
       </c>
       <c r="B58" t="n">
-        <v>78891</v>
+        <v>100279</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7870,41 +7792,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>283</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461715</v>
+        <v>461834</v>
       </c>
       <c r="R58" t="n">
-        <v>7050700</v>
+        <v>7050707</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7933,7 +7855,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7943,12 +7865,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:56</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På kvist på klen gran i gransumpskog</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7963,22 +7880,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124261248</v>
+        <v>124261741</v>
       </c>
       <c r="B59" t="n">
-        <v>91030</v>
+        <v>90977</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7987,41 +7904,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461756</v>
+        <v>461728</v>
       </c>
       <c r="R59" t="n">
-        <v>7050765</v>
+        <v>7050768</v>
       </c>
       <c r="S59" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8050,7 +7967,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8060,7 +7977,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8075,22 +7997,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Emil Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124260947</v>
+        <v>124259967</v>
       </c>
       <c r="B60" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8103,34 +8025,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461749</v>
+        <v>461623</v>
       </c>
       <c r="R60" t="n">
-        <v>7050709</v>
+        <v>7050871</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8162,7 +8089,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8172,7 +8099,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Rikligt på en skadad rönn.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8183,26 +8115,51 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124241603</v>
+        <v>124262595</v>
       </c>
       <c r="B61" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8211,55 +8168,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461712</v>
+        <v>461615</v>
       </c>
       <c r="R61" t="n">
-        <v>7050513</v>
+        <v>7050725</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8283,27 +8226,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:55</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Minst 78 plantor och 3 vinterståndare inom ca 1 m2 i gammal granskog.</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8318,6 +8256,26 @@
       <c r="AH61" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8335,10 +8293,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124263066</v>
+        <v>124262878</v>
       </c>
       <c r="B62" t="n">
-        <v>77743</v>
+        <v>74901</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8351,21 +8309,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8375,10 +8333,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461654</v>
+        <v>461633</v>
       </c>
       <c r="R62" t="n">
-        <v>7050616</v>
+        <v>7050666</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8410,7 +8368,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8420,12 +8378,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 170 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8452,10 +8410,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124259169</v>
+        <v>124262979</v>
       </c>
       <c r="B63" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8468,37 +8426,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461539</v>
+        <v>461543</v>
       </c>
       <c r="R63" t="n">
-        <v>7050804</v>
+        <v>7050645</v>
       </c>
       <c r="S63" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8527,7 +8490,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8537,7 +8500,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8548,51 +8516,26 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124262807</v>
+        <v>124264003</v>
       </c>
       <c r="B64" t="n">
-        <v>74901</v>
+        <v>98101</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8601,41 +8544,60 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461633</v>
+        <v>461546</v>
       </c>
       <c r="R64" t="n">
-        <v>7050701</v>
+        <v>7050666</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8664,7 +8626,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8674,12 +8636,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På gammal gran i gransumpskog</t>
+          <t>Minst 51 plantor inom ca 2 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8690,26 +8652,31 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124263837</v>
+        <v>124260873</v>
       </c>
       <c r="B65" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8722,21 +8689,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8746,13 +8713,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>461549</v>
+        <v>461744</v>
       </c>
       <c r="R65" t="n">
-        <v>7050671</v>
+        <v>7050919</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8781,7 +8748,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8791,12 +8758,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:16</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8807,26 +8769,51 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124263536</v>
+        <v>124260993</v>
       </c>
       <c r="B66" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8839,16 +8826,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -8864,17 +8851,17 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Småfloarna, Småfloarna, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>461544</v>
+        <v>461776</v>
       </c>
       <c r="R66" t="n">
-        <v>7050635</v>
+        <v>7050859</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8903,7 +8890,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8913,12 +8900,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gammal gran i gammal granskog</t>
+          <t>Rejäla hackspår.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8929,26 +8916,51 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124260842</v>
+        <v>124261793</v>
       </c>
       <c r="B67" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8961,37 +8973,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461785</v>
+        <v>461776</v>
       </c>
       <c r="R67" t="n">
-        <v>7050704</v>
+        <v>7050867</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9020,7 +9037,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9030,12 +9047,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>Letade efter hästmyra</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9050,22 +9067,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>August Nordin, Ludvig Nordin, Emil Nordin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124261167</v>
+        <v>124263802</v>
       </c>
       <c r="B68" t="n">
-        <v>74901</v>
+        <v>98101</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9074,25 +9091,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -9102,10 +9119,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>461741</v>
+        <v>461536</v>
       </c>
       <c r="R68" t="n">
-        <v>7050704</v>
+        <v>7050642</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9137,7 +9154,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9147,12 +9164,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På gammal gran i gransumpskog</t>
+          <t>Ca 40 ex inom en kvadratmeter</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9172,17 +9189,17 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Emil Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124259289</v>
+        <v>124259169</v>
       </c>
       <c r="B69" t="n">
-        <v>95347</v>
+        <v>78810</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9191,25 +9208,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2813</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9219,13 +9236,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>461716</v>
+        <v>461539</v>
       </c>
       <c r="R69" t="n">
-        <v>7050630</v>
+        <v>7050804</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9254,7 +9271,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9264,12 +9281,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På marken i gammal sumpgranskog</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9280,26 +9292,51 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124260468</v>
+        <v>124262035</v>
       </c>
       <c r="B70" t="n">
-        <v>74901</v>
+        <v>79891</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9312,37 +9349,46 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>461783</v>
+        <v>461712</v>
       </c>
       <c r="R70" t="n">
-        <v>7050722</v>
+        <v>7050901</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9371,7 +9417,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9381,12 +9427,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal fuktig granskog</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9401,22 +9447,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124260993</v>
+        <v>124260631</v>
       </c>
       <c r="B71" t="n">
-        <v>57529</v>
+        <v>74901</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9429,42 +9475,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Småfloarna, Småfloarna, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>461776</v>
+        <v>461864</v>
       </c>
       <c r="R71" t="n">
-        <v>7050859</v>
+        <v>7050679</v>
       </c>
       <c r="S71" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9493,7 +9534,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9503,12 +9544,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:41</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår.</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9519,51 +9555,26 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124261213</v>
+        <v>124263683</v>
       </c>
       <c r="B72" t="n">
-        <v>77743</v>
+        <v>98101</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9572,41 +9583,60 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>461731</v>
+        <v>461584</v>
       </c>
       <c r="R72" t="n">
-        <v>7050704</v>
+        <v>7050644</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9635,7 +9665,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9645,12 +9675,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På gammal gran i gransumpskog</t>
+          <t>Minst 63 plantor inom ca 2 x 1 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9661,26 +9691,31 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124260479</v>
+        <v>124263837</v>
       </c>
       <c r="B73" t="n">
-        <v>79891</v>
+        <v>77743</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9693,42 +9728,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>461666</v>
+        <v>461549</v>
       </c>
       <c r="R73" t="n">
-        <v>7050837</v>
+        <v>7050671</v>
       </c>
       <c r="S73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9757,7 +9787,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9767,12 +9797,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns intill en bäck i gammal högväxt granskog.</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9783,51 +9813,26 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124261077</v>
+        <v>124263132</v>
       </c>
       <c r="B74" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9840,37 +9845,51 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>461731</v>
+        <v>461570</v>
       </c>
       <c r="R74" t="n">
-        <v>7050711</v>
+        <v>7050652</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9899,7 +9918,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9909,12 +9928,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal fuktig granskog</t>
+          <t>Rikligt med fruktkroppar i en grov gran.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9925,26 +9944,51 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124258944</v>
+        <v>124260090</v>
       </c>
       <c r="B75" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9953,60 +9997,41 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>461559</v>
+        <v>461642</v>
       </c>
       <c r="R75" t="n">
-        <v>7050789</v>
+        <v>7050845</v>
       </c>
       <c r="S75" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10035,7 +10060,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10045,12 +10070,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10065,6 +10085,26 @@
       <c r="AH75" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10082,10 +10122,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124262198</v>
+        <v>124260947</v>
       </c>
       <c r="B76" t="n">
-        <v>105102</v>
+        <v>78810</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10094,25 +10134,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -10122,13 +10162,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>461687</v>
+        <v>461749</v>
       </c>
       <c r="R76" t="n">
-        <v>7050752</v>
+        <v>7050709</v>
       </c>
       <c r="S76" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -10157,7 +10197,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10167,12 +10207,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>På marken i fuktig gammal granskog</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10199,10 +10234,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124263373</v>
+        <v>124261444</v>
       </c>
       <c r="B77" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10215,21 +10250,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -10239,10 +10274,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>461587</v>
+        <v>461810</v>
       </c>
       <c r="R77" t="n">
-        <v>7050582</v>
+        <v>7050829</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10274,7 +10309,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10284,7 +10319,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10299,22 +10339,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124263675</v>
+        <v>124263225</v>
       </c>
       <c r="B78" t="n">
-        <v>79892</v>
+        <v>91012</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10327,21 +10367,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10351,10 +10391,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>461551</v>
+        <v>461603</v>
       </c>
       <c r="R78" t="n">
-        <v>7050634</v>
+        <v>7050578</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10386,7 +10426,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10396,12 +10436,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På sälg ca 60 cm i diameter</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10416,22 +10456,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124262725</v>
+        <v>124259946</v>
       </c>
       <c r="B79" t="n">
-        <v>78810</v>
+        <v>78891</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10444,21 +10484,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10468,10 +10508,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>461642</v>
+        <v>461815</v>
       </c>
       <c r="R79" t="n">
-        <v>7050696</v>
+        <v>7050652</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10503,7 +10543,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10513,12 +10553,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal fuktig granskog nära bäck</t>
+          <t>På tunn levande gren på gammal klen gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10545,10 +10585,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124262595</v>
+        <v>124263852</v>
       </c>
       <c r="B80" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10561,21 +10601,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10585,13 +10625,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>461615</v>
+        <v>461549</v>
       </c>
       <c r="R80" t="n">
-        <v>7050725</v>
+        <v>7050671</v>
       </c>
       <c r="S80" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10620,7 +10660,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10630,7 +10670,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10641,51 +10686,26 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124261444</v>
+        <v>124261471</v>
       </c>
       <c r="B81" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10698,37 +10718,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>461810</v>
+        <v>461800</v>
       </c>
       <c r="R81" t="n">
-        <v>7050829</v>
+        <v>7050827</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10757,7 +10777,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10767,12 +10787,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På kolade tallstubbe.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10783,26 +10803,51 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Stump # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124258987</v>
+        <v>124262908</v>
       </c>
       <c r="B82" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10815,21 +10860,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10839,10 +10884,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>461689</v>
+        <v>461633</v>
       </c>
       <c r="R82" t="n">
-        <v>7050585</v>
+        <v>7050666</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10874,7 +10919,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10884,12 +10929,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran (ca 170 år gammal) i gammal granskog</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10916,10 +10961,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124259946</v>
+        <v>124262725</v>
       </c>
       <c r="B83" t="n">
-        <v>78891</v>
+        <v>78810</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10932,21 +10977,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10956,10 +11001,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>461815</v>
+        <v>461642</v>
       </c>
       <c r="R83" t="n">
-        <v>7050652</v>
+        <v>7050696</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10991,7 +11036,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11001,12 +11046,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På tunn levande gren på gammal klen gran i gammal fuktig granskog</t>
+          <t>På gammal gran i gammal fuktig granskog nära bäck</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11033,10 +11078,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124260773</v>
+        <v>124258987</v>
       </c>
       <c r="B84" t="n">
-        <v>91673</v>
+        <v>78810</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11045,43 +11090,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>898</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>461785</v>
+        <v>461689</v>
       </c>
       <c r="R84" t="n">
-        <v>7050704</v>
+        <v>7050585</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11113,7 +11153,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11123,12 +11163,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>På gammal ullticka på granlåga i bördig, fuktig lågarik granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11139,21 +11179,6 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -11170,10 +11195,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124263170</v>
+        <v>124264084</v>
       </c>
       <c r="B85" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11186,37 +11211,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>461624</v>
+        <v>461561</v>
       </c>
       <c r="R85" t="n">
-        <v>7050624</v>
+        <v>7050657</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -11245,7 +11270,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11255,12 +11280,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>På gammal gran i fuktig äldre granskog</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11271,26 +11291,51 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124261471</v>
+        <v>124263675</v>
       </c>
       <c r="B86" t="n">
-        <v>78547</v>
+        <v>79892</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11303,37 +11348,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>461800</v>
+        <v>461551</v>
       </c>
       <c r="R86" t="n">
-        <v>7050827</v>
+        <v>7050634</v>
       </c>
       <c r="S86" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -11362,7 +11407,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11372,12 +11417,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>På kolade tallstubbe.</t>
+          <t>På sälg ca 60 cm i diameter</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11388,51 +11433,26 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Stump # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124261626</v>
+        <v>124260773</v>
       </c>
       <c r="B87" t="n">
-        <v>56714</v>
+        <v>91673</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11441,46 +11461,46 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>102612</v>
+        <v>898</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>461768</v>
+        <v>461785</v>
       </c>
       <c r="R87" t="n">
-        <v>7050794</v>
+        <v>7050704</v>
       </c>
       <c r="S87" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11509,7 +11529,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11519,7 +11539,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>På gammal ullticka på granlåga i bördig, fuktig lågarik granskog</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11531,30 +11556,40 @@
       <c r="AG87" t="b">
         <v>0</v>
       </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>Granskog</t>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124260090</v>
+        <v>124258793</v>
       </c>
       <c r="B88" t="n">
-        <v>78810</v>
+        <v>95335</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11563,25 +11598,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -11591,13 +11626,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>461642</v>
+        <v>461641</v>
       </c>
       <c r="R88" t="n">
-        <v>7050845</v>
+        <v>7050551</v>
       </c>
       <c r="S88" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11626,7 +11661,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11636,7 +11671,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11647,51 +11687,26 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124263059</v>
+        <v>124260702</v>
       </c>
       <c r="B89" t="n">
-        <v>74901</v>
+        <v>100279</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11700,41 +11715,46 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6440</v>
+        <v>222498</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>461654</v>
+        <v>461678</v>
       </c>
       <c r="R89" t="n">
-        <v>7050616</v>
+        <v>7050823</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11763,7 +11783,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11773,12 +11793,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Både blåvioletta och vita blommor.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11789,26 +11809,31 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124260158</v>
+        <v>124262632</v>
       </c>
       <c r="B90" t="n">
-        <v>79891</v>
+        <v>79857</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11817,25 +11842,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>229748</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -11845,10 +11870,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>461793</v>
+        <v>461651</v>
       </c>
       <c r="R90" t="n">
-        <v>7050683</v>
+        <v>7050724</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11880,7 +11905,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11890,12 +11915,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På bark på död rönnstubbe</t>
+          <t>På rönn vid bäck i gammal granskog</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11922,10 +11947,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124262348</v>
+        <v>124262044</v>
       </c>
       <c r="B91" t="n">
-        <v>79920</v>
+        <v>77743</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11934,25 +11959,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6462</v>
+        <v>228579</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -11962,10 +11987,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>461656</v>
+        <v>461724</v>
       </c>
       <c r="R91" t="n">
-        <v>7050743</v>
+        <v>7050772</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11997,7 +12022,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -12007,12 +12032,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>På rönn vid bäck</t>
+          <t>På bark på stam av levande gammal gran (28 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12039,10 +12064,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124264084</v>
+        <v>124259378</v>
       </c>
       <c r="B92" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12055,37 +12080,42 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>461561</v>
+        <v>461603</v>
       </c>
       <c r="R92" t="n">
-        <v>7050657</v>
+        <v>7050832</v>
       </c>
       <c r="S92" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -12114,7 +12144,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -12124,7 +12154,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Ymnigt med lunglav på en gammal grov sälg. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12143,22 +12178,22 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -12176,7 +12211,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124262878</v>
+        <v>124259784</v>
       </c>
       <c r="B93" t="n">
         <v>74901</v>
@@ -12216,10 +12251,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>461633</v>
+        <v>461789</v>
       </c>
       <c r="R93" t="n">
-        <v>7050666</v>
+        <v>7050616</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12251,7 +12286,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -12261,12 +12296,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 170 år) i gammal granskog</t>
+          <t>På gammal gran ca 5m från bäck i äldre granskog</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12281,22 +12316,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124263250</v>
+        <v>124259184</v>
       </c>
       <c r="B94" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12309,21 +12344,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -12333,10 +12368,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>461629</v>
+        <v>461677</v>
       </c>
       <c r="R94" t="n">
-        <v>7050621</v>
+        <v>7050616</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12368,7 +12403,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12378,12 +12413,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Ett 100-tal bålar på ett 10-tal granar</t>
+          <t>På död gran i sumpgranskog</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12410,10 +12445,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124259967</v>
+        <v>124261248</v>
       </c>
       <c r="B95" t="n">
-        <v>79891</v>
+        <v>91030</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12426,42 +12461,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>461623</v>
+        <v>461756</v>
       </c>
       <c r="R95" t="n">
-        <v>7050871</v>
+        <v>7050765</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -12490,7 +12520,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12500,12 +12530,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Rikligt på en skadad rönn.</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12516,51 +12541,26 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Emil Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124260205</v>
+        <v>124259759</v>
       </c>
       <c r="B96" t="n">
-        <v>79920</v>
+        <v>77743</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12569,25 +12569,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6462</v>
+        <v>228579</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -12597,10 +12597,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>461793</v>
+        <v>461789</v>
       </c>
       <c r="R96" t="n">
-        <v>7050683</v>
+        <v>7050616</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12632,7 +12632,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12642,12 +12642,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>På bark på rönnhögststubbe i gammal fuktig granskog</t>
+          <t>På gammal gran ca 5 m från bäck i äldre granskog</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12662,12 +12662,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>

--- a/artfynd/A 12479-2025 artfynd.xlsx
+++ b/artfynd/A 12479-2025 artfynd.xlsx
@@ -1618,10 +1618,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124242084</v>
+        <v>124243366</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1634,34 +1634,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461835</v>
+        <v>461694</v>
       </c>
       <c r="R9" t="n">
-        <v>7050524</v>
+        <v>7050529</v>
       </c>
       <c r="S9" t="n">
         <v>7</v>
@@ -1693,7 +1698,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1703,7 +1708,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i en murken granhögstubbe.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1732,12 +1742,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1755,10 +1765,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124243366</v>
+        <v>124242084</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1771,39 +1781,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461694</v>
+        <v>461835</v>
       </c>
       <c r="R10" t="n">
-        <v>7050529</v>
+        <v>7050524</v>
       </c>
       <c r="S10" t="n">
         <v>7</v>
@@ -1835,7 +1840,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1845,12 +1850,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:57</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i en murken granhögstubbe.</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2754,10 +2754,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124260158</v>
+        <v>124260115</v>
       </c>
       <c r="B17" t="n">
-        <v>79891</v>
+        <v>100279</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2766,41 +2766,46 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461793</v>
+        <v>461636</v>
       </c>
       <c r="R17" t="n">
-        <v>7050683</v>
+        <v>7050841</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2829,7 +2834,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2839,12 +2844,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På bark på död rönnstubbe</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2855,26 +2855,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124262970</v>
+        <v>124259426</v>
       </c>
       <c r="B18" t="n">
-        <v>79892</v>
+        <v>77743</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2887,34 +2892,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461598</v>
+        <v>461787</v>
       </c>
       <c r="R18" t="n">
-        <v>7050665</v>
+        <v>7050628</v>
       </c>
       <c r="S18" t="n">
         <v>9</v>
@@ -2946,7 +2951,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2956,12 +2961,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Enstaka på en flerstammig sälg.</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2972,51 +2972,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124260115</v>
+        <v>124260158</v>
       </c>
       <c r="B19" t="n">
-        <v>100279</v>
+        <v>79891</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3025,46 +3000,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461636</v>
+        <v>461793</v>
       </c>
       <c r="R19" t="n">
-        <v>7050841</v>
+        <v>7050683</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3093,7 +3063,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3103,7 +3073,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På bark på död rönnstubbe</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3114,31 +3089,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124259426</v>
+        <v>124262970</v>
       </c>
       <c r="B20" t="n">
-        <v>77743</v>
+        <v>79892</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3151,34 +3121,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461787</v>
+        <v>461598</v>
       </c>
       <c r="R20" t="n">
-        <v>7050628</v>
+        <v>7050665</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -3210,7 +3180,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3220,7 +3190,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Enstaka på en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3231,26 +3206,51 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124260479</v>
+        <v>124263257</v>
       </c>
       <c r="B21" t="n">
-        <v>79891</v>
+        <v>57529</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3263,27 +3263,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3292,13 +3296,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461666</v>
+        <v>461584</v>
       </c>
       <c r="R21" t="n">
-        <v>7050837</v>
+        <v>7050588</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3327,7 +3331,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3337,12 +3341,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:23</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Fyndplatsen finns intill en bäck i gammal högväxt granskog.</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3353,51 +3352,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124263257</v>
+        <v>124241603</v>
       </c>
       <c r="B22" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3406,50 +3380,55 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461584</v>
+        <v>461712</v>
       </c>
       <c r="R22" t="n">
-        <v>7050588</v>
+        <v>7050513</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3473,22 +3452,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Minst 78 plantor och 3 vinterståndare inom ca 1 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3499,26 +3483,31 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124260842</v>
+        <v>124260479</v>
       </c>
       <c r="B23" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3531,37 +3520,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461785</v>
+        <v>461666</v>
       </c>
       <c r="R23" t="n">
-        <v>7050704</v>
+        <v>7050837</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3590,7 +3584,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3600,12 +3594,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>Fyndplatsen finns intill en bäck i gammal högväxt granskog.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3616,26 +3610,51 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124241603</v>
+        <v>124260842</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3644,52 +3663,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461712</v>
+        <v>461785</v>
       </c>
       <c r="R24" t="n">
-        <v>7050513</v>
+        <v>7050704</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3716,27 +3721,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Minst 78 plantor och 3 vinterståndare inom ca 1 m2 i gammal granskog.</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3747,31 +3752,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124259895</v>
+        <v>124262348</v>
       </c>
       <c r="B25" t="n">
-        <v>74893</v>
+        <v>79920</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3780,25 +3780,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>308</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461797</v>
+        <v>461656</v>
       </c>
       <c r="R25" t="n">
-        <v>7050670</v>
+        <v>7050743</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Rikligt på ved på basen av granhögstubbe i fuktig gammal granskog</t>
+          <t>På rönn vid bäck</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3885,10 +3885,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124262348</v>
+        <v>124261077</v>
       </c>
       <c r="B26" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3897,25 +3897,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461656</v>
+        <v>461731</v>
       </c>
       <c r="R26" t="n">
-        <v>7050743</v>
+        <v>7050711</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På rönn vid bäck</t>
+          <t>På gammal gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4002,10 +4002,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124261077</v>
+        <v>124259895</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>74893</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4018,21 +4018,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -4042,10 +4042,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461731</v>
+        <v>461797</v>
       </c>
       <c r="R27" t="n">
-        <v>7050711</v>
+        <v>7050670</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4077,7 +4077,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal fuktig granskog</t>
+          <t>Rikligt på ved på basen av granhögstubbe i fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4616,10 +4616,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124259877</v>
+        <v>124263066</v>
       </c>
       <c r="B32" t="n">
-        <v>79891</v>
+        <v>77743</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4632,42 +4632,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461614</v>
+        <v>461654</v>
       </c>
       <c r="R32" t="n">
-        <v>7050862</v>
+        <v>7050616</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4696,7 +4691,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4706,12 +4701,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ymnig påväxt på en grov gammal sälg där vissa bålar är fertila med apothecier.</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4722,51 +4717,26 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124263066</v>
+        <v>124259877</v>
       </c>
       <c r="B33" t="n">
-        <v>77743</v>
+        <v>79891</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4779,37 +4749,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461654</v>
+        <v>461614</v>
       </c>
       <c r="R33" t="n">
-        <v>7050616</v>
+        <v>7050862</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4838,7 +4813,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4848,12 +4823,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Ymnig påväxt på en grov gammal sälg där vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4864,16 +4839,41 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -5631,10 +5631,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124261167</v>
+        <v>124262353</v>
       </c>
       <c r="B40" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5647,21 +5647,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5671,10 +5671,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461741</v>
+        <v>461655</v>
       </c>
       <c r="R40" t="n">
-        <v>7050704</v>
+        <v>7050759</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På gammal gran i gransumpskog</t>
+          <t>På gran ca 40 cm i diameter intill bäck</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5741,17 +5741,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Emil Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124262932</v>
+        <v>124261167</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5764,43 +5764,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461633</v>
+        <v>461741</v>
       </c>
       <c r="R41" t="n">
-        <v>7050666</v>
+        <v>7050704</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5832,7 +5823,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5842,12 +5833,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På gammal gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5862,22 +5853,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Emil Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124262353</v>
+        <v>124262932</v>
       </c>
       <c r="B42" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5890,34 +5881,43 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461655</v>
+        <v>461633</v>
       </c>
       <c r="R42" t="n">
-        <v>7050759</v>
+        <v>7050666</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5949,7 +5949,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5959,12 +5959,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På gran ca 40 cm i diameter intill bäck</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5979,22 +5979,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124263373</v>
+        <v>124263059</v>
       </c>
       <c r="B43" t="n">
-        <v>77743</v>
+        <v>74901</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6007,21 +6007,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461587</v>
+        <v>461654</v>
       </c>
       <c r="R43" t="n">
-        <v>7050582</v>
+        <v>7050616</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6066,7 +6066,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6076,7 +6076,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6091,22 +6096,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124263059</v>
+        <v>124263103</v>
       </c>
       <c r="B44" t="n">
-        <v>74901</v>
+        <v>79891</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6119,21 +6124,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6143,13 +6148,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461654</v>
+        <v>461643</v>
       </c>
       <c r="R44" t="n">
-        <v>7050616</v>
+        <v>7050590</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6178,7 +6183,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6188,12 +6193,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal rönn I gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6220,10 +6225,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124263103</v>
+        <v>124263170</v>
       </c>
       <c r="B45" t="n">
-        <v>79891</v>
+        <v>77743</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6236,21 +6241,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -6260,13 +6265,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461643</v>
+        <v>461624</v>
       </c>
       <c r="R45" t="n">
-        <v>7050590</v>
+        <v>7050624</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6295,7 +6300,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6305,12 +6310,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På gammal rönn I gammal granskog</t>
+          <t>På gammal gran i fuktig äldre granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6325,19 +6330,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124263170</v>
+        <v>124263373</v>
       </c>
       <c r="B46" t="n">
         <v>77743</v>
@@ -6377,10 +6382,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461624</v>
+        <v>461587</v>
       </c>
       <c r="R46" t="n">
-        <v>7050624</v>
+        <v>7050582</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6412,7 +6417,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6422,12 +6427,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På gammal gran i fuktig äldre granskog</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6454,10 +6454,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124261849</v>
+        <v>124259251</v>
       </c>
       <c r="B47" t="n">
-        <v>78891</v>
+        <v>98101</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6466,41 +6466,50 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>283</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461733</v>
+        <v>461721</v>
       </c>
       <c r="R47" t="n">
-        <v>7050778</v>
+        <v>7050576</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6529,7 +6538,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6539,12 +6548,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ett ex på klen gran som saknar topp i äldre granskog</t>
+          <t>Inom en yta på 3x7m</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6559,22 +6568,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124259251</v>
+        <v>124261849</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>78891</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6583,50 +6592,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461721</v>
+        <v>461733</v>
       </c>
       <c r="R48" t="n">
-        <v>7050576</v>
+        <v>7050778</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Inom en yta på 3x7m</t>
+          <t>Ett ex på klen gran som saknar topp i äldre granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6685,22 +6685,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124261213</v>
+        <v>124262454</v>
       </c>
       <c r="B49" t="n">
-        <v>77743</v>
+        <v>79891</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6713,21 +6713,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6737,10 +6737,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>461731</v>
+        <v>461608</v>
       </c>
       <c r="R49" t="n">
-        <v>7050704</v>
+        <v>7050779</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6772,7 +6772,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På gammal gran i gransumpskog</t>
+          <t>Enstaka bålar på en skadad rönn.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6798,26 +6798,51 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124262454</v>
+        <v>124261213</v>
       </c>
       <c r="B50" t="n">
-        <v>79891</v>
+        <v>77743</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6830,21 +6855,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6854,10 +6879,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>461608</v>
+        <v>461731</v>
       </c>
       <c r="R50" t="n">
-        <v>7050779</v>
+        <v>7050704</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6889,7 +6914,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6899,12 +6924,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en skadad rönn.</t>
+          <t>På gammal gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6915,41 +6940,16 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -7892,10 +7892,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124261741</v>
+        <v>124264003</v>
       </c>
       <c r="B59" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7904,41 +7904,60 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461728</v>
+        <v>461546</v>
       </c>
       <c r="R59" t="n">
-        <v>7050768</v>
+        <v>7050666</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7967,7 +7986,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7977,12 +7996,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>Minst 51 plantor inom ca 2 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7993,16 +8012,21 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -8410,10 +8434,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124262979</v>
+        <v>124261741</v>
       </c>
       <c r="B63" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8422,43 +8446,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461543</v>
+        <v>461728</v>
       </c>
       <c r="R63" t="n">
-        <v>7050645</v>
+        <v>7050768</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8490,7 +8509,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8500,12 +8519,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8520,22 +8539,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124264003</v>
+        <v>124262979</v>
       </c>
       <c r="B64" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8544,45 +8563,31 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8591,13 +8596,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461546</v>
+        <v>461543</v>
       </c>
       <c r="R64" t="n">
-        <v>7050666</v>
+        <v>7050645</v>
       </c>
       <c r="S64" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8626,7 +8631,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8636,12 +8641,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Minst 51 plantor inom ca 2 m2 i gammal granskog.</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8652,21 +8657,16 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -9571,10 +9571,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124263683</v>
+        <v>124263837</v>
       </c>
       <c r="B72" t="n">
-        <v>98101</v>
+        <v>77743</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9583,60 +9583,41 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>461584</v>
+        <v>461549</v>
       </c>
       <c r="R72" t="n">
-        <v>7050644</v>
+        <v>7050671</v>
       </c>
       <c r="S72" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9665,7 +9646,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9675,12 +9656,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Minst 63 plantor inom ca 2 x 1 m2 i gammal granskog.</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9691,31 +9672,26 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124263837</v>
+        <v>124263683</v>
       </c>
       <c r="B73" t="n">
-        <v>77743</v>
+        <v>98101</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9724,41 +9700,60 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>461549</v>
+        <v>461584</v>
       </c>
       <c r="R73" t="n">
-        <v>7050671</v>
+        <v>7050644</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9787,7 +9782,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9797,12 +9792,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Minst 63 plantor inom ca 2 x 1 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9813,16 +9808,21 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -10351,10 +10351,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124263225</v>
+        <v>124259946</v>
       </c>
       <c r="B78" t="n">
-        <v>91012</v>
+        <v>78891</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10367,21 +10367,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10391,10 +10391,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>461603</v>
+        <v>461815</v>
       </c>
       <c r="R78" t="n">
-        <v>7050578</v>
+        <v>7050652</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På tunn levande gren på gammal klen gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10468,10 +10468,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124259946</v>
+        <v>124263852</v>
       </c>
       <c r="B79" t="n">
-        <v>78891</v>
+        <v>74901</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10484,21 +10484,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>283</v>
+        <v>6440</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10508,10 +10508,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>461815</v>
+        <v>461549</v>
       </c>
       <c r="R79" t="n">
-        <v>7050652</v>
+        <v>7050671</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10543,7 +10543,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>På tunn levande gren på gammal klen gran i gammal fuktig granskog</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10578,17 +10578,17 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124263852</v>
+        <v>124263225</v>
       </c>
       <c r="B80" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10601,21 +10601,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10625,10 +10625,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>461549</v>
+        <v>461603</v>
       </c>
       <c r="R80" t="n">
-        <v>7050671</v>
+        <v>7050578</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10660,7 +10660,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10670,12 +10670,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -11449,10 +11449,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124260773</v>
+        <v>124262632</v>
       </c>
       <c r="B87" t="n">
-        <v>91673</v>
+        <v>79857</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11461,43 +11461,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>898</v>
+        <v>229748</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>461785</v>
+        <v>461651</v>
       </c>
       <c r="R87" t="n">
-        <v>7050704</v>
+        <v>7050724</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11529,7 +11524,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11539,12 +11534,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>På gammal ullticka på granlåga i bördig, fuktig lågarik granskog</t>
+          <t>På rönn vid bäck i gammal granskog</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11555,21 +11550,6 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -11586,10 +11566,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124258793</v>
+        <v>124262044</v>
       </c>
       <c r="B88" t="n">
-        <v>95335</v>
+        <v>77743</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11598,25 +11578,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2809</v>
+        <v>228579</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -11626,10 +11606,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>461641</v>
+        <v>461724</v>
       </c>
       <c r="R88" t="n">
-        <v>7050551</v>
+        <v>7050772</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11661,7 +11641,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11671,12 +11651,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran (28 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11830,10 +11810,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124262632</v>
+        <v>124260773</v>
       </c>
       <c r="B90" t="n">
-        <v>79857</v>
+        <v>91673</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11842,38 +11822,43 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>229748</v>
+        <v>898</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>461651</v>
+        <v>461785</v>
       </c>
       <c r="R90" t="n">
-        <v>7050724</v>
+        <v>7050704</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11905,7 +11890,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11915,12 +11900,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På rönn vid bäck i gammal granskog</t>
+          <t>På gammal ullticka på granlåga i bördig, fuktig lågarik granskog</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11931,6 +11916,21 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -11947,10 +11947,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124262044</v>
+        <v>124258793</v>
       </c>
       <c r="B91" t="n">
-        <v>77743</v>
+        <v>95335</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11959,25 +11959,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228579</v>
+        <v>2809</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -11987,10 +11987,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>461724</v>
+        <v>461641</v>
       </c>
       <c r="R91" t="n">
-        <v>7050772</v>
+        <v>7050551</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12022,7 +12022,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -12032,12 +12032,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (28 cm dbh) i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD91" t="b">

--- a/artfynd/A 12479-2025 artfynd.xlsx
+++ b/artfynd/A 12479-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124242253</v>
+        <v>124243366</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461780</v>
+        <v>461694</v>
       </c>
       <c r="R2" t="n">
-        <v>7050582</v>
+        <v>7050529</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i en murken granhögstubbe.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,12 +799,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -812,10 +822,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124243782</v>
+        <v>124244822</v>
       </c>
       <c r="B3" t="n">
-        <v>95335</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -824,41 +834,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461757</v>
+        <v>461680</v>
       </c>
       <c r="R3" t="n">
-        <v>7050561</v>
+        <v>7050615</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +902,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,12 +912,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Vid en bäck i gammal granskog.</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,6 +927,26 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -934,10 +964,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124244822</v>
+        <v>124244006</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -950,42 +980,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461680</v>
+        <v>461840</v>
       </c>
       <c r="R4" t="n">
-        <v>7050615</v>
+        <v>7050563</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1014,7 +1039,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1024,7 +1049,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Enstaka på en grov sälglåga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,22 +1073,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1076,10 +1106,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124244322</v>
+        <v>124241982</v>
       </c>
       <c r="B5" t="n">
-        <v>100279</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1088,46 +1118,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461935</v>
+        <v>461758</v>
       </c>
       <c r="R5" t="n">
-        <v>7050570</v>
+        <v>7050534</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1156,7 +1181,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1166,7 +1191,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1181,6 +1211,26 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1198,10 +1248,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124244983</v>
+        <v>124243996</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1210,38 +1260,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461652</v>
+        <v>461837</v>
       </c>
       <c r="R6" t="n">
-        <v>7050519</v>
+        <v>7050572</v>
       </c>
       <c r="S6" t="n">
         <v>7</v>
@@ -1273,7 +1328,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1283,7 +1338,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På en grov sälglåga.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1302,22 +1362,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1335,10 +1395,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124243996</v>
+        <v>124244322</v>
       </c>
       <c r="B7" t="n">
-        <v>79927</v>
+        <v>100279</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1351,27 +1411,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1380,13 +1440,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461837</v>
+        <v>461935</v>
       </c>
       <c r="R7" t="n">
-        <v>7050572</v>
+        <v>7050570</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1415,7 +1475,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1425,12 +1485,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:23</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På en grov sälglåga.</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1445,26 +1500,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1482,10 +1517,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124244357</v>
+        <v>124243782</v>
       </c>
       <c r="B8" t="n">
-        <v>57883</v>
+        <v>95335</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1498,51 +1533,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>2809</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461909</v>
+        <v>461757</v>
       </c>
       <c r="R8" t="n">
-        <v>7050579</v>
+        <v>7050561</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1571,7 +1592,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1581,12 +1602,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>I flerskiktad äldre granskog.</t>
+          <t>Vid en bäck i gammal granskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1618,10 +1639,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124243366</v>
+        <v>124244491</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1634,42 +1655,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461694</v>
+        <v>461860</v>
       </c>
       <c r="R9" t="n">
-        <v>7050529</v>
+        <v>7050631</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1698,7 +1714,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1708,12 +1724,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i en murken granhögstubbe.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1742,12 +1758,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1765,7 +1781,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124242084</v>
+        <v>124241219</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1801,14 +1817,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461835</v>
+        <v>461671</v>
       </c>
       <c r="R10" t="n">
-        <v>7050524</v>
+        <v>7050487</v>
       </c>
       <c r="S10" t="n">
         <v>7</v>
@@ -1840,7 +1856,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1850,7 +1866,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1902,10 +1918,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124241982</v>
+        <v>124244443</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1918,21 +1934,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1942,13 +1958,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461758</v>
+        <v>461867</v>
       </c>
       <c r="R11" t="n">
-        <v>7050534</v>
+        <v>7050617</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1977,7 +1993,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1987,12 +2003,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På en sälglåga.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2011,22 +2027,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2044,7 +2060,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124244491</v>
+        <v>124242084</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -2084,13 +2100,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461860</v>
+        <v>461835</v>
       </c>
       <c r="R12" t="n">
-        <v>7050631</v>
+        <v>7050524</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2119,7 +2135,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2129,12 +2145,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:46</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2186,7 +2197,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124241219</v>
+        <v>124242253</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -2222,17 +2233,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461671</v>
+        <v>461780</v>
       </c>
       <c r="R13" t="n">
-        <v>7050487</v>
+        <v>7050582</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2261,7 +2272,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2271,7 +2282,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2323,7 +2334,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124244443</v>
+        <v>124244983</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -2359,17 +2370,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461867</v>
+        <v>461652</v>
       </c>
       <c r="R14" t="n">
-        <v>7050617</v>
+        <v>7050519</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2398,7 +2409,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2408,12 +2419,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:43</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2442,12 +2448,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2612,10 +2618,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124244006</v>
+        <v>124244357</v>
       </c>
       <c r="B16" t="n">
-        <v>79891</v>
+        <v>57883</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2624,41 +2630,55 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461840</v>
+        <v>461909</v>
       </c>
       <c r="R16" t="n">
-        <v>7050563</v>
+        <v>7050579</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2687,7 +2707,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2697,12 +2717,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Enstaka på en grov sälglåga.</t>
+          <t>I flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2717,26 +2737,6 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2754,10 +2754,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124260115</v>
+        <v>124259251</v>
       </c>
       <c r="B17" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2766,46 +2766,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461636</v>
+        <v>461721</v>
       </c>
       <c r="R17" t="n">
-        <v>7050841</v>
+        <v>7050576</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2834,7 +2838,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2844,7 +2848,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Inom en yta på 3x7m</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2855,31 +2864,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124259426</v>
+        <v>124263802</v>
       </c>
       <c r="B18" t="n">
-        <v>77743</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2888,41 +2892,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461787</v>
+        <v>461536</v>
       </c>
       <c r="R18" t="n">
-        <v>7050628</v>
+        <v>7050642</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2951,7 +2955,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2961,7 +2965,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ca 40 ex inom en kvadratmeter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2976,22 +2985,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124260158</v>
+        <v>124259289</v>
       </c>
       <c r="B19" t="n">
-        <v>79891</v>
+        <v>95347</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3000,25 +3009,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>2813</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -3028,10 +3037,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461793</v>
+        <v>461716</v>
       </c>
       <c r="R19" t="n">
-        <v>7050683</v>
+        <v>7050630</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3063,7 +3072,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3073,12 +3082,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På bark på död rönnstubbe</t>
+          <t>På marken i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3098,17 +3107,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124262970</v>
+        <v>124261741</v>
       </c>
       <c r="B20" t="n">
-        <v>79892</v>
+        <v>90977</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3117,41 +3126,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461598</v>
+        <v>461728</v>
       </c>
       <c r="R20" t="n">
-        <v>7050665</v>
+        <v>7050768</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3180,7 +3189,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3190,12 +3199,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Enstaka på en flerstammig sälg.</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3206,51 +3215,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124263257</v>
+        <v>124260090</v>
       </c>
       <c r="B21" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3263,46 +3247,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461584</v>
+        <v>461642</v>
       </c>
       <c r="R21" t="n">
-        <v>7050588</v>
+        <v>7050845</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3331,7 +3306,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3341,7 +3316,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3352,26 +3327,51 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124241603</v>
+        <v>124259169</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3380,55 +3380,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461712</v>
+        <v>461539</v>
       </c>
       <c r="R22" t="n">
-        <v>7050513</v>
+        <v>7050804</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3452,27 +3438,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:55</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Minst 78 plantor och 3 vinterståndare inom ca 1 m2 i gammal granskog.</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3487,6 +3468,26 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3504,7 +3505,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124260479</v>
+        <v>124259378</v>
       </c>
       <c r="B23" t="n">
         <v>79891</v>
@@ -3540,7 +3541,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3549,10 +3550,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461666</v>
+        <v>461603</v>
       </c>
       <c r="R23" t="n">
-        <v>7050837</v>
+        <v>7050832</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3584,7 +3585,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3594,12 +3595,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns intill en bäck i gammal högväxt granskog.</t>
+          <t>Ymnigt med lunglav på en gammal grov sälg. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3618,12 +3619,12 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
@@ -3633,7 +3634,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3651,10 +3652,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124260842</v>
+        <v>124263001</v>
       </c>
       <c r="B24" t="n">
-        <v>91012</v>
+        <v>79920</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3663,38 +3664,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461785</v>
+        <v>461597</v>
       </c>
       <c r="R24" t="n">
-        <v>7050704</v>
+        <v>7050664</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3726,7 +3732,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3736,12 +3742,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3752,26 +3753,51 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124262348</v>
+        <v>124262725</v>
       </c>
       <c r="B25" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3780,25 +3806,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3808,10 +3834,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461656</v>
+        <v>461642</v>
       </c>
       <c r="R25" t="n">
-        <v>7050743</v>
+        <v>7050696</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3843,7 +3869,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3853,12 +3879,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På rönn vid bäck</t>
+          <t>På gammal gran i gammal fuktig granskog nära bäck</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3885,10 +3911,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124261077</v>
+        <v>124260468</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3901,21 +3927,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3925,10 +3951,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461731</v>
+        <v>461783</v>
       </c>
       <c r="R26" t="n">
-        <v>7050711</v>
+        <v>7050722</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3960,7 +3986,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3970,12 +3996,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal fuktig granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4002,10 +4028,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124259895</v>
+        <v>124260115</v>
       </c>
       <c r="B27" t="n">
-        <v>74893</v>
+        <v>100279</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4014,41 +4040,46 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>308</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461797</v>
+        <v>461636</v>
       </c>
       <c r="R27" t="n">
-        <v>7050670</v>
+        <v>7050841</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4077,7 +4108,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4087,12 +4118,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt på ved på basen av granhögstubbe i fuktig gammal granskog</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4103,26 +4129,31 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124259289</v>
+        <v>124262044</v>
       </c>
       <c r="B28" t="n">
-        <v>95347</v>
+        <v>77743</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4131,25 +4162,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2813</v>
+        <v>228579</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4159,10 +4190,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461716</v>
+        <v>461724</v>
       </c>
       <c r="R28" t="n">
-        <v>7050630</v>
+        <v>7050772</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4194,7 +4225,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4204,12 +4235,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På marken i gammal sumpgranskog</t>
+          <t>På bark på stam av levande gammal gran (28 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4236,10 +4267,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124263536</v>
+        <v>124259967</v>
       </c>
       <c r="B29" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4252,27 +4283,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4281,13 +4312,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461544</v>
+        <v>461623</v>
       </c>
       <c r="R29" t="n">
-        <v>7050635</v>
+        <v>7050871</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4316,7 +4347,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4326,12 +4357,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gammal gran i gammal granskog</t>
+          <t>Rikligt på en skadad rönn.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4342,26 +4373,51 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124262198</v>
+        <v>124260947</v>
       </c>
       <c r="B30" t="n">
-        <v>105102</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4370,25 +4426,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4398,13 +4454,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461687</v>
+        <v>461749</v>
       </c>
       <c r="R30" t="n">
-        <v>7050752</v>
+        <v>7050709</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4433,7 +4489,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4443,12 +4499,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På marken i fuktig gammal granskog</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4475,10 +4526,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124258944</v>
+        <v>124263059</v>
       </c>
       <c r="B31" t="n">
-        <v>57883</v>
+        <v>74901</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4487,60 +4538,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103015</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461559</v>
+        <v>461654</v>
       </c>
       <c r="R31" t="n">
-        <v>7050789</v>
+        <v>7050616</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4569,7 +4601,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4579,12 +4611,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4595,31 +4627,26 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124263066</v>
+        <v>124262632</v>
       </c>
       <c r="B32" t="n">
-        <v>77743</v>
+        <v>79857</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4628,25 +4655,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228579</v>
+        <v>229748</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4656,10 +4683,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461654</v>
+        <v>461651</v>
       </c>
       <c r="R32" t="n">
-        <v>7050616</v>
+        <v>7050724</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4691,7 +4718,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4701,12 +4728,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På rönn vid bäck i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4733,10 +4760,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124259877</v>
+        <v>124261793</v>
       </c>
       <c r="B33" t="n">
-        <v>79891</v>
+        <v>57529</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4749,42 +4776,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461614</v>
+        <v>461776</v>
       </c>
       <c r="R33" t="n">
-        <v>7050862</v>
+        <v>7050867</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4813,7 +4840,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4823,12 +4850,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ymnig påväxt på en grov gammal sälg där vissa bålar är fertila med apothecier.</t>
+          <t>Letade efter hästmyra</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4839,51 +4866,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>August Nordin, Ludvig Nordin, Emil Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124263001</v>
+        <v>124260479</v>
       </c>
       <c r="B34" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4892,46 +4894,46 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461597</v>
+        <v>461666</v>
       </c>
       <c r="R34" t="n">
-        <v>7050664</v>
+        <v>7050837</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4960,7 +4962,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4970,7 +4972,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns intill en bäck i gammal högväxt granskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4989,12 +4996,12 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
@@ -5004,7 +5011,7 @@
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5022,10 +5029,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124262686</v>
+        <v>124263852</v>
       </c>
       <c r="B35" t="n">
-        <v>79920</v>
+        <v>74901</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5034,46 +5041,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461617</v>
+        <v>461549</v>
       </c>
       <c r="R35" t="n">
-        <v>7050728</v>
+        <v>7050671</v>
       </c>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5102,7 +5104,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5112,7 +5114,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5123,51 +5130,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124260205</v>
+        <v>124259895</v>
       </c>
       <c r="B36" t="n">
-        <v>79920</v>
+        <v>74893</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5176,25 +5158,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5204,10 +5186,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461793</v>
+        <v>461797</v>
       </c>
       <c r="R36" t="n">
-        <v>7050683</v>
+        <v>7050670</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5239,7 +5221,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5249,12 +5231,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På bark på rönnhögststubbe i gammal fuktig granskog</t>
+          <t>Rikligt på ved på basen av granhögstubbe i fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5281,10 +5263,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124263649</v>
+        <v>124262970</v>
       </c>
       <c r="B37" t="n">
-        <v>79920</v>
+        <v>79892</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5293,41 +5275,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461556</v>
+        <v>461598</v>
       </c>
       <c r="R37" t="n">
-        <v>7050632</v>
+        <v>7050665</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5356,7 +5338,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5366,12 +5348,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På gammal grov sälg i gammal granskog</t>
+          <t>Enstaka på en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5382,26 +5364,51 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124262760</v>
+        <v>124261248</v>
       </c>
       <c r="B38" t="n">
-        <v>57883</v>
+        <v>91030</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5410,50 +5417,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461558</v>
+        <v>461756</v>
       </c>
       <c r="R38" t="n">
-        <v>7050692</v>
+        <v>7050765</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5482,7 +5480,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5492,7 +5490,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5512,17 +5510,17 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Emil Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124260054</v>
+        <v>124261167</v>
       </c>
       <c r="B39" t="n">
-        <v>96979</v>
+        <v>74901</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5531,41 +5529,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461843</v>
+        <v>461741</v>
       </c>
       <c r="R39" t="n">
-        <v>7050661</v>
+        <v>7050704</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5594,7 +5592,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5604,7 +5602,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På gammal gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5619,22 +5622,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Emil Nordin, Ludvig Nordin</t>
+          <t>Ulrika Nordin, Emil Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124262353</v>
+        <v>124260873</v>
       </c>
       <c r="B40" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5647,21 +5650,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5671,13 +5674,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461655</v>
+        <v>461744</v>
       </c>
       <c r="R40" t="n">
-        <v>7050759</v>
+        <v>7050919</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5706,7 +5709,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5716,12 +5719,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På gran ca 40 cm i diameter intill bäck</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5732,26 +5730,51 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124261167</v>
+        <v>124259426</v>
       </c>
       <c r="B41" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5764,37 +5787,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461741</v>
+        <v>461787</v>
       </c>
       <c r="R41" t="n">
-        <v>7050704</v>
+        <v>7050628</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5823,7 +5846,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5833,12 +5856,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:48</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På gammal gran i gransumpskog</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5853,22 +5871,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Emil Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124262932</v>
+        <v>124260054</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>96979</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5877,50 +5895,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461633</v>
+        <v>461843</v>
       </c>
       <c r="R42" t="n">
-        <v>7050666</v>
+        <v>7050661</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5949,7 +5958,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5959,12 +5968,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5979,22 +5983,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Emil Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124263059</v>
+        <v>124261077</v>
       </c>
       <c r="B43" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6007,21 +6011,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -6031,10 +6035,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461654</v>
+        <v>461731</v>
       </c>
       <c r="R43" t="n">
-        <v>7050616</v>
+        <v>7050711</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6066,7 +6070,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6076,12 +6080,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6108,10 +6112,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124263103</v>
+        <v>124263536</v>
       </c>
       <c r="B44" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6124,37 +6128,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461643</v>
+        <v>461544</v>
       </c>
       <c r="R44" t="n">
-        <v>7050590</v>
+        <v>7050635</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6183,7 +6192,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6193,12 +6202,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På gammal rönn I gammal granskog</t>
+          <t>Äldre ringhack på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6225,10 +6234,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124263170</v>
+        <v>124263132</v>
       </c>
       <c r="B45" t="n">
-        <v>77743</v>
+        <v>91030</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6241,37 +6250,51 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228579</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461624</v>
+        <v>461570</v>
       </c>
       <c r="R45" t="n">
-        <v>7050624</v>
+        <v>7050652</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6300,7 +6323,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6310,12 +6333,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På gammal gran i fuktig äldre granskog</t>
+          <t>Rikligt med fruktkroppar i en grov gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6326,26 +6349,51 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124263373</v>
+        <v>124260773</v>
       </c>
       <c r="B46" t="n">
-        <v>77743</v>
+        <v>91673</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6354,38 +6402,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228579</v>
+        <v>898</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461587</v>
+        <v>461785</v>
       </c>
       <c r="R46" t="n">
-        <v>7050582</v>
+        <v>7050704</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6417,7 +6470,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6427,7 +6480,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På gammal ullticka på granlåga i bördig, fuktig lågarik granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6438,26 +6496,41 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124259251</v>
+        <v>124262807</v>
       </c>
       <c r="B47" t="n">
-        <v>98101</v>
+        <v>74901</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6466,50 +6539,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461721</v>
+        <v>461633</v>
       </c>
       <c r="R47" t="n">
-        <v>7050576</v>
+        <v>7050701</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6538,7 +6602,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6548,12 +6612,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Inom en yta på 3x7m</t>
+          <t>På gammal gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6568,22 +6632,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124261849</v>
+        <v>124262686</v>
       </c>
       <c r="B48" t="n">
-        <v>78891</v>
+        <v>79920</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6592,41 +6656,46 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>283</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461733</v>
+        <v>461617</v>
       </c>
       <c r="R48" t="n">
-        <v>7050778</v>
+        <v>7050728</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6655,7 +6724,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6665,12 +6734,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:08</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ett ex på klen gran som saknar topp i äldre granskog</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6681,26 +6745,51 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124262454</v>
+        <v>124258944</v>
       </c>
       <c r="B49" t="n">
-        <v>79891</v>
+        <v>57883</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6709,41 +6798,60 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>461608</v>
+        <v>461559</v>
       </c>
       <c r="R49" t="n">
-        <v>7050779</v>
+        <v>7050789</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6772,7 +6880,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6782,12 +6890,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en skadad rönn.</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6802,26 +6910,6 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6839,10 +6927,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124261213</v>
+        <v>124260536</v>
       </c>
       <c r="B50" t="n">
-        <v>77743</v>
+        <v>100279</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6851,41 +6939,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228579</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>461731</v>
+        <v>461834</v>
       </c>
       <c r="R50" t="n">
-        <v>7050704</v>
+        <v>7050707</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6914,7 +7002,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6924,12 +7012,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:48</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På gammal gran i gransumpskog</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6944,22 +7027,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124262807</v>
+        <v>124261213</v>
       </c>
       <c r="B51" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6972,21 +7055,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6996,10 +7079,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461633</v>
+        <v>461731</v>
       </c>
       <c r="R51" t="n">
-        <v>7050701</v>
+        <v>7050704</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7031,7 +7114,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7041,7 +7124,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -7073,10 +7156,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124261626</v>
+        <v>124262908</v>
       </c>
       <c r="B52" t="n">
-        <v>56714</v>
+        <v>77743</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7089,42 +7172,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102612</v>
+        <v>228579</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461768</v>
+        <v>461633</v>
       </c>
       <c r="R52" t="n">
-        <v>7050794</v>
+        <v>7050666</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7153,7 +7231,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7163,7 +7241,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran (ca 170 år gammal) i gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7174,31 +7257,26 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124260175</v>
+        <v>124258987</v>
       </c>
       <c r="B53" t="n">
-        <v>74885</v>
+        <v>78810</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7207,25 +7285,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7235,10 +7313,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461793</v>
+        <v>461689</v>
       </c>
       <c r="R53" t="n">
-        <v>7050683</v>
+        <v>7050585</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7270,7 +7348,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7280,12 +7358,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På ved på rönnhögstubbe i gammal fuktig granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7312,10 +7390,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124261426</v>
+        <v>124263250</v>
       </c>
       <c r="B54" t="n">
-        <v>78891</v>
+        <v>78810</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7328,21 +7406,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7352,10 +7430,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>461715</v>
+        <v>461629</v>
       </c>
       <c r="R54" t="n">
-        <v>7050700</v>
+        <v>7050621</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7387,7 +7465,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7397,12 +7475,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På kvist på klen gran i gransumpskog</t>
+          <t>Ett 100-tal bålar på ett 10-tal granar</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7429,10 +7507,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124262526</v>
+        <v>124260175</v>
       </c>
       <c r="B55" t="n">
-        <v>79927</v>
+        <v>74885</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7445,21 +7523,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>6439</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7469,10 +7547,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>461665</v>
+        <v>461793</v>
       </c>
       <c r="R55" t="n">
-        <v>7050738</v>
+        <v>7050683</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7504,7 +7582,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7514,12 +7592,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På död rönn intill bäck</t>
+          <t>På ved på rönnhögstubbe i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7534,19 +7612,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124260468</v>
+        <v>124262878</v>
       </c>
       <c r="B56" t="n">
         <v>74901</v>
@@ -7586,10 +7664,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461783</v>
+        <v>461633</v>
       </c>
       <c r="R56" t="n">
-        <v>7050722</v>
+        <v>7050666</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7621,7 +7699,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7631,12 +7709,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal fuktig granskog</t>
+          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 170 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7663,10 +7741,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124263250</v>
+        <v>124259877</v>
       </c>
       <c r="B57" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7679,37 +7757,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461629</v>
+        <v>461614</v>
       </c>
       <c r="R57" t="n">
-        <v>7050621</v>
+        <v>7050862</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7738,7 +7821,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7748,12 +7831,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ett 100-tal bålar på ett 10-tal granar</t>
+          <t>Ymnig påväxt på en grov gammal sälg där vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7764,26 +7847,51 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124260536</v>
+        <v>124261849</v>
       </c>
       <c r="B58" t="n">
-        <v>100279</v>
+        <v>78891</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7792,41 +7900,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461834</v>
+        <v>461733</v>
       </c>
       <c r="R58" t="n">
-        <v>7050707</v>
+        <v>7050778</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7855,7 +7963,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7865,7 +7973,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ett ex på klen gran som saknar topp i äldre granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7880,22 +7993,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124264003</v>
+        <v>124263373</v>
       </c>
       <c r="B59" t="n">
-        <v>98101</v>
+        <v>77743</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7904,60 +8017,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461546</v>
+        <v>461587</v>
       </c>
       <c r="R59" t="n">
-        <v>7050666</v>
+        <v>7050582</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7986,7 +8080,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7996,12 +8090,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:12</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Minst 51 plantor inom ca 2 m2 i gammal granskog.</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8012,31 +8101,26 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124259967</v>
+        <v>124262760</v>
       </c>
       <c r="B60" t="n">
-        <v>79891</v>
+        <v>57883</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8045,31 +8129,35 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -8078,13 +8166,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461623</v>
+        <v>461558</v>
       </c>
       <c r="R60" t="n">
-        <v>7050871</v>
+        <v>7050692</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8113,7 +8201,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8123,12 +8211,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Rikligt på en skadad rönn.</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8139,51 +8222,26 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124262595</v>
+        <v>124263257</v>
       </c>
       <c r="B61" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8196,37 +8254,46 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461615</v>
+        <v>461584</v>
       </c>
       <c r="R61" t="n">
-        <v>7050725</v>
+        <v>7050588</v>
       </c>
       <c r="S61" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8255,7 +8322,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8265,7 +8332,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8276,48 +8343,23 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124262878</v>
+        <v>124260631</v>
       </c>
       <c r="B62" t="n">
         <v>74901</v>
@@ -8353,14 +8395,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461633</v>
+        <v>461864</v>
       </c>
       <c r="R62" t="n">
-        <v>7050666</v>
+        <v>7050679</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8392,7 +8434,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8402,12 +8444,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 170 år) i gammal granskog</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8422,22 +8459,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124261741</v>
+        <v>124260205</v>
       </c>
       <c r="B63" t="n">
-        <v>90977</v>
+        <v>79920</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8450,21 +8487,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8474,10 +8511,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461728</v>
+        <v>461793</v>
       </c>
       <c r="R63" t="n">
-        <v>7050768</v>
+        <v>7050683</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8509,7 +8546,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8519,12 +8556,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På bark på rönnhögststubbe i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8544,17 +8581,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124262979</v>
+        <v>124263683</v>
       </c>
       <c r="B64" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8563,31 +8600,45 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8596,13 +8647,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461543</v>
+        <v>461584</v>
       </c>
       <c r="R64" t="n">
-        <v>7050645</v>
+        <v>7050644</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8631,7 +8682,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8641,12 +8692,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Minst 63 plantor inom ca 2 x 1 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8657,26 +8708,31 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124260873</v>
+        <v>124263170</v>
       </c>
       <c r="B65" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8689,21 +8745,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8713,13 +8769,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>461744</v>
+        <v>461624</v>
       </c>
       <c r="R65" t="n">
-        <v>7050919</v>
+        <v>7050624</v>
       </c>
       <c r="S65" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8748,7 +8804,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8758,7 +8814,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På gammal gran i fuktig äldre granskog</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8769,51 +8830,26 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124260993</v>
+        <v>124259759</v>
       </c>
       <c r="B66" t="n">
-        <v>57529</v>
+        <v>77743</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8826,42 +8862,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>228579</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Småfloarna, Småfloarna, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>461776</v>
+        <v>461789</v>
       </c>
       <c r="R66" t="n">
-        <v>7050859</v>
+        <v>7050616</v>
       </c>
       <c r="S66" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8890,7 +8921,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8900,12 +8931,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Rejäla hackspår.</t>
+          <t>På gammal gran ca 5 m från bäck i äldre granskog</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8916,51 +8947,26 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124261793</v>
+        <v>124263103</v>
       </c>
       <c r="B67" t="n">
-        <v>57529</v>
+        <v>79891</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8973,42 +8979,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461776</v>
+        <v>461643</v>
       </c>
       <c r="R67" t="n">
-        <v>7050867</v>
+        <v>7050590</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9037,7 +9038,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9047,12 +9048,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Letade efter hästmyra</t>
+          <t>På gammal rönn I gammal granskog</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9067,22 +9068,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>August Nordin, Ludvig Nordin, Emil Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124263802</v>
+        <v>124262454</v>
       </c>
       <c r="B68" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9091,25 +9092,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -9119,10 +9120,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>461536</v>
+        <v>461608</v>
       </c>
       <c r="R68" t="n">
-        <v>7050642</v>
+        <v>7050779</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9154,7 +9155,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9164,12 +9165,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ca 40 ex inom en kvadratmeter</t>
+          <t>Enstaka bålar på en skadad rönn.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9180,23 +9181,48 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124259169</v>
+        <v>124262595</v>
       </c>
       <c r="B69" t="n">
         <v>78810</v>
@@ -9236,13 +9262,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>461539</v>
+        <v>461615</v>
       </c>
       <c r="R69" t="n">
-        <v>7050804</v>
+        <v>7050725</v>
       </c>
       <c r="S69" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9271,7 +9297,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9281,7 +9307,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9310,12 +9336,12 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9333,10 +9359,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124262035</v>
+        <v>124259184</v>
       </c>
       <c r="B70" t="n">
-        <v>79891</v>
+        <v>74901</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9349,46 +9375,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>461712</v>
+        <v>461677</v>
       </c>
       <c r="R70" t="n">
-        <v>7050901</v>
+        <v>7050616</v>
       </c>
       <c r="S70" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9417,7 +9434,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9427,12 +9444,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>På död gran i sumpgranskog</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9447,22 +9464,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124260631</v>
+        <v>124241603</v>
       </c>
       <c r="B71" t="n">
-        <v>74901</v>
+        <v>98101</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9471,38 +9488,52 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>461864</v>
+        <v>461712</v>
       </c>
       <c r="R71" t="n">
-        <v>7050679</v>
+        <v>7050513</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9529,22 +9560,27 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Minst 78 plantor och 3 vinterståndare inom ca 1 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9555,26 +9591,31 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124263837</v>
+        <v>124264003</v>
       </c>
       <c r="B72" t="n">
-        <v>77743</v>
+        <v>98101</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9583,41 +9624,60 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>461549</v>
+        <v>461546</v>
       </c>
       <c r="R72" t="n">
-        <v>7050671</v>
+        <v>7050666</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9646,7 +9706,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9656,12 +9716,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Minst 51 plantor inom ca 2 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9672,26 +9732,31 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124263683</v>
+        <v>124262353</v>
       </c>
       <c r="B73" t="n">
-        <v>98101</v>
+        <v>77743</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9700,60 +9765,41 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>461584</v>
+        <v>461655</v>
       </c>
       <c r="R73" t="n">
-        <v>7050644</v>
+        <v>7050759</v>
       </c>
       <c r="S73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9782,7 +9828,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9792,12 +9838,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Minst 63 plantor inom ca 2 x 1 m2 i gammal granskog.</t>
+          <t>På gran ca 40 cm i diameter intill bäck</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9808,31 +9854,26 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124263132</v>
+        <v>124263837</v>
       </c>
       <c r="B74" t="n">
-        <v>91030</v>
+        <v>77743</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9845,51 +9886,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>461570</v>
+        <v>461549</v>
       </c>
       <c r="R74" t="n">
-        <v>7050652</v>
+        <v>7050671</v>
       </c>
       <c r="S74" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9918,7 +9945,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9928,12 +9955,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i en grov gran.</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9944,51 +9971,26 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124260090</v>
+        <v>124261426</v>
       </c>
       <c r="B75" t="n">
-        <v>78810</v>
+        <v>78891</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10001,21 +10003,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -10025,13 +10027,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>461642</v>
+        <v>461715</v>
       </c>
       <c r="R75" t="n">
-        <v>7050845</v>
+        <v>7050700</v>
       </c>
       <c r="S75" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10060,7 +10062,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10070,7 +10072,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>På kvist på klen gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10081,51 +10088,26 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124260947</v>
+        <v>124263225</v>
       </c>
       <c r="B76" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10138,21 +10120,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -10162,10 +10144,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>461749</v>
+        <v>461603</v>
       </c>
       <c r="R76" t="n">
-        <v>7050709</v>
+        <v>7050578</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10197,7 +10179,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10207,7 +10189,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10234,10 +10221,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124261444</v>
+        <v>124260702</v>
       </c>
       <c r="B77" t="n">
-        <v>78810</v>
+        <v>100279</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10246,41 +10233,46 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>461810</v>
+        <v>461678</v>
       </c>
       <c r="R77" t="n">
-        <v>7050829</v>
+        <v>7050823</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10309,7 +10301,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10319,12 +10311,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>Både blåvioletta och vita blommor.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10335,26 +10327,31 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124259946</v>
+        <v>124262198</v>
       </c>
       <c r="B78" t="n">
-        <v>78891</v>
+        <v>105102</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10363,25 +10360,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>283</v>
+        <v>221725</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10391,13 +10388,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>461815</v>
+        <v>461687</v>
       </c>
       <c r="R78" t="n">
-        <v>7050652</v>
+        <v>7050752</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10426,7 +10423,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10436,12 +10433,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På tunn levande gren på gammal klen gran i gammal fuktig granskog</t>
+          <t>På marken i fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10468,10 +10465,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124263852</v>
+        <v>124264084</v>
       </c>
       <c r="B79" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10484,37 +10481,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>461549</v>
+        <v>461561</v>
       </c>
       <c r="R79" t="n">
-        <v>7050671</v>
+        <v>7050657</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10543,7 +10540,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10553,12 +10550,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:16</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10569,26 +10561,51 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124263225</v>
+        <v>124259784</v>
       </c>
       <c r="B80" t="n">
-        <v>91012</v>
+        <v>74901</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10601,21 +10618,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10625,10 +10642,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>461603</v>
+        <v>461789</v>
       </c>
       <c r="R80" t="n">
-        <v>7050578</v>
+        <v>7050616</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10660,7 +10677,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10670,12 +10687,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gammal gran ca 5m från bäck i äldre granskog</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10690,22 +10707,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124261471</v>
+        <v>124262348</v>
       </c>
       <c r="B81" t="n">
-        <v>78547</v>
+        <v>79920</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10714,41 +10731,41 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>461800</v>
+        <v>461656</v>
       </c>
       <c r="R81" t="n">
-        <v>7050827</v>
+        <v>7050743</v>
       </c>
       <c r="S81" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10777,7 +10794,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10787,12 +10804,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På kolade tallstubbe.</t>
+          <t>På rönn vid bäck</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10803,51 +10820,26 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Stump # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124262908</v>
+        <v>124263649</v>
       </c>
       <c r="B82" t="n">
-        <v>77743</v>
+        <v>79920</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10856,25 +10848,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228579</v>
+        <v>6462</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10884,10 +10876,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>461633</v>
+        <v>461556</v>
       </c>
       <c r="R82" t="n">
-        <v>7050666</v>
+        <v>7050632</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10919,7 +10911,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10929,12 +10921,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (ca 170 år gammal) i gammal granskog</t>
+          <t>På gammal grov sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10961,10 +10953,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124262725</v>
+        <v>124261471</v>
       </c>
       <c r="B83" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10977,37 +10969,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>461642</v>
+        <v>461800</v>
       </c>
       <c r="R83" t="n">
-        <v>7050696</v>
+        <v>7050827</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -11036,7 +11028,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11046,12 +11038,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal fuktig granskog nära bäck</t>
+          <t>På kolade tallstubbe.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11062,26 +11054,51 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Stump # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124258987</v>
+        <v>124260993</v>
       </c>
       <c r="B84" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11094,37 +11111,42 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Småfloarna, Småfloarna, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>461689</v>
+        <v>461776</v>
       </c>
       <c r="R84" t="n">
-        <v>7050585</v>
+        <v>7050859</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11153,7 +11175,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11163,12 +11185,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Rejäla hackspår.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11179,23 +11201,48 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124264084</v>
+        <v>124261444</v>
       </c>
       <c r="B85" t="n">
         <v>78810</v>
@@ -11231,17 +11278,17 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>461561</v>
+        <v>461810</v>
       </c>
       <c r="R85" t="n">
-        <v>7050657</v>
+        <v>7050829</v>
       </c>
       <c r="S85" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -11270,7 +11317,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11280,7 +11327,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11291,51 +11343,26 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124263675</v>
+        <v>124262932</v>
       </c>
       <c r="B86" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11348,34 +11375,43 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>461551</v>
+        <v>461633</v>
       </c>
       <c r="R86" t="n">
-        <v>7050634</v>
+        <v>7050666</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11407,7 +11443,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11417,12 +11453,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>På sälg ca 60 cm i diameter</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11437,22 +11473,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124262632</v>
+        <v>124260842</v>
       </c>
       <c r="B87" t="n">
-        <v>79857</v>
+        <v>91012</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11461,25 +11497,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229748</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -11489,10 +11525,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>461651</v>
+        <v>461785</v>
       </c>
       <c r="R87" t="n">
-        <v>7050724</v>
+        <v>7050704</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11524,7 +11560,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11534,12 +11570,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>På rönn vid bäck i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11566,10 +11602,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124262044</v>
+        <v>124261626</v>
       </c>
       <c r="B88" t="n">
-        <v>77743</v>
+        <v>56714</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11582,37 +11618,42 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228579</v>
+        <v>102612</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>461724</v>
+        <v>461768</v>
       </c>
       <c r="R88" t="n">
-        <v>7050772</v>
+        <v>7050794</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11641,7 +11682,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11651,12 +11692,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:16</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran (28 cm dbh) i gammal granskog</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11667,26 +11703,31 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124260702</v>
+        <v>124260158</v>
       </c>
       <c r="B89" t="n">
-        <v>100279</v>
+        <v>79891</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11695,46 +11736,41 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>461678</v>
+        <v>461793</v>
       </c>
       <c r="R89" t="n">
-        <v>7050823</v>
+        <v>7050683</v>
       </c>
       <c r="S89" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11763,7 +11799,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11773,12 +11809,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Både blåvioletta och vita blommor.</t>
+          <t>På bark på död rönnstubbe</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11789,31 +11825,26 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
-      </c>
-      <c r="AH89" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124260773</v>
+        <v>124262035</v>
       </c>
       <c r="B90" t="n">
-        <v>91673</v>
+        <v>79891</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11822,31 +11853,35 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>898</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -11855,13 +11890,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>461785</v>
+        <v>461712</v>
       </c>
       <c r="R90" t="n">
-        <v>7050704</v>
+        <v>7050901</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11890,7 +11925,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11900,12 +11935,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På gammal ullticka på granlåga i bördig, fuktig lågarik granskog</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11916,41 +11951,26 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124258793</v>
+        <v>124262526</v>
       </c>
       <c r="B91" t="n">
-        <v>95335</v>
+        <v>79927</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11963,21 +11983,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2809</v>
+        <v>6464</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -11987,10 +12007,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>461641</v>
+        <v>461665</v>
       </c>
       <c r="R91" t="n">
-        <v>7050551</v>
+        <v>7050738</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12022,7 +12042,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -12032,12 +12052,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På död rönn intill bäck</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12052,22 +12072,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124259378</v>
+        <v>124262979</v>
       </c>
       <c r="B92" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12080,42 +12100,42 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>461603</v>
+        <v>461543</v>
       </c>
       <c r="R92" t="n">
-        <v>7050832</v>
+        <v>7050645</v>
       </c>
       <c r="S92" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -12144,7 +12164,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -12154,12 +12174,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglav på en gammal grov sälg. Vissa bålar är fertila med apothecier.</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12170,51 +12190,26 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AH92" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124259784</v>
+        <v>124263066</v>
       </c>
       <c r="B93" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -12227,21 +12222,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -12251,7 +12246,7 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>461789</v>
+        <v>461654</v>
       </c>
       <c r="R93" t="n">
         <v>7050616</v>
@@ -12286,7 +12281,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -12296,12 +12291,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>På gammal gran ca 5m från bäck i äldre granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12316,22 +12311,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124259184</v>
+        <v>124258793</v>
       </c>
       <c r="B94" t="n">
-        <v>74901</v>
+        <v>95335</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12340,25 +12335,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6440</v>
+        <v>2809</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -12368,10 +12363,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>461677</v>
+        <v>461641</v>
       </c>
       <c r="R94" t="n">
-        <v>7050616</v>
+        <v>7050551</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12403,7 +12398,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12413,12 +12408,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>På död gran i sumpgranskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12433,22 +12428,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124261248</v>
+        <v>124263675</v>
       </c>
       <c r="B95" t="n">
-        <v>91030</v>
+        <v>79892</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12461,37 +12456,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>461756</v>
+        <v>461551</v>
       </c>
       <c r="R95" t="n">
-        <v>7050765</v>
+        <v>7050634</v>
       </c>
       <c r="S95" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -12520,7 +12515,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12530,7 +12525,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>På sälg ca 60 cm i diameter</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12545,22 +12545,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Emil Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124259759</v>
+        <v>124259946</v>
       </c>
       <c r="B96" t="n">
-        <v>77743</v>
+        <v>78891</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12573,21 +12573,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228579</v>
+        <v>283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -12597,10 +12597,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>461789</v>
+        <v>461815</v>
       </c>
       <c r="R96" t="n">
-        <v>7050616</v>
+        <v>7050652</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12632,7 +12632,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12642,12 +12642,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>På gammal gran ca 5 m från bäck i äldre granskog</t>
+          <t>På tunn levande gren på gammal klen gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12662,12 +12662,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>

--- a/artfynd/A 12479-2025 artfynd.xlsx
+++ b/artfynd/A 12479-2025 artfynd.xlsx
@@ -3794,10 +3794,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124262725</v>
+        <v>124262044</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3810,21 +3810,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3834,10 +3834,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461642</v>
+        <v>461724</v>
       </c>
       <c r="R25" t="n">
-        <v>7050696</v>
+        <v>7050772</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal fuktig granskog nära bäck</t>
+          <t>På bark på stam av levande gammal gran (28 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3911,10 +3911,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124260468</v>
+        <v>124262725</v>
       </c>
       <c r="B26" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3927,21 +3927,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461783</v>
+        <v>461642</v>
       </c>
       <c r="R26" t="n">
-        <v>7050722</v>
+        <v>7050696</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal fuktig granskog</t>
+          <t>På gammal gran i gammal fuktig granskog nära bäck</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4028,10 +4028,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124260115</v>
+        <v>124260468</v>
       </c>
       <c r="B27" t="n">
-        <v>100279</v>
+        <v>74901</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4040,46 +4040,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461636</v>
+        <v>461783</v>
       </c>
       <c r="R27" t="n">
-        <v>7050841</v>
+        <v>7050722</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4108,7 +4103,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4118,7 +4113,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4129,31 +4129,26 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124262044</v>
+        <v>124260115</v>
       </c>
       <c r="B28" t="n">
-        <v>77743</v>
+        <v>100279</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4162,41 +4157,46 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228579</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461724</v>
+        <v>461636</v>
       </c>
       <c r="R28" t="n">
-        <v>7050772</v>
+        <v>7050841</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4235,12 +4235,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:16</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran (28 cm dbh) i gammal granskog</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4251,16 +4246,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -6927,10 +6927,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124260536</v>
+        <v>124261213</v>
       </c>
       <c r="B50" t="n">
-        <v>100279</v>
+        <v>77743</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6939,41 +6939,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>228579</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>461834</v>
+        <v>461731</v>
       </c>
       <c r="R50" t="n">
-        <v>7050707</v>
+        <v>7050704</v>
       </c>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7012,7 +7012,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På gammal gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7027,19 +7032,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124261213</v>
+        <v>124262908</v>
       </c>
       <c r="B51" t="n">
         <v>77743</v>
@@ -7079,10 +7084,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461731</v>
+        <v>461633</v>
       </c>
       <c r="R51" t="n">
-        <v>7050704</v>
+        <v>7050666</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7114,7 +7119,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7124,12 +7129,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På gammal gran i gransumpskog</t>
+          <t>På bark på stam av levande gammal gran (ca 170 år gammal) i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7144,22 +7149,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124262908</v>
+        <v>124260536</v>
       </c>
       <c r="B52" t="n">
-        <v>77743</v>
+        <v>100279</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7168,41 +7173,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228579</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461633</v>
+        <v>461834</v>
       </c>
       <c r="R52" t="n">
-        <v>7050666</v>
+        <v>7050707</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7231,7 +7236,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7241,12 +7246,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran (ca 170 år gammal) i gammal granskog</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7261,12 +7261,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -8846,10 +8846,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124259759</v>
+        <v>124263103</v>
       </c>
       <c r="B66" t="n">
-        <v>77743</v>
+        <v>79891</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8862,21 +8862,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8886,13 +8886,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>461789</v>
+        <v>461643</v>
       </c>
       <c r="R66" t="n">
-        <v>7050616</v>
+        <v>7050590</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8931,12 +8931,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På gammal gran ca 5 m från bäck i äldre granskog</t>
+          <t>På gammal rönn I gammal granskog</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8951,22 +8951,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124263103</v>
+        <v>124259759</v>
       </c>
       <c r="B67" t="n">
-        <v>79891</v>
+        <v>77743</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8979,21 +8979,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -9003,13 +9003,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461643</v>
+        <v>461789</v>
       </c>
       <c r="R67" t="n">
-        <v>7050590</v>
+        <v>7050616</v>
       </c>
       <c r="S67" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9048,12 +9048,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>På gammal rönn I gammal granskog</t>
+          <t>På gammal gran ca 5 m från bäck i äldre granskog</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9068,12 +9068,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -11602,10 +11602,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124261626</v>
+        <v>124260158</v>
       </c>
       <c r="B88" t="n">
-        <v>56714</v>
+        <v>79891</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11618,42 +11618,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>461768</v>
+        <v>461793</v>
       </c>
       <c r="R88" t="n">
-        <v>7050794</v>
+        <v>7050683</v>
       </c>
       <c r="S88" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11682,7 +11677,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11692,7 +11687,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>På bark på död rönnstubbe</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11703,31 +11703,26 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124260158</v>
+        <v>124261626</v>
       </c>
       <c r="B89" t="n">
-        <v>79891</v>
+        <v>56714</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11740,37 +11735,42 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>461793</v>
+        <v>461768</v>
       </c>
       <c r="R89" t="n">
-        <v>7050683</v>
+        <v>7050794</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11809,12 +11809,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>På bark på död rönnstubbe</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11825,16 +11820,21 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>

--- a/artfynd/A 12479-2025 artfynd.xlsx
+++ b/artfynd/A 12479-2025 artfynd.xlsx
@@ -3794,10 +3794,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124262044</v>
+        <v>124262725</v>
       </c>
       <c r="B25" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3810,21 +3810,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3834,10 +3834,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461724</v>
+        <v>461642</v>
       </c>
       <c r="R25" t="n">
-        <v>7050772</v>
+        <v>7050696</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (28 cm dbh) i gammal granskog</t>
+          <t>På gammal gran i gammal fuktig granskog nära bäck</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3911,10 +3911,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124262725</v>
+        <v>124260468</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3927,21 +3927,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461642</v>
+        <v>461783</v>
       </c>
       <c r="R26" t="n">
-        <v>7050696</v>
+        <v>7050722</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal fuktig granskog nära bäck</t>
+          <t>På bark på stam av levande gammal gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4028,10 +4028,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124260468</v>
+        <v>124260115</v>
       </c>
       <c r="B27" t="n">
-        <v>74901</v>
+        <v>100279</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4040,41 +4040,46 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461783</v>
+        <v>461636</v>
       </c>
       <c r="R27" t="n">
-        <v>7050722</v>
+        <v>7050841</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4103,7 +4108,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4113,12 +4118,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal fuktig granskog</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4129,26 +4129,31 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124260115</v>
+        <v>124262044</v>
       </c>
       <c r="B28" t="n">
-        <v>100279</v>
+        <v>77743</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4157,46 +4162,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>228579</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461636</v>
+        <v>461724</v>
       </c>
       <c r="R28" t="n">
-        <v>7050841</v>
+        <v>7050772</v>
       </c>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4235,7 +4235,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran (28 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4246,21 +4251,16 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -5146,10 +5146,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124259895</v>
+        <v>124261248</v>
       </c>
       <c r="B36" t="n">
-        <v>74893</v>
+        <v>91030</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5162,37 +5162,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>308</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461797</v>
+        <v>461756</v>
       </c>
       <c r="R36" t="n">
-        <v>7050670</v>
+        <v>7050765</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5221,7 +5221,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5231,12 +5231,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Rikligt på ved på basen av granhögstubbe i fuktig gammal granskog</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5251,22 +5246,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Emil Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124262970</v>
+        <v>124261167</v>
       </c>
       <c r="B37" t="n">
-        <v>79892</v>
+        <v>74901</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5279,37 +5274,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461598</v>
+        <v>461741</v>
       </c>
       <c r="R37" t="n">
-        <v>7050665</v>
+        <v>7050704</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5338,7 +5333,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5348,12 +5343,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Enstaka på en flerstammig sälg.</t>
+          <t>På gammal gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5364,51 +5359,26 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin, Emil Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124261248</v>
+        <v>124260873</v>
       </c>
       <c r="B38" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5421,37 +5391,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461756</v>
+        <v>461744</v>
       </c>
       <c r="R38" t="n">
-        <v>7050765</v>
+        <v>7050919</v>
       </c>
       <c r="S38" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5480,7 +5450,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5490,7 +5460,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5501,26 +5471,51 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Emil Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124261167</v>
+        <v>124259426</v>
       </c>
       <c r="B39" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5533,37 +5528,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461741</v>
+        <v>461787</v>
       </c>
       <c r="R39" t="n">
-        <v>7050704</v>
+        <v>7050628</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5592,7 +5587,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5602,12 +5597,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:48</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På gammal gran i gransumpskog</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5622,22 +5612,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Emil Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124260873</v>
+        <v>124259895</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>74893</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5650,21 +5640,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5674,13 +5664,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461744</v>
+        <v>461797</v>
       </c>
       <c r="R40" t="n">
-        <v>7050919</v>
+        <v>7050670</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5709,7 +5699,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5719,7 +5709,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Rikligt på ved på basen av granhögstubbe i fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5730,51 +5725,26 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124259426</v>
+        <v>124262970</v>
       </c>
       <c r="B41" t="n">
-        <v>77743</v>
+        <v>79892</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5787,34 +5757,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461787</v>
+        <v>461598</v>
       </c>
       <c r="R41" t="n">
-        <v>7050628</v>
+        <v>7050665</v>
       </c>
       <c r="S41" t="n">
         <v>9</v>
@@ -5846,7 +5816,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5856,7 +5826,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Enstaka på en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5867,16 +5842,41 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6927,10 +6927,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124261213</v>
+        <v>124260536</v>
       </c>
       <c r="B50" t="n">
-        <v>77743</v>
+        <v>100279</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6939,41 +6939,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228579</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>461731</v>
+        <v>461834</v>
       </c>
       <c r="R50" t="n">
-        <v>7050704</v>
+        <v>7050707</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7012,12 +7012,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:48</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På gammal gran i gransumpskog</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7032,19 +7027,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124262908</v>
+        <v>124261213</v>
       </c>
       <c r="B51" t="n">
         <v>77743</v>
@@ -7084,10 +7079,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461633</v>
+        <v>461731</v>
       </c>
       <c r="R51" t="n">
-        <v>7050666</v>
+        <v>7050704</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7119,7 +7114,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7129,12 +7124,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (ca 170 år gammal) i gammal granskog</t>
+          <t>På gammal gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7149,22 +7144,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124260536</v>
+        <v>124262908</v>
       </c>
       <c r="B52" t="n">
-        <v>100279</v>
+        <v>77743</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7173,41 +7168,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>228579</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461834</v>
+        <v>461633</v>
       </c>
       <c r="R52" t="n">
-        <v>7050707</v>
+        <v>7050666</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7236,7 +7231,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7246,7 +7241,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran (ca 170 år gammal) i gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7261,12 +7261,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -8117,10 +8117,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124262760</v>
+        <v>124260631</v>
       </c>
       <c r="B60" t="n">
-        <v>57883</v>
+        <v>74901</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8129,50 +8129,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103015</v>
+        <v>6440</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461558</v>
+        <v>461864</v>
       </c>
       <c r="R60" t="n">
-        <v>7050692</v>
+        <v>7050679</v>
       </c>
       <c r="S60" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8201,7 +8192,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8211,7 +8202,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8359,10 +8350,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124260631</v>
+        <v>124262760</v>
       </c>
       <c r="B62" t="n">
-        <v>74901</v>
+        <v>57883</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8371,41 +8362,50 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6440</v>
+        <v>103015</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461864</v>
+        <v>461558</v>
       </c>
       <c r="R62" t="n">
-        <v>7050679</v>
+        <v>7050692</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8444,7 +8444,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8846,10 +8846,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124263103</v>
+        <v>124259759</v>
       </c>
       <c r="B66" t="n">
-        <v>79891</v>
+        <v>77743</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8862,21 +8862,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8886,13 +8886,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>461643</v>
+        <v>461789</v>
       </c>
       <c r="R66" t="n">
-        <v>7050590</v>
+        <v>7050616</v>
       </c>
       <c r="S66" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8931,12 +8931,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På gammal rönn I gammal granskog</t>
+          <t>På gammal gran ca 5 m från bäck i äldre granskog</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8951,22 +8951,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124259759</v>
+        <v>124263103</v>
       </c>
       <c r="B67" t="n">
-        <v>77743</v>
+        <v>79891</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8979,21 +8979,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -9003,13 +9003,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461789</v>
+        <v>461643</v>
       </c>
       <c r="R67" t="n">
-        <v>7050616</v>
+        <v>7050590</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9048,12 +9048,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>På gammal gran ca 5 m från bäck i äldre granskog</t>
+          <t>På gammal rönn I gammal granskog</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9068,22 +9068,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124262454</v>
+        <v>124260702</v>
       </c>
       <c r="B68" t="n">
-        <v>79891</v>
+        <v>100279</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9092,41 +9092,46 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>461608</v>
+        <v>461678</v>
       </c>
       <c r="R68" t="n">
-        <v>7050779</v>
+        <v>7050823</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9155,7 +9160,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9165,12 +9170,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en skadad rönn.</t>
+          <t>Både blåvioletta och vita blommor.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9185,26 +9190,6 @@
       <c r="AH68" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9222,10 +9207,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124262595</v>
+        <v>124262198</v>
       </c>
       <c r="B69" t="n">
-        <v>78810</v>
+        <v>105102</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9234,25 +9219,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9262,13 +9247,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>461615</v>
+        <v>461687</v>
       </c>
       <c r="R69" t="n">
-        <v>7050725</v>
+        <v>7050752</v>
       </c>
       <c r="S69" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9297,7 +9282,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9307,7 +9292,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På marken i fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9318,51 +9308,26 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124259184</v>
+        <v>124262353</v>
       </c>
       <c r="B70" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9375,21 +9340,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9399,10 +9364,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>461677</v>
+        <v>461655</v>
       </c>
       <c r="R70" t="n">
-        <v>7050616</v>
+        <v>7050759</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9434,7 +9399,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9444,12 +9409,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På död gran i sumpgranskog</t>
+          <t>På gran ca 40 cm i diameter intill bäck</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9476,10 +9441,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124241603</v>
+        <v>124263837</v>
       </c>
       <c r="B71" t="n">
-        <v>98101</v>
+        <v>77743</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9488,52 +9453,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>461712</v>
+        <v>461549</v>
       </c>
       <c r="R71" t="n">
-        <v>7050513</v>
+        <v>7050671</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9560,27 +9511,27 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Minst 78 plantor och 3 vinterståndare inom ca 1 m2 i gammal granskog.</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9591,28 +9542,23 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124264003</v>
+        <v>124241603</v>
       </c>
       <c r="B72" t="n">
         <v>98101</v>
@@ -9647,7 +9593,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>78</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9660,24 +9606,19 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>461546</v>
+        <v>461712</v>
       </c>
       <c r="R72" t="n">
-        <v>7050666</v>
+        <v>7050513</v>
       </c>
       <c r="S72" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9701,27 +9642,27 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Minst 51 plantor inom ca 2 m2 i gammal granskog.</t>
+          <t>Minst 78 plantor och 3 vinterståndare inom ca 1 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9753,10 +9694,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124262353</v>
+        <v>124262454</v>
       </c>
       <c r="B73" t="n">
-        <v>77743</v>
+        <v>79891</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9769,21 +9710,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9793,10 +9734,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>461655</v>
+        <v>461608</v>
       </c>
       <c r="R73" t="n">
-        <v>7050759</v>
+        <v>7050779</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9828,7 +9769,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9838,12 +9779,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På gran ca 40 cm i diameter intill bäck</t>
+          <t>Enstaka bålar på en skadad rönn.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9854,26 +9795,51 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124263837</v>
+        <v>124262595</v>
       </c>
       <c r="B74" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9886,21 +9852,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9910,13 +9876,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>461549</v>
+        <v>461615</v>
       </c>
       <c r="R74" t="n">
-        <v>7050671</v>
+        <v>7050725</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9945,7 +9911,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9955,12 +9921,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:16</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9971,26 +9932,51 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124261426</v>
+        <v>124259184</v>
       </c>
       <c r="B75" t="n">
-        <v>78891</v>
+        <v>74901</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10003,21 +9989,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>283</v>
+        <v>6440</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -10027,10 +10013,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>461715</v>
+        <v>461677</v>
       </c>
       <c r="R75" t="n">
-        <v>7050700</v>
+        <v>7050616</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10062,7 +10048,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10072,12 +10058,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>På kvist på klen gran i gransumpskog</t>
+          <t>På död gran i sumpgranskog</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10104,10 +10090,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124263225</v>
+        <v>124261426</v>
       </c>
       <c r="B76" t="n">
-        <v>91012</v>
+        <v>78891</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10120,21 +10106,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -10144,10 +10130,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>461603</v>
+        <v>461715</v>
       </c>
       <c r="R76" t="n">
-        <v>7050578</v>
+        <v>7050700</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10179,7 +10165,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10189,12 +10175,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På kvist på klen gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10209,22 +10195,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124260702</v>
+        <v>124263225</v>
       </c>
       <c r="B77" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10233,46 +10219,41 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>461678</v>
+        <v>461603</v>
       </c>
       <c r="R77" t="n">
-        <v>7050823</v>
+        <v>7050578</v>
       </c>
       <c r="S77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10301,7 +10282,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10311,12 +10292,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Både blåvioletta och vita blommor.</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10327,31 +10308,26 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124262198</v>
+        <v>124264003</v>
       </c>
       <c r="B78" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10360,41 +10336,60 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>461687</v>
+        <v>461546</v>
       </c>
       <c r="R78" t="n">
-        <v>7050752</v>
+        <v>7050666</v>
       </c>
       <c r="S78" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10423,7 +10418,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10433,12 +10428,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På marken i fuktig gammal granskog</t>
+          <t>Minst 51 plantor inom ca 2 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10449,16 +10444,21 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>

--- a/artfynd/A 12479-2025 artfynd.xlsx
+++ b/artfynd/A 12479-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124243366</v>
+        <v>124244006</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461694</v>
+        <v>461840</v>
       </c>
       <c r="R2" t="n">
-        <v>7050529</v>
+        <v>7050563</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i en murken granhögstubbe.</t>
+          <t>Enstaka på en grov sälglåga.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,22 +784,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -822,10 +817,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124244822</v>
+        <v>124243782</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>95335</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -834,46 +829,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461680</v>
+        <v>461757</v>
       </c>
       <c r="R3" t="n">
-        <v>7050615</v>
+        <v>7050561</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -902,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -912,7 +902,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Vid en bäck i gammal granskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,26 +922,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -964,10 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124244006</v>
+        <v>124244983</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -980,37 +955,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461840</v>
+        <v>461652</v>
       </c>
       <c r="R4" t="n">
-        <v>7050563</v>
+        <v>7050519</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1039,7 +1014,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1049,12 +1024,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:24</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Enstaka på en grov sälglåga.</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1073,22 +1043,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1106,10 +1076,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124241982</v>
+        <v>124243996</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>79927</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1118,41 +1088,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461758</v>
+        <v>461837</v>
       </c>
       <c r="R5" t="n">
-        <v>7050534</v>
+        <v>7050572</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1181,7 +1156,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1191,12 +1166,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På en sälglåga.</t>
+          <t>På en grov sälglåga.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1248,10 +1223,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124243996</v>
+        <v>124242253</v>
       </c>
       <c r="B6" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1260,46 +1235,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461837</v>
+        <v>461780</v>
       </c>
       <c r="R6" t="n">
-        <v>7050572</v>
+        <v>7050582</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1328,7 +1298,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1338,12 +1308,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På en grov sälglåga.</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1362,22 +1327,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1395,10 +1360,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124244322</v>
+        <v>124243366</v>
       </c>
       <c r="B7" t="n">
-        <v>100279</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1407,46 +1372,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461935</v>
+        <v>461694</v>
       </c>
       <c r="R7" t="n">
-        <v>7050570</v>
+        <v>7050529</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1475,7 +1440,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1485,7 +1450,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i en murken granhögstubbe.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1500,6 +1470,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1517,10 +1507,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124243782</v>
+        <v>124241982</v>
       </c>
       <c r="B8" t="n">
-        <v>95335</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1529,25 +1519,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2809</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1557,13 +1547,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461757</v>
+        <v>461758</v>
       </c>
       <c r="R8" t="n">
-        <v>7050561</v>
+        <v>7050534</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1592,7 +1582,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1602,12 +1592,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Vid en bäck i gammal granskog.</t>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1622,6 +1612,26 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1781,10 +1791,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124241219</v>
+        <v>124244069</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1793,41 +1803,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461671</v>
+        <v>461842</v>
       </c>
       <c r="R10" t="n">
-        <v>7050487</v>
+        <v>7050570</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1856,7 +1871,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1866,7 +1881,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På en grov sälglåga.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1885,22 +1905,22 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1918,10 +1938,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124244443</v>
+        <v>124244357</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1930,38 +1950,52 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461867</v>
+        <v>461909</v>
       </c>
       <c r="R11" t="n">
-        <v>7050617</v>
+        <v>7050579</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1993,7 +2027,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2003,12 +2037,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>I flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2023,26 +2057,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2060,7 +2074,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124242084</v>
+        <v>124244443</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -2100,13 +2114,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461835</v>
+        <v>461867</v>
       </c>
       <c r="R12" t="n">
-        <v>7050524</v>
+        <v>7050617</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2135,7 +2149,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2145,7 +2159,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2174,12 +2193,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2197,7 +2216,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124242253</v>
+        <v>124242084</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -2237,13 +2256,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461780</v>
+        <v>461835</v>
       </c>
       <c r="R13" t="n">
-        <v>7050582</v>
+        <v>7050524</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2272,7 +2291,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2282,7 +2301,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2334,7 +2353,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124244983</v>
+        <v>124241219</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -2374,10 +2393,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461652</v>
+        <v>461671</v>
       </c>
       <c r="R14" t="n">
-        <v>7050519</v>
+        <v>7050487</v>
       </c>
       <c r="S14" t="n">
         <v>7</v>
@@ -2409,7 +2428,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2419,7 +2438,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2471,10 +2490,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124244069</v>
+        <v>124244322</v>
       </c>
       <c r="B15" t="n">
-        <v>79920</v>
+        <v>100279</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2487,27 +2506,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2516,13 +2535,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461842</v>
+        <v>461935</v>
       </c>
       <c r="R15" t="n">
         <v>7050570</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2551,7 +2570,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2561,12 +2580,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:26</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På en grov sälglåga.</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2581,26 +2595,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2618,10 +2612,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124244357</v>
+        <v>124244822</v>
       </c>
       <c r="B16" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2630,52 +2624,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461909</v>
+        <v>461680</v>
       </c>
       <c r="R16" t="n">
-        <v>7050579</v>
+        <v>7050615</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
@@ -2707,7 +2692,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2717,12 +2702,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:37</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>I flerskiktad äldre granskog.</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2737,6 +2717,26 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2754,10 +2754,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124259251</v>
+        <v>124262807</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>74901</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2766,50 +2766,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461721</v>
+        <v>461633</v>
       </c>
       <c r="R17" t="n">
-        <v>7050576</v>
+        <v>7050701</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2838,7 +2829,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2848,12 +2839,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Inom en yta på 3x7m</t>
+          <t>På gammal gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2868,22 +2859,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124263802</v>
+        <v>124259378</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2892,41 +2883,46 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461536</v>
+        <v>461603</v>
       </c>
       <c r="R18" t="n">
-        <v>7050642</v>
+        <v>7050832</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2955,7 +2951,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2965,12 +2961,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ca 40 ex inom en kvadratmeter</t>
+          <t>Ymnigt med lunglav på en gammal grov sälg. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2981,26 +2977,51 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124259289</v>
+        <v>124258793</v>
       </c>
       <c r="B19" t="n">
-        <v>95347</v>
+        <v>95335</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3013,21 +3034,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2813</v>
+        <v>2809</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -3037,10 +3058,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461716</v>
+        <v>461641</v>
       </c>
       <c r="R19" t="n">
-        <v>7050630</v>
+        <v>7050551</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3072,7 +3093,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3082,12 +3103,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På marken i gammal sumpgranskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3114,10 +3135,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124261741</v>
+        <v>124264003</v>
       </c>
       <c r="B20" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3126,41 +3147,60 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461728</v>
+        <v>461546</v>
       </c>
       <c r="R20" t="n">
-        <v>7050768</v>
+        <v>7050666</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3189,7 +3229,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3199,12 +3239,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>Minst 51 plantor inom ca 2 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3215,26 +3255,31 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124260090</v>
+        <v>124262198</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>105102</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3243,25 +3288,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3271,13 +3316,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461642</v>
+        <v>461687</v>
       </c>
       <c r="R21" t="n">
-        <v>7050845</v>
+        <v>7050752</v>
       </c>
       <c r="S21" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3306,7 +3351,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3316,7 +3361,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På marken i fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3327,48 +3377,23 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124259169</v>
+        <v>124264084</v>
       </c>
       <c r="B22" t="n">
         <v>78810</v>
@@ -3404,17 +3429,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461539</v>
+        <v>461561</v>
       </c>
       <c r="R22" t="n">
-        <v>7050804</v>
+        <v>7050657</v>
       </c>
       <c r="S22" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3443,7 +3468,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3453,7 +3478,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3505,10 +3530,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124259378</v>
+        <v>124262979</v>
       </c>
       <c r="B23" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3521,42 +3546,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461603</v>
+        <v>461543</v>
       </c>
       <c r="R23" t="n">
-        <v>7050832</v>
+        <v>7050645</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3585,7 +3610,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3595,12 +3620,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglav på en gammal grov sälg. Vissa bålar är fertila med apothecier.</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3611,51 +3636,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124263001</v>
+        <v>124261426</v>
       </c>
       <c r="B24" t="n">
-        <v>79920</v>
+        <v>78891</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3664,43 +3664,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461597</v>
+        <v>461715</v>
       </c>
       <c r="R24" t="n">
-        <v>7050664</v>
+        <v>7050700</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3732,7 +3727,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3742,7 +3737,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På kvist på klen gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3753,51 +3753,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124262725</v>
+        <v>124262044</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3810,21 +3785,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3834,10 +3809,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461642</v>
+        <v>461724</v>
       </c>
       <c r="R25" t="n">
-        <v>7050696</v>
+        <v>7050772</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3869,7 +3844,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3879,12 +3854,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal fuktig granskog nära bäck</t>
+          <t>På bark på stam av levande gammal gran (28 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3911,7 +3886,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124260468</v>
+        <v>124262878</v>
       </c>
       <c r="B26" t="n">
         <v>74901</v>
@@ -3951,10 +3926,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461783</v>
+        <v>461633</v>
       </c>
       <c r="R26" t="n">
-        <v>7050722</v>
+        <v>7050666</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3986,7 +3961,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3996,12 +3971,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal fuktig granskog</t>
+          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 170 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4028,10 +4003,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124260115</v>
+        <v>124260993</v>
       </c>
       <c r="B27" t="n">
-        <v>100279</v>
+        <v>57529</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4040,43 +4015,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Småfloarna, Småfloarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461636</v>
+        <v>461776</v>
       </c>
       <c r="R27" t="n">
-        <v>7050841</v>
+        <v>7050859</v>
       </c>
       <c r="S27" t="n">
         <v>11</v>
@@ -4108,7 +4083,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4118,7 +4093,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4133,6 +4113,26 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4150,7 +4150,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124262044</v>
+        <v>124263170</v>
       </c>
       <c r="B28" t="n">
         <v>77743</v>
@@ -4190,10 +4190,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461724</v>
+        <v>461624</v>
       </c>
       <c r="R28" t="n">
-        <v>7050772</v>
+        <v>7050624</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (28 cm dbh) i gammal granskog</t>
+          <t>På gammal gran i fuktig äldre granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4255,22 +4255,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124259967</v>
+        <v>124263225</v>
       </c>
       <c r="B29" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4283,39 +4283,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461623</v>
+        <v>461603</v>
       </c>
       <c r="R29" t="n">
-        <v>7050871</v>
+        <v>7050578</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4347,7 +4342,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4357,12 +4352,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rikligt på en skadad rönn.</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4373,51 +4368,26 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124260947</v>
+        <v>124262526</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4426,25 +4396,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4454,10 +4424,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461749</v>
+        <v>461665</v>
       </c>
       <c r="R30" t="n">
-        <v>7050709</v>
+        <v>7050738</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4489,7 +4459,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4499,7 +4469,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På död rönn intill bäck</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4514,22 +4489,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124263059</v>
+        <v>124260205</v>
       </c>
       <c r="B31" t="n">
-        <v>74901</v>
+        <v>79920</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4538,25 +4513,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4566,10 +4541,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461654</v>
+        <v>461793</v>
       </c>
       <c r="R31" t="n">
-        <v>7050616</v>
+        <v>7050683</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4601,7 +4576,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4611,12 +4586,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På bark på rönnhögststubbe i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4643,10 +4618,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124262632</v>
+        <v>124261626</v>
       </c>
       <c r="B32" t="n">
-        <v>79857</v>
+        <v>56714</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4655,41 +4630,46 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229748</v>
+        <v>102612</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461651</v>
+        <v>461768</v>
       </c>
       <c r="R32" t="n">
-        <v>7050724</v>
+        <v>7050794</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4718,7 +4698,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4728,12 +4708,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:35</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På rönn vid bäck i gammal granskog</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4744,26 +4719,31 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124261793</v>
+        <v>124263837</v>
       </c>
       <c r="B33" t="n">
-        <v>57529</v>
+        <v>77743</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4776,42 +4756,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>228579</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461776</v>
+        <v>461549</v>
       </c>
       <c r="R33" t="n">
-        <v>7050867</v>
+        <v>7050671</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4840,7 +4815,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4850,12 +4825,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Letade efter hästmyra</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4870,19 +4845,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>August Nordin, Ludvig Nordin, Emil Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124260479</v>
+        <v>124259877</v>
       </c>
       <c r="B34" t="n">
         <v>79891</v>
@@ -4918,7 +4893,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4927,10 +4902,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461666</v>
+        <v>461614</v>
       </c>
       <c r="R34" t="n">
-        <v>7050837</v>
+        <v>7050862</v>
       </c>
       <c r="S34" t="n">
         <v>9</v>
@@ -4962,7 +4937,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4972,12 +4947,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns intill en bäck i gammal högväxt granskog.</t>
+          <t>Ymnig påväxt på en grov gammal sälg där vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4996,12 +4971,12 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
@@ -5011,7 +4986,7 @@
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5029,10 +5004,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124263852</v>
+        <v>124263649</v>
       </c>
       <c r="B35" t="n">
-        <v>74901</v>
+        <v>79920</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5041,25 +5016,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -5069,10 +5044,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461549</v>
+        <v>461556</v>
       </c>
       <c r="R35" t="n">
-        <v>7050671</v>
+        <v>7050632</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5104,7 +5079,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5114,12 +5089,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På gammal grov sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5139,17 +5114,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124261248</v>
+        <v>124262970</v>
       </c>
       <c r="B36" t="n">
-        <v>91030</v>
+        <v>79892</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5162,37 +5137,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461756</v>
+        <v>461598</v>
       </c>
       <c r="R36" t="n">
-        <v>7050765</v>
+        <v>7050665</v>
       </c>
       <c r="S36" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5221,7 +5196,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5231,7 +5206,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Enstaka på en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5242,26 +5222,51 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Emil Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124261167</v>
+        <v>124260947</v>
       </c>
       <c r="B37" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5274,21 +5279,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5298,10 +5303,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461741</v>
+        <v>461749</v>
       </c>
       <c r="R37" t="n">
-        <v>7050704</v>
+        <v>7050709</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5333,7 +5338,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5343,12 +5348,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:48</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På gammal gran i gransumpskog</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5363,22 +5363,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Emil Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124260873</v>
+        <v>124260631</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5391,37 +5391,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461744</v>
+        <v>461864</v>
       </c>
       <c r="R38" t="n">
-        <v>7050919</v>
+        <v>7050679</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5471,51 +5471,26 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124259426</v>
+        <v>124261167</v>
       </c>
       <c r="B39" t="n">
-        <v>77743</v>
+        <v>74901</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5528,37 +5503,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461787</v>
+        <v>461741</v>
       </c>
       <c r="R39" t="n">
-        <v>7050628</v>
+        <v>7050704</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5587,7 +5562,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5597,7 +5572,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På gammal gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5612,22 +5592,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin, Emil Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124259895</v>
+        <v>124261213</v>
       </c>
       <c r="B40" t="n">
-        <v>74893</v>
+        <v>77743</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5640,21 +5620,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>308</v>
+        <v>228579</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5664,10 +5644,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461797</v>
+        <v>461731</v>
       </c>
       <c r="R40" t="n">
-        <v>7050670</v>
+        <v>7050704</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5699,7 +5679,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5709,12 +5689,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Rikligt på ved på basen av granhögstubbe i fuktig gammal granskog</t>
+          <t>På gammal gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5729,22 +5709,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124262970</v>
+        <v>124260054</v>
       </c>
       <c r="B41" t="n">
-        <v>79892</v>
+        <v>96979</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5753,38 +5733,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461598</v>
+        <v>461843</v>
       </c>
       <c r="R41" t="n">
-        <v>7050665</v>
+        <v>7050661</v>
       </c>
       <c r="S41" t="n">
         <v>9</v>
@@ -5816,7 +5796,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5826,12 +5806,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Enstaka på en flerstammig sälg.</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5842,51 +5817,26 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124260054</v>
+        <v>124260115</v>
       </c>
       <c r="B42" t="n">
-        <v>96979</v>
+        <v>100279</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5899,37 +5849,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461843</v>
+        <v>461636</v>
       </c>
       <c r="R42" t="n">
-        <v>7050661</v>
+        <v>7050841</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5958,7 +5913,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5968,7 +5923,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5979,26 +5934,31 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Emil Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124261077</v>
+        <v>124259895</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>74893</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6011,21 +5971,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -6035,10 +5995,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461731</v>
+        <v>461797</v>
       </c>
       <c r="R43" t="n">
-        <v>7050711</v>
+        <v>7050670</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6070,7 +6030,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6080,12 +6040,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal fuktig granskog</t>
+          <t>Rikligt på ved på basen av granhögstubbe i fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6112,14 +6072,14 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124263536</v>
+        <v>124258987</v>
       </c>
       <c r="B44" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6128,42 +6088,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461544</v>
+        <v>461689</v>
       </c>
       <c r="R44" t="n">
-        <v>7050635</v>
+        <v>7050585</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6192,7 +6147,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6202,12 +6157,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6227,17 +6182,17 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124263132</v>
+        <v>124263103</v>
       </c>
       <c r="B45" t="n">
-        <v>91030</v>
+        <v>79891</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6250,48 +6205,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461570</v>
+        <v>461643</v>
       </c>
       <c r="R45" t="n">
-        <v>7050652</v>
+        <v>7050590</v>
       </c>
       <c r="S45" t="n">
         <v>8</v>
@@ -6323,7 +6264,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6333,12 +6274,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i en grov gran.</t>
+          <t>På gammal rönn I gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6349,51 +6290,26 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124260773</v>
+        <v>124262353</v>
       </c>
       <c r="B46" t="n">
-        <v>91673</v>
+        <v>77743</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6402,43 +6318,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>898</v>
+        <v>228579</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461785</v>
+        <v>461655</v>
       </c>
       <c r="R46" t="n">
-        <v>7050704</v>
+        <v>7050759</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6470,7 +6381,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6480,12 +6391,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gammal ullticka på granlåga i bördig, fuktig lågarik granskog</t>
+          <t>På gran ca 40 cm i diameter intill bäck</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6496,41 +6407,26 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124262807</v>
+        <v>124260702</v>
       </c>
       <c r="B47" t="n">
-        <v>74901</v>
+        <v>100279</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6539,41 +6435,46 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6440</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461633</v>
+        <v>461678</v>
       </c>
       <c r="R47" t="n">
-        <v>7050701</v>
+        <v>7050823</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6602,7 +6503,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6612,12 +6513,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gammal gran i gransumpskog</t>
+          <t>Både blåvioletta och vita blommor.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6628,26 +6529,31 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124262686</v>
+        <v>124263675</v>
       </c>
       <c r="B48" t="n">
-        <v>79920</v>
+        <v>79892</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6656,46 +6562,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461617</v>
+        <v>461551</v>
       </c>
       <c r="R48" t="n">
-        <v>7050728</v>
+        <v>7050634</v>
       </c>
       <c r="S48" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6724,7 +6625,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6734,7 +6635,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På sälg ca 60 cm i diameter</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6745,51 +6651,26 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124258944</v>
+        <v>124263257</v>
       </c>
       <c r="B49" t="n">
-        <v>57883</v>
+        <v>57529</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6798,20 +6679,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -6824,34 +6705,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M49" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>461559</v>
+        <v>461584</v>
       </c>
       <c r="R49" t="n">
-        <v>7050789</v>
+        <v>7050588</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6880,7 +6751,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6890,12 +6761,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6906,31 +6772,26 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124260536</v>
+        <v>124263132</v>
       </c>
       <c r="B50" t="n">
-        <v>100279</v>
+        <v>91030</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6939,41 +6800,55 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>461834</v>
+        <v>461570</v>
       </c>
       <c r="R50" t="n">
-        <v>7050707</v>
+        <v>7050652</v>
       </c>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7002,7 +6877,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7012,7 +6887,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rikligt med fruktkroppar i en grov gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7023,26 +6903,51 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124261213</v>
+        <v>124262035</v>
       </c>
       <c r="B51" t="n">
-        <v>77743</v>
+        <v>79891</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7055,37 +6960,46 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461731</v>
+        <v>461712</v>
       </c>
       <c r="R51" t="n">
-        <v>7050704</v>
+        <v>7050901</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7114,7 +7028,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7124,12 +7038,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På gammal gran i gransumpskog</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7144,22 +7058,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124262908</v>
+        <v>124261077</v>
       </c>
       <c r="B52" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7172,21 +7086,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -7196,10 +7110,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461633</v>
+        <v>461731</v>
       </c>
       <c r="R52" t="n">
-        <v>7050666</v>
+        <v>7050711</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7231,7 +7145,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7241,12 +7155,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (ca 170 år gammal) i gammal granskog</t>
+          <t>På gammal gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7273,10 +7187,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124258987</v>
+        <v>124263059</v>
       </c>
       <c r="B53" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7289,21 +7203,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7313,10 +7227,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461689</v>
+        <v>461654</v>
       </c>
       <c r="R53" t="n">
-        <v>7050585</v>
+        <v>7050616</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7348,7 +7262,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7358,12 +7272,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7390,10 +7304,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124263250</v>
+        <v>124260468</v>
       </c>
       <c r="B54" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7406,21 +7320,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7430,10 +7344,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>461629</v>
+        <v>461783</v>
       </c>
       <c r="R54" t="n">
-        <v>7050621</v>
+        <v>7050722</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7465,7 +7379,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7475,12 +7389,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ett 100-tal bålar på ett 10-tal granar</t>
+          <t>På bark på stam av levande gammal gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7495,22 +7409,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124260175</v>
+        <v>124263066</v>
       </c>
       <c r="B55" t="n">
-        <v>74885</v>
+        <v>77743</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7519,25 +7433,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6439</v>
+        <v>228579</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7547,10 +7461,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>461793</v>
+        <v>461654</v>
       </c>
       <c r="R55" t="n">
-        <v>7050683</v>
+        <v>7050616</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7582,7 +7496,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7592,12 +7506,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På ved på rönnhögstubbe i gammal fuktig granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7624,10 +7538,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124262878</v>
+        <v>124262632</v>
       </c>
       <c r="B56" t="n">
-        <v>74901</v>
+        <v>79857</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7636,25 +7550,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6440</v>
+        <v>229748</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7664,10 +7578,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461633</v>
+        <v>461651</v>
       </c>
       <c r="R56" t="n">
-        <v>7050666</v>
+        <v>7050724</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7699,7 +7613,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7709,12 +7623,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 170 år) i gammal granskog</t>
+          <t>På rönn vid bäck i gammal granskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7741,10 +7655,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124259877</v>
+        <v>124260536</v>
       </c>
       <c r="B57" t="n">
-        <v>79891</v>
+        <v>100279</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7753,43 +7667,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461614</v>
+        <v>461834</v>
       </c>
       <c r="R57" t="n">
-        <v>7050862</v>
+        <v>7050707</v>
       </c>
       <c r="S57" t="n">
         <v>9</v>
@@ -7821,7 +7730,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7831,12 +7740,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ymnig påväxt på en grov gammal sälg där vissa bålar är fertila med apothecier.</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7847,51 +7751,26 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124261849</v>
+        <v>124259759</v>
       </c>
       <c r="B58" t="n">
-        <v>78891</v>
+        <v>77743</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7904,21 +7783,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>283</v>
+        <v>228579</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7928,10 +7807,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461733</v>
+        <v>461789</v>
       </c>
       <c r="R58" t="n">
-        <v>7050778</v>
+        <v>7050616</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7963,7 +7842,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7973,12 +7852,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ett ex på klen gran som saknar topp i äldre granskog</t>
+          <t>På gammal gran ca 5 m från bäck i äldre granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8005,10 +7884,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124263373</v>
+        <v>124262595</v>
       </c>
       <c r="B59" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8021,21 +7900,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -8045,13 +7924,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461587</v>
+        <v>461615</v>
       </c>
       <c r="R59" t="n">
-        <v>7050582</v>
+        <v>7050725</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8080,7 +7959,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8090,7 +7969,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8101,26 +7980,51 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124260631</v>
+        <v>124262725</v>
       </c>
       <c r="B60" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8133,34 +8037,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461864</v>
+        <v>461642</v>
       </c>
       <c r="R60" t="n">
-        <v>7050679</v>
+        <v>7050696</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8192,7 +8096,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8202,7 +8106,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal fuktig granskog nära bäck</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8217,22 +8126,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124263257</v>
+        <v>124262760</v>
       </c>
       <c r="B61" t="n">
-        <v>57529</v>
+        <v>57883</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8241,20 +8150,20 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -8278,13 +8187,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461584</v>
+        <v>461558</v>
       </c>
       <c r="R61" t="n">
-        <v>7050588</v>
+        <v>7050692</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8313,7 +8222,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8323,7 +8232,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8338,22 +8247,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124262760</v>
+        <v>124259426</v>
       </c>
       <c r="B62" t="n">
-        <v>57883</v>
+        <v>77743</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8362,50 +8271,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103015</v>
+        <v>228579</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461558</v>
+        <v>461787</v>
       </c>
       <c r="R62" t="n">
-        <v>7050692</v>
+        <v>7050628</v>
       </c>
       <c r="S62" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8434,7 +8334,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8444,7 +8344,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8464,17 +8364,17 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124260205</v>
+        <v>124260090</v>
       </c>
       <c r="B63" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8483,25 +8383,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8511,13 +8411,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461793</v>
+        <v>461642</v>
       </c>
       <c r="R63" t="n">
-        <v>7050683</v>
+        <v>7050845</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8546,7 +8446,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8556,12 +8456,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>På bark på rönnhögststubbe i gammal fuktig granskog</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8572,26 +8467,51 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124263683</v>
+        <v>124263852</v>
       </c>
       <c r="B64" t="n">
-        <v>98101</v>
+        <v>74901</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8600,60 +8520,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461584</v>
+        <v>461549</v>
       </c>
       <c r="R64" t="n">
-        <v>7050644</v>
+        <v>7050671</v>
       </c>
       <c r="S64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8682,7 +8583,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8692,12 +8593,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Minst 63 plantor inom ca 2 x 1 m2 i gammal granskog.</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8708,31 +8609,26 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124263170</v>
+        <v>124262686</v>
       </c>
       <c r="B65" t="n">
-        <v>77743</v>
+        <v>79920</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8741,41 +8637,46 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228579</v>
+        <v>6462</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>461624</v>
+        <v>461617</v>
       </c>
       <c r="R65" t="n">
-        <v>7050624</v>
+        <v>7050728</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8804,7 +8705,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8814,12 +8715,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>På gammal gran i fuktig äldre granskog</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8830,26 +8726,51 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124259759</v>
+        <v>124259169</v>
       </c>
       <c r="B66" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8862,21 +8783,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8886,13 +8807,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>461789</v>
+        <v>461539</v>
       </c>
       <c r="R66" t="n">
-        <v>7050616</v>
+        <v>7050804</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8934,11 +8855,6 @@
           <t>11:48</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På gammal gran ca 5 m från bäck i äldre granskog</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8947,26 +8863,51 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124263103</v>
+        <v>124259784</v>
       </c>
       <c r="B67" t="n">
-        <v>79891</v>
+        <v>74901</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8979,21 +8920,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -9003,13 +8944,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461643</v>
+        <v>461789</v>
       </c>
       <c r="R67" t="n">
-        <v>7050590</v>
+        <v>7050616</v>
       </c>
       <c r="S67" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9038,7 +8979,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9048,12 +8989,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>På gammal rönn I gammal granskog</t>
+          <t>På gammal gran ca 5m från bäck i äldre granskog</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9068,22 +9009,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124260702</v>
+        <v>124259184</v>
       </c>
       <c r="B68" t="n">
-        <v>100279</v>
+        <v>74901</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9092,46 +9033,41 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>461678</v>
+        <v>461677</v>
       </c>
       <c r="R68" t="n">
-        <v>7050823</v>
+        <v>7050616</v>
       </c>
       <c r="S68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9160,7 +9096,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9170,12 +9106,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Både blåvioletta och vita blommor.</t>
+          <t>På död gran i sumpgranskog</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9186,31 +9122,26 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124262198</v>
+        <v>124260175</v>
       </c>
       <c r="B69" t="n">
-        <v>105102</v>
+        <v>74885</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9223,21 +9154,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221725</v>
+        <v>6439</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9247,13 +9178,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>461687</v>
+        <v>461793</v>
       </c>
       <c r="R69" t="n">
-        <v>7050752</v>
+        <v>7050683</v>
       </c>
       <c r="S69" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9282,7 +9213,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9292,12 +9223,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På marken i fuktig gammal granskog</t>
+          <t>På ved på rönnhögstubbe i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9324,10 +9255,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124262353</v>
+        <v>124259289</v>
       </c>
       <c r="B70" t="n">
-        <v>77743</v>
+        <v>95347</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9336,25 +9267,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228579</v>
+        <v>2813</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9364,10 +9295,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>461655</v>
+        <v>461716</v>
       </c>
       <c r="R70" t="n">
-        <v>7050759</v>
+        <v>7050630</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9399,7 +9330,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9409,12 +9340,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På gran ca 40 cm i diameter intill bäck</t>
+          <t>På marken i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9429,22 +9360,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124263837</v>
+        <v>124259251</v>
       </c>
       <c r="B71" t="n">
-        <v>77743</v>
+        <v>98101</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9453,41 +9384,50 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>461549</v>
+        <v>461721</v>
       </c>
       <c r="R71" t="n">
-        <v>7050671</v>
+        <v>7050576</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9516,7 +9456,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9526,12 +9466,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Inom en yta på 3x7m</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9546,22 +9486,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124241603</v>
+        <v>124258944</v>
       </c>
       <c r="B72" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9570,55 +9510,60 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>461712</v>
+        <v>461559</v>
       </c>
       <c r="R72" t="n">
-        <v>7050513</v>
+        <v>7050789</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9642,27 +9587,27 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Minst 78 plantor och 3 vinterståndare inom ca 1 m2 i gammal granskog.</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9694,10 +9639,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124262454</v>
+        <v>124241603</v>
       </c>
       <c r="B73" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9706,38 +9651,52 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>461608</v>
+        <v>461712</v>
       </c>
       <c r="R73" t="n">
-        <v>7050779</v>
+        <v>7050513</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9764,27 +9723,27 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en skadad rönn.</t>
+          <t>Minst 78 plantor och 3 vinterståndare inom ca 1 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9799,26 +9758,6 @@
       <c r="AH73" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9836,10 +9775,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124262595</v>
+        <v>124260842</v>
       </c>
       <c r="B74" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9852,21 +9791,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9876,13 +9815,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>461615</v>
+        <v>461785</v>
       </c>
       <c r="R74" t="n">
-        <v>7050725</v>
+        <v>7050704</v>
       </c>
       <c r="S74" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9911,7 +9850,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9921,7 +9860,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9932,51 +9876,26 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124259184</v>
+        <v>124262908</v>
       </c>
       <c r="B75" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9989,21 +9908,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -10013,10 +9932,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>461677</v>
+        <v>461633</v>
       </c>
       <c r="R75" t="n">
-        <v>7050616</v>
+        <v>7050666</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10048,7 +9967,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10058,12 +9977,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>På död gran i sumpgranskog</t>
+          <t>På bark på stam av levande gammal gran (ca 170 år gammal) i gammal granskog</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10078,19 +9997,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124261426</v>
+        <v>124259946</v>
       </c>
       <c r="B76" t="n">
         <v>78891</v>
@@ -10130,10 +10049,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>461715</v>
+        <v>461815</v>
       </c>
       <c r="R76" t="n">
-        <v>7050700</v>
+        <v>7050652</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10165,7 +10084,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10175,12 +10094,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>På kvist på klen gran i gransumpskog</t>
+          <t>På tunn levande gren på gammal klen gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10195,22 +10114,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124263225</v>
+        <v>124260773</v>
       </c>
       <c r="B77" t="n">
-        <v>91012</v>
+        <v>91673</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10219,38 +10138,43 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>461603</v>
+        <v>461785</v>
       </c>
       <c r="R77" t="n">
-        <v>7050578</v>
+        <v>7050704</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10282,7 +10206,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10292,12 +10216,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gammal ullticka på granlåga i bördig, fuktig lågarik granskog</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10308,6 +10232,21 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -10324,10 +10263,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124264003</v>
+        <v>124261248</v>
       </c>
       <c r="B78" t="n">
-        <v>98101</v>
+        <v>91030</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10336,60 +10275,41 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>461546</v>
+        <v>461756</v>
       </c>
       <c r="R78" t="n">
-        <v>7050666</v>
+        <v>7050765</v>
       </c>
       <c r="S78" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10418,7 +10338,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10428,12 +10348,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:12</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Minst 51 plantor inom ca 2 m2 i gammal granskog.</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10444,28 +10359,23 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124264084</v>
+        <v>124263250</v>
       </c>
       <c r="B79" t="n">
         <v>78810</v>
@@ -10501,17 +10411,17 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>461561</v>
+        <v>461629</v>
       </c>
       <c r="R79" t="n">
-        <v>7050657</v>
+        <v>7050621</v>
       </c>
       <c r="S79" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10540,7 +10450,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10550,7 +10460,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ett 100-tal bålar på ett 10-tal granar</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10561,51 +10476,26 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124259784</v>
+        <v>124261793</v>
       </c>
       <c r="B80" t="n">
-        <v>74901</v>
+        <v>57529</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10618,37 +10508,42 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>461789</v>
+        <v>461776</v>
       </c>
       <c r="R80" t="n">
-        <v>7050616</v>
+        <v>7050867</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10677,7 +10572,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10687,12 +10582,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På gammal gran ca 5m från bäck i äldre granskog</t>
+          <t>Letade efter hästmyra</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10707,22 +10602,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>August Nordin, Ludvig Nordin, Emil Nordin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124262348</v>
+        <v>124259967</v>
       </c>
       <c r="B81" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10731,38 +10626,43 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>461656</v>
+        <v>461623</v>
       </c>
       <c r="R81" t="n">
-        <v>7050743</v>
+        <v>7050871</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10794,7 +10694,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10804,12 +10704,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På rönn vid bäck</t>
+          <t>Rikligt på en skadad rönn.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10820,26 +10720,51 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124263649</v>
+        <v>124263683</v>
       </c>
       <c r="B82" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10848,41 +10773,60 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>461556</v>
+        <v>461584</v>
       </c>
       <c r="R82" t="n">
-        <v>7050632</v>
+        <v>7050644</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10911,7 +10855,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10921,12 +10865,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På gammal grov sälg i gammal granskog</t>
+          <t>Minst 63 plantor inom ca 2 x 1 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10937,26 +10881,31 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124261471</v>
+        <v>124261849</v>
       </c>
       <c r="B83" t="n">
-        <v>78547</v>
+        <v>78891</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10969,37 +10918,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>461800</v>
+        <v>461733</v>
       </c>
       <c r="R83" t="n">
-        <v>7050827</v>
+        <v>7050778</v>
       </c>
       <c r="S83" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -11028,7 +10977,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11038,12 +10987,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På kolade tallstubbe.</t>
+          <t>Ett ex på klen gran som saknar topp i äldre granskog</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11054,51 +11003,26 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Stump # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124260993</v>
+        <v>124261444</v>
       </c>
       <c r="B84" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11111,42 +11035,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Småfloarna, Småfloarna, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>461776</v>
+        <v>461810</v>
       </c>
       <c r="R84" t="n">
-        <v>7050859</v>
+        <v>7050829</v>
       </c>
       <c r="S84" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11175,7 +11094,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11185,12 +11104,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Rejäla hackspår.</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11201,48 +11120,23 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124261444</v>
+        <v>124260873</v>
       </c>
       <c r="B85" t="n">
         <v>78810</v>
@@ -11282,13 +11176,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>461810</v>
+        <v>461744</v>
       </c>
       <c r="R85" t="n">
-        <v>7050829</v>
+        <v>7050919</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -11317,7 +11211,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11327,12 +11221,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:57</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11343,26 +11232,51 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124262932</v>
+        <v>124262454</v>
       </c>
       <c r="B86" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11375,43 +11289,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>461633</v>
+        <v>461608</v>
       </c>
       <c r="R86" t="n">
-        <v>7050666</v>
+        <v>7050779</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11443,7 +11348,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11453,12 +11358,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>Enstaka bålar på en skadad rönn.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11469,26 +11374,51 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124260842</v>
+        <v>124260479</v>
       </c>
       <c r="B87" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11501,37 +11431,42 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>461785</v>
+        <v>461666</v>
       </c>
       <c r="R87" t="n">
-        <v>7050704</v>
+        <v>7050837</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11560,7 +11495,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11570,12 +11505,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>Fyndplatsen finns intill en bäck i gammal högväxt granskog.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11586,26 +11521,51 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124260158</v>
+        <v>124262348</v>
       </c>
       <c r="B88" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11614,25 +11574,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -11642,10 +11602,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>461793</v>
+        <v>461656</v>
       </c>
       <c r="R88" t="n">
-        <v>7050683</v>
+        <v>7050743</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11677,7 +11637,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11687,12 +11647,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På bark på död rönnstubbe</t>
+          <t>På rönn vid bäck</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11719,10 +11679,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124261626</v>
+        <v>124261471</v>
       </c>
       <c r="B89" t="n">
-        <v>56714</v>
+        <v>78547</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11735,42 +11695,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>102612</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>461768</v>
+        <v>461800</v>
       </c>
       <c r="R89" t="n">
-        <v>7050794</v>
+        <v>7050827</v>
       </c>
       <c r="S89" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11799,7 +11754,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11809,7 +11764,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>På kolade tallstubbe.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11824,6 +11784,26 @@
       <c r="AH89" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Stump # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -11841,10 +11821,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124262035</v>
+        <v>124261741</v>
       </c>
       <c r="B90" t="n">
-        <v>79891</v>
+        <v>90977</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11853,50 +11833,41 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>461712</v>
+        <v>461728</v>
       </c>
       <c r="R90" t="n">
-        <v>7050901</v>
+        <v>7050768</v>
       </c>
       <c r="S90" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11925,7 +11896,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11935,12 +11906,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11955,22 +11926,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124262526</v>
+        <v>124260158</v>
       </c>
       <c r="B91" t="n">
-        <v>79927</v>
+        <v>79891</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11979,25 +11950,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -12007,10 +11978,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>461665</v>
+        <v>461793</v>
       </c>
       <c r="R91" t="n">
-        <v>7050738</v>
+        <v>7050683</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12042,7 +12013,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -12052,12 +12023,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>På död rönn intill bäck</t>
+          <t>På bark på död rönnstubbe</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12072,22 +12043,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124262979</v>
+        <v>124263001</v>
       </c>
       <c r="B92" t="n">
-        <v>91012</v>
+        <v>79920</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12096,31 +12067,31 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -12129,10 +12100,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>461543</v>
+        <v>461597</v>
       </c>
       <c r="R92" t="n">
-        <v>7050645</v>
+        <v>7050664</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12164,7 +12135,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -12174,12 +12145,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:47</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12190,26 +12156,51 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM92" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124263066</v>
+        <v>124263802</v>
       </c>
       <c r="B93" t="n">
-        <v>77743</v>
+        <v>98101</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -12218,25 +12209,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -12246,10 +12237,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>461654</v>
+        <v>461536</v>
       </c>
       <c r="R93" t="n">
-        <v>7050616</v>
+        <v>7050642</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12281,7 +12272,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -12291,12 +12282,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Ca 40 ex inom en kvadratmeter</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12311,22 +12302,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124258793</v>
+        <v>124263373</v>
       </c>
       <c r="B94" t="n">
-        <v>95335</v>
+        <v>77743</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12335,25 +12326,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2809</v>
+        <v>228579</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -12363,10 +12354,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>461641</v>
+        <v>461587</v>
       </c>
       <c r="R94" t="n">
-        <v>7050551</v>
+        <v>7050582</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12398,7 +12389,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12408,12 +12399,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:41</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12428,22 +12414,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124263675</v>
+        <v>124262932</v>
       </c>
       <c r="B95" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12456,34 +12442,43 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>461551</v>
+        <v>461633</v>
       </c>
       <c r="R95" t="n">
-        <v>7050634</v>
+        <v>7050666</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12515,7 +12510,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12525,12 +12520,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>På sälg ca 60 cm i diameter</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12545,26 +12540,26 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124259946</v>
+        <v>124263536</v>
       </c>
       <c r="B96" t="n">
-        <v>78891</v>
+        <v>57513</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12573,37 +12568,42 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>283</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>461815</v>
+        <v>461544</v>
       </c>
       <c r="R96" t="n">
-        <v>7050652</v>
+        <v>7050635</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12632,7 +12632,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12642,12 +12642,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>På tunn levande gren på gammal klen gran i gammal fuktig granskog</t>
+          <t>Äldre ringhack på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD96" t="b">

--- a/artfynd/A 12479-2025 artfynd.xlsx
+++ b/artfynd/A 12479-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124244006</v>
+        <v>124244491</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461840</v>
+        <v>461860</v>
       </c>
       <c r="R2" t="n">
-        <v>7050563</v>
+        <v>7050631</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Enstaka på en grov sälglåga.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,22 +784,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -817,10 +817,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124243782</v>
+        <v>124241219</v>
       </c>
       <c r="B3" t="n">
-        <v>95335</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,41 +829,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461757</v>
+        <v>461671</v>
       </c>
       <c r="R3" t="n">
-        <v>7050561</v>
+        <v>7050487</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,12 +902,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Vid en bäck i gammal granskog.</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,6 +917,26 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -939,10 +954,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124244983</v>
+        <v>124243782</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>95335</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,41 +966,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461652</v>
+        <v>461757</v>
       </c>
       <c r="R4" t="n">
-        <v>7050519</v>
+        <v>7050561</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1014,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1024,7 +1039,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Vid en bäck i gammal granskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,26 +1059,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1076,10 +1076,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124243996</v>
+        <v>124242084</v>
       </c>
       <c r="B5" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1088,43 +1088,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461837</v>
+        <v>461835</v>
       </c>
       <c r="R5" t="n">
-        <v>7050572</v>
+        <v>7050524</v>
       </c>
       <c r="S5" t="n">
         <v>7</v>
@@ -1156,7 +1151,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1166,12 +1161,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:23</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På en grov sälglåga.</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1190,22 +1180,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1223,7 +1213,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124242253</v>
+        <v>124244983</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1259,17 +1249,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461780</v>
+        <v>461652</v>
       </c>
       <c r="R6" t="n">
-        <v>7050582</v>
+        <v>7050519</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1298,7 +1288,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1308,7 +1298,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1360,10 +1350,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124243366</v>
+        <v>124244822</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1376,42 +1366,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461694</v>
+        <v>461680</v>
       </c>
       <c r="R7" t="n">
-        <v>7050529</v>
+        <v>7050615</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1440,7 +1430,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1450,12 +1440,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:57</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i en murken granhögstubbe.</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1484,12 +1469,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1507,10 +1492,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124241982</v>
+        <v>124243996</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>79927</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1519,41 +1504,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461758</v>
+        <v>461837</v>
       </c>
       <c r="R8" t="n">
-        <v>7050534</v>
+        <v>7050572</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1582,7 +1572,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1592,12 +1582,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På en sälglåga.</t>
+          <t>På en grov sälglåga.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1649,10 +1639,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124244491</v>
+        <v>124244006</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1665,21 +1655,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1689,13 +1679,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461860</v>
+        <v>461840</v>
       </c>
       <c r="R9" t="n">
-        <v>7050631</v>
+        <v>7050563</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1724,7 +1714,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1734,12 +1724,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Enstaka på en grov sälglåga.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1758,22 +1748,22 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1791,10 +1781,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124244069</v>
+        <v>124244322</v>
       </c>
       <c r="B10" t="n">
-        <v>79920</v>
+        <v>100279</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1807,27 +1797,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1836,13 +1826,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461842</v>
+        <v>461935</v>
       </c>
       <c r="R10" t="n">
         <v>7050570</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1871,7 +1861,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1881,12 +1871,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:26</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På en grov sälglåga.</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1901,26 +1886,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2216,10 +2181,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124242084</v>
+        <v>124241982</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2232,21 +2197,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2256,13 +2221,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461835</v>
+        <v>461758</v>
       </c>
       <c r="R13" t="n">
-        <v>7050524</v>
+        <v>7050534</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2291,7 +2256,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2301,7 +2266,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2320,22 +2290,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2353,7 +2323,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124241219</v>
+        <v>124242253</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -2389,17 +2359,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461671</v>
+        <v>461780</v>
       </c>
       <c r="R14" t="n">
-        <v>7050487</v>
+        <v>7050582</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2428,7 +2398,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2438,7 +2408,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2490,10 +2460,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124244322</v>
+        <v>124243366</v>
       </c>
       <c r="B15" t="n">
-        <v>100279</v>
+        <v>57529</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2502,46 +2472,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461935</v>
+        <v>461694</v>
       </c>
       <c r="R15" t="n">
-        <v>7050570</v>
+        <v>7050529</v>
       </c>
       <c r="S15" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2570,7 +2540,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2580,7 +2550,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i en murken granhögstubbe.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2595,6 +2570,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2612,10 +2607,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124244822</v>
+        <v>124244069</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2624,25 +2619,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2653,17 +2648,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461680</v>
+        <v>461842</v>
       </c>
       <c r="R16" t="n">
-        <v>7050615</v>
+        <v>7050570</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2692,7 +2687,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2702,7 +2697,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På en grov sälglåga.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2721,22 +2721,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2754,10 +2754,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124262807</v>
+        <v>124263649</v>
       </c>
       <c r="B17" t="n">
-        <v>74901</v>
+        <v>79920</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2766,25 +2766,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461633</v>
+        <v>461556</v>
       </c>
       <c r="R17" t="n">
-        <v>7050701</v>
+        <v>7050632</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gammal gran i gransumpskog</t>
+          <t>På gammal grov sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2859,22 +2859,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124259378</v>
+        <v>124259946</v>
       </c>
       <c r="B18" t="n">
-        <v>79891</v>
+        <v>78891</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2887,42 +2887,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461603</v>
+        <v>461815</v>
       </c>
       <c r="R18" t="n">
-        <v>7050832</v>
+        <v>7050652</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2951,7 +2946,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2961,12 +2956,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglav på en gammal grov sälg. Vissa bålar är fertila med apothecier.</t>
+          <t>På tunn levande gren på gammal klen gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2977,51 +2972,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124258793</v>
+        <v>124259289</v>
       </c>
       <c r="B19" t="n">
-        <v>95335</v>
+        <v>95347</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3034,21 +3004,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2809</v>
+        <v>2813</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -3058,10 +3028,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461641</v>
+        <v>461716</v>
       </c>
       <c r="R19" t="n">
-        <v>7050551</v>
+        <v>7050630</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3093,7 +3063,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3103,12 +3073,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På marken i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3135,10 +3105,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124264003</v>
+        <v>124260090</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3147,60 +3117,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461546</v>
+        <v>461642</v>
       </c>
       <c r="R20" t="n">
-        <v>7050666</v>
+        <v>7050845</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3229,7 +3180,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3239,12 +3190,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:12</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Minst 51 plantor inom ca 2 m2 i gammal granskog.</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3259,6 +3205,26 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3276,10 +3242,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124262198</v>
+        <v>124262595</v>
       </c>
       <c r="B21" t="n">
-        <v>105102</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3288,25 +3254,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3316,13 +3282,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461687</v>
+        <v>461615</v>
       </c>
       <c r="R21" t="n">
-        <v>7050752</v>
+        <v>7050725</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3351,7 +3317,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3361,12 +3327,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På marken i fuktig gammal granskog</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3377,26 +3338,51 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124264084</v>
+        <v>124263001</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3405,41 +3391,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461561</v>
+        <v>461597</v>
       </c>
       <c r="R22" t="n">
-        <v>7050657</v>
+        <v>7050664</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3468,7 +3459,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3478,7 +3469,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3497,22 +3488,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3530,10 +3521,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124262979</v>
+        <v>124263852</v>
       </c>
       <c r="B23" t="n">
-        <v>91012</v>
+        <v>74901</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3546,39 +3537,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461543</v>
+        <v>461549</v>
       </c>
       <c r="R23" t="n">
-        <v>7050645</v>
+        <v>7050671</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3610,7 +3596,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3620,12 +3606,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3640,22 +3626,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124261426</v>
+        <v>124261444</v>
       </c>
       <c r="B24" t="n">
-        <v>78891</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3668,21 +3654,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3692,10 +3678,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461715</v>
+        <v>461810</v>
       </c>
       <c r="R24" t="n">
-        <v>7050700</v>
+        <v>7050829</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3727,7 +3713,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3737,12 +3723,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På kvist på klen gran i gransumpskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3757,22 +3743,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124262044</v>
+        <v>124259784</v>
       </c>
       <c r="B25" t="n">
-        <v>77743</v>
+        <v>74901</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3785,21 +3771,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3809,10 +3795,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461724</v>
+        <v>461789</v>
       </c>
       <c r="R25" t="n">
-        <v>7050772</v>
+        <v>7050616</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3844,7 +3830,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3854,12 +3840,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (28 cm dbh) i gammal granskog</t>
+          <t>På gammal gran ca 5m från bäck i äldre granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3874,22 +3860,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124262878</v>
+        <v>124262044</v>
       </c>
       <c r="B26" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3902,21 +3888,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3926,10 +3912,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461633</v>
+        <v>461724</v>
       </c>
       <c r="R26" t="n">
-        <v>7050666</v>
+        <v>7050772</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3961,7 +3947,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3971,12 +3957,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 170 år) i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran (28 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4003,10 +3989,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124260993</v>
+        <v>124264084</v>
       </c>
       <c r="B27" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4019,42 +4005,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Småfloarna, Småfloarna, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461776</v>
+        <v>461561</v>
       </c>
       <c r="R27" t="n">
-        <v>7050859</v>
+        <v>7050657</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4083,7 +4064,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4093,12 +4074,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:41</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår.</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4127,12 +4103,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4150,10 +4126,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124263170</v>
+        <v>124260115</v>
       </c>
       <c r="B28" t="n">
-        <v>77743</v>
+        <v>100279</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4162,41 +4138,46 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228579</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461624</v>
+        <v>461636</v>
       </c>
       <c r="R28" t="n">
-        <v>7050624</v>
+        <v>7050841</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4225,7 +4206,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4235,12 +4216,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På gammal gran i fuktig äldre granskog</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4251,26 +4227,31 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124263225</v>
+        <v>124261793</v>
       </c>
       <c r="B29" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4283,37 +4264,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461603</v>
+        <v>461776</v>
       </c>
       <c r="R29" t="n">
-        <v>7050578</v>
+        <v>7050867</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4342,7 +4328,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4352,12 +4338,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>Letade efter hästmyra</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4372,12 +4358,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>August Nordin, Ludvig Nordin, Emil Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4501,10 +4487,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124260205</v>
+        <v>124260468</v>
       </c>
       <c r="B31" t="n">
-        <v>79920</v>
+        <v>74901</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4513,25 +4499,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4541,10 +4527,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461793</v>
+        <v>461783</v>
       </c>
       <c r="R31" t="n">
-        <v>7050683</v>
+        <v>7050722</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4576,7 +4562,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4586,12 +4572,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På bark på rönnhögststubbe i gammal fuktig granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4618,10 +4604,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124261626</v>
+        <v>124241603</v>
       </c>
       <c r="B32" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4630,31 +4616,40 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4663,13 +4658,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461768</v>
+        <v>461712</v>
       </c>
       <c r="R32" t="n">
-        <v>7050794</v>
+        <v>7050513</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4693,22 +4688,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Minst 78 plantor och 3 vinterståndare inom ca 1 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4740,10 +4740,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124263837</v>
+        <v>124262932</v>
       </c>
       <c r="B33" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4756,34 +4756,43 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461549</v>
+        <v>461633</v>
       </c>
       <c r="R33" t="n">
-        <v>7050671</v>
+        <v>7050666</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4815,7 +4824,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4825,12 +4834,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4850,17 +4859,17 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124259877</v>
+        <v>124262807</v>
       </c>
       <c r="B34" t="n">
-        <v>79891</v>
+        <v>74901</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4873,42 +4882,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461614</v>
+        <v>461633</v>
       </c>
       <c r="R34" t="n">
-        <v>7050862</v>
+        <v>7050701</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4937,7 +4941,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4947,12 +4951,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ymnig påväxt på en grov gammal sälg där vissa bålar är fertila med apothecier.</t>
+          <t>På gammal gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4963,51 +4967,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124263649</v>
+        <v>124260479</v>
       </c>
       <c r="B35" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5016,41 +4995,46 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461556</v>
+        <v>461666</v>
       </c>
       <c r="R35" t="n">
-        <v>7050632</v>
+        <v>7050837</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5079,7 +5063,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5089,12 +5073,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gammal grov sälg i gammal granskog</t>
+          <t>Fyndplatsen finns intill en bäck i gammal högväxt granskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5105,26 +5089,51 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124262970</v>
+        <v>124262979</v>
       </c>
       <c r="B36" t="n">
-        <v>79892</v>
+        <v>91012</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5137,37 +5146,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461598</v>
+        <v>461543</v>
       </c>
       <c r="R36" t="n">
-        <v>7050665</v>
+        <v>7050645</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5196,7 +5210,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5206,12 +5220,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Enstaka på en flerstammig sälg.</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5222,51 +5236,26 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124260947</v>
+        <v>124263170</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5279,21 +5268,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5303,10 +5292,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461749</v>
+        <v>461624</v>
       </c>
       <c r="R37" t="n">
-        <v>7050709</v>
+        <v>7050624</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5338,7 +5327,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5348,7 +5337,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På gammal gran i fuktig äldre granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5363,22 +5357,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124260631</v>
+        <v>124261741</v>
       </c>
       <c r="B38" t="n">
-        <v>74901</v>
+        <v>90977</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5387,38 +5381,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461864</v>
+        <v>461728</v>
       </c>
       <c r="R38" t="n">
-        <v>7050679</v>
+        <v>7050768</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5450,7 +5444,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5460,7 +5454,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5475,22 +5474,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124261167</v>
+        <v>124262454</v>
       </c>
       <c r="B39" t="n">
-        <v>74901</v>
+        <v>79891</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5503,21 +5502,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5527,10 +5526,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461741</v>
+        <v>461608</v>
       </c>
       <c r="R39" t="n">
-        <v>7050704</v>
+        <v>7050779</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5562,7 +5561,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5572,12 +5571,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På gammal gran i gransumpskog</t>
+          <t>Enstaka bålar på en skadad rönn.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5588,26 +5587,51 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Emil Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124261213</v>
+        <v>124260873</v>
       </c>
       <c r="B40" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5620,21 +5644,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5644,13 +5668,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461731</v>
+        <v>461744</v>
       </c>
       <c r="R40" t="n">
-        <v>7050704</v>
+        <v>7050919</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5679,7 +5703,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5689,12 +5713,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:48</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På gammal gran i gransumpskog</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5705,26 +5724,51 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124260054</v>
+        <v>124263675</v>
       </c>
       <c r="B41" t="n">
-        <v>96979</v>
+        <v>79892</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5733,41 +5777,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461843</v>
+        <v>461551</v>
       </c>
       <c r="R41" t="n">
-        <v>7050661</v>
+        <v>7050634</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5796,7 +5840,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5806,7 +5850,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På sälg ca 60 cm i diameter</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5821,22 +5870,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Emil Nordin, Ludvig Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124260115</v>
+        <v>124262198</v>
       </c>
       <c r="B42" t="n">
-        <v>100279</v>
+        <v>105102</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5849,42 +5898,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>221725</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461636</v>
+        <v>461687</v>
       </c>
       <c r="R42" t="n">
-        <v>7050841</v>
+        <v>7050752</v>
       </c>
       <c r="S42" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5913,7 +5957,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5923,7 +5967,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På marken i fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5934,31 +5983,26 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124259895</v>
+        <v>124260175</v>
       </c>
       <c r="B43" t="n">
-        <v>74893</v>
+        <v>74885</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5967,25 +6011,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>308</v>
+        <v>6439</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5995,10 +6039,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461797</v>
+        <v>461793</v>
       </c>
       <c r="R43" t="n">
-        <v>7050670</v>
+        <v>7050683</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6030,7 +6074,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6040,12 +6084,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Rikligt på ved på basen av granhögstubbe i fuktig gammal granskog</t>
+          <t>På ved på rönnhögstubbe i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6072,10 +6116,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124258987</v>
+        <v>124262353</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6088,21 +6132,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6112,10 +6156,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461689</v>
+        <v>461655</v>
       </c>
       <c r="R44" t="n">
-        <v>7050585</v>
+        <v>7050759</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6147,7 +6191,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6157,12 +6201,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gran ca 40 cm i diameter intill bäck</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6177,22 +6221,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124263103</v>
+        <v>124260773</v>
       </c>
       <c r="B45" t="n">
-        <v>79891</v>
+        <v>91673</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6201,41 +6245,46 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>898</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461643</v>
+        <v>461785</v>
       </c>
       <c r="R45" t="n">
-        <v>7050590</v>
+        <v>7050704</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6264,7 +6313,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6274,12 +6323,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På gammal rönn I gammal granskog</t>
+          <t>På gammal ullticka på granlåga i bördig, fuktig lågarik granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6290,6 +6339,21 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6306,10 +6370,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124262353</v>
+        <v>124264003</v>
       </c>
       <c r="B46" t="n">
-        <v>77743</v>
+        <v>98101</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6318,41 +6382,60 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461655</v>
+        <v>461546</v>
       </c>
       <c r="R46" t="n">
-        <v>7050759</v>
+        <v>7050666</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6381,7 +6464,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6391,12 +6474,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gran ca 40 cm i diameter intill bäck</t>
+          <t>Minst 51 plantor inom ca 2 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6407,26 +6490,31 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124260702</v>
+        <v>124263103</v>
       </c>
       <c r="B47" t="n">
-        <v>100279</v>
+        <v>79891</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6435,46 +6523,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461678</v>
+        <v>461643</v>
       </c>
       <c r="R47" t="n">
-        <v>7050823</v>
+        <v>7050590</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6503,7 +6586,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6513,12 +6596,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Både blåvioletta och vita blommor.</t>
+          <t>På gammal rönn I gammal granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6529,31 +6612,26 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124263675</v>
+        <v>124258944</v>
       </c>
       <c r="B48" t="n">
-        <v>79892</v>
+        <v>57883</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6562,41 +6640,60 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>103015</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461551</v>
+        <v>461559</v>
       </c>
       <c r="R48" t="n">
-        <v>7050634</v>
+        <v>7050789</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6625,7 +6722,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6635,12 +6732,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På sälg ca 60 cm i diameter</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6651,26 +6748,31 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124263257</v>
+        <v>124262686</v>
       </c>
       <c r="B49" t="n">
-        <v>57529</v>
+        <v>79920</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6679,35 +6781,31 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6716,13 +6814,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>461584</v>
+        <v>461617</v>
       </c>
       <c r="R49" t="n">
-        <v>7050588</v>
+        <v>7050728</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6751,7 +6849,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6761,7 +6859,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6772,26 +6870,51 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124263132</v>
+        <v>124262725</v>
       </c>
       <c r="B50" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6804,51 +6927,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>461570</v>
+        <v>461642</v>
       </c>
       <c r="R50" t="n">
-        <v>7050652</v>
+        <v>7050696</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6877,7 +6986,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6887,12 +6996,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i en grov gran.</t>
+          <t>På gammal gran i gammal fuktig granskog nära bäck</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6903,51 +7012,26 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124262035</v>
+        <v>124260842</v>
       </c>
       <c r="B51" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6960,46 +7044,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461712</v>
+        <v>461785</v>
       </c>
       <c r="R51" t="n">
-        <v>7050901</v>
+        <v>7050704</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7028,7 +7103,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7038,12 +7113,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7058,22 +7133,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124261077</v>
+        <v>124259895</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>74893</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7086,21 +7161,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -7110,10 +7185,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461731</v>
+        <v>461797</v>
       </c>
       <c r="R52" t="n">
-        <v>7050711</v>
+        <v>7050670</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7145,7 +7220,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7155,12 +7230,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal fuktig granskog</t>
+          <t>Rikligt på ved på basen av granhögstubbe i fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7304,10 +7379,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124260468</v>
+        <v>124261248</v>
       </c>
       <c r="B54" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7320,37 +7395,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>461783</v>
+        <v>461756</v>
       </c>
       <c r="R54" t="n">
-        <v>7050722</v>
+        <v>7050765</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7379,7 +7454,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7389,12 +7464,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal fuktig granskog</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7409,22 +7479,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Emil Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124263066</v>
+        <v>124260947</v>
       </c>
       <c r="B55" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7437,21 +7507,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7461,10 +7531,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>461654</v>
+        <v>461749</v>
       </c>
       <c r="R55" t="n">
-        <v>7050616</v>
+        <v>7050709</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7496,7 +7566,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7506,12 +7576,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7538,10 +7603,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124262632</v>
+        <v>124261426</v>
       </c>
       <c r="B56" t="n">
-        <v>79857</v>
+        <v>78891</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7550,25 +7615,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229748</v>
+        <v>283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7578,10 +7643,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461651</v>
+        <v>461715</v>
       </c>
       <c r="R56" t="n">
-        <v>7050724</v>
+        <v>7050700</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7613,7 +7678,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7623,12 +7688,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På rönn vid bäck i gammal granskog</t>
+          <t>På kvist på klen gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7643,22 +7708,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124260536</v>
+        <v>124262035</v>
       </c>
       <c r="B57" t="n">
-        <v>100279</v>
+        <v>79891</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7667,41 +7732,50 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461834</v>
+        <v>461712</v>
       </c>
       <c r="R57" t="n">
-        <v>7050707</v>
+        <v>7050901</v>
       </c>
       <c r="S57" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7730,7 +7804,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7740,7 +7814,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7755,19 +7834,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124259759</v>
+        <v>124263066</v>
       </c>
       <c r="B58" t="n">
         <v>77743</v>
@@ -7807,7 +7886,7 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461789</v>
+        <v>461654</v>
       </c>
       <c r="R58" t="n">
         <v>7050616</v>
@@ -7842,7 +7921,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7852,12 +7931,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På gammal gran ca 5 m från bäck i äldre granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7872,22 +7951,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124262595</v>
+        <v>124262878</v>
       </c>
       <c r="B59" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7900,21 +7979,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7924,13 +8003,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461615</v>
+        <v>461633</v>
       </c>
       <c r="R59" t="n">
-        <v>7050725</v>
+        <v>7050666</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7959,7 +8038,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7969,7 +8048,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 170 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7980,51 +8064,26 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124262725</v>
+        <v>124261167</v>
       </c>
       <c r="B60" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8037,21 +8096,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -8061,10 +8120,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461642</v>
+        <v>461741</v>
       </c>
       <c r="R60" t="n">
-        <v>7050696</v>
+        <v>7050704</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8096,7 +8155,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8106,12 +8165,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal fuktig granskog nära bäck</t>
+          <t>På gammal gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8126,22 +8185,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Emil Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124262760</v>
+        <v>124258987</v>
       </c>
       <c r="B61" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8150,50 +8209,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461558</v>
+        <v>461689</v>
       </c>
       <c r="R61" t="n">
-        <v>7050692</v>
+        <v>7050585</v>
       </c>
       <c r="S61" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8222,7 +8272,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8232,7 +8282,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8247,22 +8302,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124259426</v>
+        <v>124261626</v>
       </c>
       <c r="B62" t="n">
-        <v>77743</v>
+        <v>56714</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8275,37 +8330,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228579</v>
+        <v>102612</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461787</v>
+        <v>461768</v>
       </c>
       <c r="R62" t="n">
-        <v>7050628</v>
+        <v>7050794</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8334,7 +8394,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8344,7 +8404,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8355,26 +8415,31 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124260090</v>
+        <v>124263802</v>
       </c>
       <c r="B63" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8383,25 +8448,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8411,13 +8476,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461642</v>
+        <v>461536</v>
       </c>
       <c r="R63" t="n">
-        <v>7050845</v>
+        <v>7050642</v>
       </c>
       <c r="S63" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8446,7 +8511,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8456,7 +8521,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ca 40 ex inom en kvadratmeter</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8467,51 +8537,26 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124263852</v>
+        <v>124261213</v>
       </c>
       <c r="B64" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8524,21 +8569,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8548,10 +8593,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461549</v>
+        <v>461731</v>
       </c>
       <c r="R64" t="n">
-        <v>7050671</v>
+        <v>7050704</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8583,7 +8628,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8593,12 +8638,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På gammal gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8613,22 +8658,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124262686</v>
+        <v>124262760</v>
       </c>
       <c r="B65" t="n">
-        <v>79920</v>
+        <v>57883</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8641,27 +8686,31 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6462</v>
+        <v>103015</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -8670,13 +8719,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>461617</v>
+        <v>461558</v>
       </c>
       <c r="R65" t="n">
-        <v>7050728</v>
+        <v>7050692</v>
       </c>
       <c r="S65" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8705,7 +8754,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8715,7 +8764,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8726,51 +8775,26 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124259169</v>
+        <v>124260702</v>
       </c>
       <c r="B66" t="n">
-        <v>78810</v>
+        <v>100279</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8779,41 +8803,46 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>461539</v>
+        <v>461678</v>
       </c>
       <c r="R66" t="n">
-        <v>7050804</v>
+        <v>7050823</v>
       </c>
       <c r="S66" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8842,7 +8871,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8852,7 +8881,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Både blåvioletta och vita blommor.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8867,26 +8901,6 @@
       <c r="AH66" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8904,10 +8918,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124259784</v>
+        <v>124261077</v>
       </c>
       <c r="B67" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8920,21 +8934,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8944,10 +8958,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461789</v>
+        <v>461731</v>
       </c>
       <c r="R67" t="n">
-        <v>7050616</v>
+        <v>7050711</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8979,7 +8993,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8989,12 +9003,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>På gammal gran ca 5m från bäck i äldre granskog</t>
+          <t>På gammal gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9009,22 +9023,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124259184</v>
+        <v>124259426</v>
       </c>
       <c r="B68" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9037,37 +9051,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>461677</v>
+        <v>461787</v>
       </c>
       <c r="R68" t="n">
-        <v>7050616</v>
+        <v>7050628</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9096,7 +9110,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9106,12 +9120,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På död gran i sumpgranskog</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9126,22 +9135,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124260175</v>
+        <v>124259378</v>
       </c>
       <c r="B69" t="n">
-        <v>74885</v>
+        <v>79891</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9150,41 +9159,46 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6439</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>461793</v>
+        <v>461603</v>
       </c>
       <c r="R69" t="n">
-        <v>7050683</v>
+        <v>7050832</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9213,7 +9227,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9223,12 +9237,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På ved på rönnhögstubbe i gammal fuktig granskog</t>
+          <t>Ymnigt med lunglav på en gammal grov sälg. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9239,26 +9253,51 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124259289</v>
+        <v>124262970</v>
       </c>
       <c r="B70" t="n">
-        <v>95347</v>
+        <v>79892</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9267,41 +9306,41 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2813</v>
+        <v>2081</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>461716</v>
+        <v>461598</v>
       </c>
       <c r="R70" t="n">
-        <v>7050630</v>
+        <v>7050665</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9330,7 +9369,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9340,12 +9379,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På marken i gammal sumpgranskog</t>
+          <t>Enstaka på en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9356,26 +9395,51 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124259251</v>
+        <v>124263250</v>
       </c>
       <c r="B71" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9384,50 +9448,41 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>461721</v>
+        <v>461629</v>
       </c>
       <c r="R71" t="n">
-        <v>7050576</v>
+        <v>7050621</v>
       </c>
       <c r="S71" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9456,7 +9511,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9466,12 +9521,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Inom en yta på 3x7m</t>
+          <t>Ett 100-tal bålar på ett 10-tal granar</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9486,22 +9541,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124258944</v>
+        <v>124260631</v>
       </c>
       <c r="B72" t="n">
-        <v>57883</v>
+        <v>74901</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9510,60 +9565,41 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103015</v>
+        <v>6440</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>461559</v>
+        <v>461864</v>
       </c>
       <c r="R72" t="n">
-        <v>7050789</v>
+        <v>7050679</v>
       </c>
       <c r="S72" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9592,7 +9628,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9602,12 +9638,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9618,28 +9649,23 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124241603</v>
+        <v>124263683</v>
       </c>
       <c r="B73" t="n">
         <v>98101</v>
@@ -9674,7 +9700,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>63</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -9687,19 +9713,24 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>461712</v>
+        <v>461584</v>
       </c>
       <c r="R73" t="n">
-        <v>7050513</v>
+        <v>7050644</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9723,27 +9754,27 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Minst 78 plantor och 3 vinterståndare inom ca 1 m2 i gammal granskog.</t>
+          <t>Minst 63 plantor inom ca 2 x 1 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9775,10 +9806,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124260842</v>
+        <v>124259967</v>
       </c>
       <c r="B74" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9791,34 +9822,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>461785</v>
+        <v>461623</v>
       </c>
       <c r="R74" t="n">
-        <v>7050704</v>
+        <v>7050871</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9850,7 +9886,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9860,12 +9896,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>Rikligt på en skadad rönn.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9876,26 +9912,51 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124262908</v>
+        <v>124261471</v>
       </c>
       <c r="B75" t="n">
-        <v>77743</v>
+        <v>78547</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9908,37 +9969,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228579</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>461633</v>
+        <v>461800</v>
       </c>
       <c r="R75" t="n">
-        <v>7050666</v>
+        <v>7050827</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9967,7 +10028,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9977,12 +10038,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (ca 170 år gammal) i gammal granskog</t>
+          <t>På kolade tallstubbe.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9993,26 +10054,51 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Stump # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124259946</v>
+        <v>124259169</v>
       </c>
       <c r="B76" t="n">
-        <v>78891</v>
+        <v>78810</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10025,21 +10111,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -10049,13 +10135,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>461815</v>
+        <v>461539</v>
       </c>
       <c r="R76" t="n">
-        <v>7050652</v>
+        <v>7050804</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -10084,7 +10170,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10094,12 +10180,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>På tunn levande gren på gammal klen gran i gammal fuktig granskog</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10110,26 +10191,51 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124260773</v>
+        <v>124260536</v>
       </c>
       <c r="B77" t="n">
-        <v>91673</v>
+        <v>100279</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10138,46 +10244,41 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>898</v>
+        <v>222498</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>461785</v>
+        <v>461834</v>
       </c>
       <c r="R77" t="n">
-        <v>7050704</v>
+        <v>7050707</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10206,7 +10307,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10216,12 +10317,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På gammal ullticka på granlåga i bördig, fuktig lågarik granskog</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10232,41 +10328,26 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124261248</v>
+        <v>124263837</v>
       </c>
       <c r="B78" t="n">
-        <v>91030</v>
+        <v>77743</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10279,37 +10360,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>461756</v>
+        <v>461549</v>
       </c>
       <c r="R78" t="n">
-        <v>7050765</v>
+        <v>7050671</v>
       </c>
       <c r="S78" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10338,7 +10419,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10348,7 +10429,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10363,22 +10449,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124263250</v>
+        <v>124259877</v>
       </c>
       <c r="B79" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10391,37 +10477,42 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>461629</v>
+        <v>461614</v>
       </c>
       <c r="R79" t="n">
-        <v>7050621</v>
+        <v>7050862</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10450,7 +10541,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10460,12 +10551,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ett 100-tal bålar på ett 10-tal granar</t>
+          <t>Ymnig påväxt på en grov gammal sälg där vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10476,26 +10567,51 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124261793</v>
+        <v>124262908</v>
       </c>
       <c r="B80" t="n">
-        <v>57529</v>
+        <v>77743</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10508,42 +10624,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>228579</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>461776</v>
+        <v>461633</v>
       </c>
       <c r="R80" t="n">
-        <v>7050867</v>
+        <v>7050666</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10572,7 +10683,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10582,12 +10693,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Letade efter hästmyra</t>
+          <t>På bark på stam av levande gammal gran (ca 170 år gammal) i gammal granskog</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10602,22 +10713,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>August Nordin, Ludvig Nordin, Emil Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124259967</v>
+        <v>124259251</v>
       </c>
       <c r="B81" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10626,46 +10737,50 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>461623</v>
+        <v>461721</v>
       </c>
       <c r="R81" t="n">
-        <v>7050871</v>
+        <v>7050576</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10694,7 +10809,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10704,12 +10819,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Rikligt på en skadad rönn.</t>
+          <t>Inom en yta på 3x7m</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10720,51 +10835,26 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124263683</v>
+        <v>124259184</v>
       </c>
       <c r="B82" t="n">
-        <v>98101</v>
+        <v>74901</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10773,60 +10863,41 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>461584</v>
+        <v>461677</v>
       </c>
       <c r="R82" t="n">
-        <v>7050644</v>
+        <v>7050616</v>
       </c>
       <c r="S82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10855,7 +10926,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10865,12 +10936,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Minst 63 plantor inom ca 2 x 1 m2 i gammal granskog.</t>
+          <t>På död gran i sumpgranskog</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10881,21 +10952,16 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -11019,10 +11085,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124261444</v>
+        <v>124263132</v>
       </c>
       <c r="B84" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11035,37 +11101,51 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>461810</v>
+        <v>461570</v>
       </c>
       <c r="R84" t="n">
-        <v>7050829</v>
+        <v>7050652</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11094,7 +11174,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11104,12 +11184,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>Rikligt med fruktkroppar i en grov gran.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11120,26 +11200,51 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124260873</v>
+        <v>124262632</v>
       </c>
       <c r="B85" t="n">
-        <v>78810</v>
+        <v>79857</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11148,25 +11253,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -11176,13 +11281,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>461744</v>
+        <v>461651</v>
       </c>
       <c r="R85" t="n">
-        <v>7050919</v>
+        <v>7050724</v>
       </c>
       <c r="S85" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -11211,7 +11316,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11221,7 +11326,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>På rönn vid bäck i gammal granskog</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11232,51 +11342,26 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124262454</v>
+        <v>124263373</v>
       </c>
       <c r="B86" t="n">
-        <v>79891</v>
+        <v>77743</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11289,21 +11374,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -11313,10 +11398,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>461608</v>
+        <v>461587</v>
       </c>
       <c r="R86" t="n">
-        <v>7050779</v>
+        <v>7050582</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11348,7 +11433,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11358,12 +11443,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på en skadad rönn.</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11374,51 +11454,26 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124260479</v>
+        <v>124260993</v>
       </c>
       <c r="B87" t="n">
-        <v>79891</v>
+        <v>57529</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11431,42 +11486,42 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Småfloarna, Småfloarna, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>461666</v>
+        <v>461776</v>
       </c>
       <c r="R87" t="n">
-        <v>7050837</v>
+        <v>7050859</v>
       </c>
       <c r="S87" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11495,7 +11550,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11505,12 +11560,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns intill en bäck i gammal högväxt granskog.</t>
+          <t>Rejäla hackspår.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11529,22 +11584,22 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11562,7 +11617,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124262348</v>
+        <v>124260205</v>
       </c>
       <c r="B88" t="n">
         <v>79920</v>
@@ -11602,10 +11657,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>461656</v>
+        <v>461793</v>
       </c>
       <c r="R88" t="n">
-        <v>7050743</v>
+        <v>7050683</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11637,7 +11692,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11647,12 +11702,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På rönn vid bäck</t>
+          <t>På bark på rönnhögststubbe i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11679,10 +11734,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124261471</v>
+        <v>124263257</v>
       </c>
       <c r="B89" t="n">
-        <v>78547</v>
+        <v>57529</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11695,37 +11750,46 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>461800</v>
+        <v>461584</v>
       </c>
       <c r="R89" t="n">
-        <v>7050827</v>
+        <v>7050588</v>
       </c>
       <c r="S89" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11754,7 +11818,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11764,12 +11828,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>På kolade tallstubbe.</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11780,51 +11839,26 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
-      </c>
-      <c r="AH89" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Stump # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124261741</v>
+        <v>124260054</v>
       </c>
       <c r="B90" t="n">
-        <v>90977</v>
+        <v>96979</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11837,37 +11871,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>461728</v>
+        <v>461843</v>
       </c>
       <c r="R90" t="n">
-        <v>7050768</v>
+        <v>7050661</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11896,7 +11930,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11906,12 +11940,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11926,12 +11955,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Emil Nordin</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -12055,10 +12084,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124263001</v>
+        <v>124259759</v>
       </c>
       <c r="B92" t="n">
-        <v>79920</v>
+        <v>77743</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12067,43 +12096,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6462</v>
+        <v>228579</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>461597</v>
+        <v>461789</v>
       </c>
       <c r="R92" t="n">
-        <v>7050664</v>
+        <v>7050616</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12135,7 +12159,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -12145,7 +12169,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>På gammal gran ca 5 m från bäck i äldre granskog</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12156,51 +12185,26 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AH92" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124263802</v>
+        <v>124263225</v>
       </c>
       <c r="B93" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -12209,25 +12213,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -12237,10 +12241,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>461536</v>
+        <v>461603</v>
       </c>
       <c r="R93" t="n">
-        <v>7050642</v>
+        <v>7050578</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12272,7 +12276,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -12282,12 +12286,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Ca 40 ex inom en kvadratmeter</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12302,22 +12306,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124263373</v>
+        <v>124258793</v>
       </c>
       <c r="B94" t="n">
-        <v>77743</v>
+        <v>95335</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12326,25 +12330,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228579</v>
+        <v>2809</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -12354,10 +12358,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>461587</v>
+        <v>461641</v>
       </c>
       <c r="R94" t="n">
-        <v>7050582</v>
+        <v>7050551</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12389,7 +12393,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12399,7 +12403,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12414,22 +12423,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124262932</v>
+        <v>124262348</v>
       </c>
       <c r="B95" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12438,47 +12447,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>461633</v>
+        <v>461656</v>
       </c>
       <c r="R95" t="n">
-        <v>7050666</v>
+        <v>7050743</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12520,12 +12520,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På rönn vid bäck</t>
         </is>
       </c>
       <c r="AD95" t="b">

--- a/artfynd/A 12479-2025 artfynd.xlsx
+++ b/artfynd/A 12479-2025 artfynd.xlsx
@@ -1076,7 +1076,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124242084</v>
+        <v>124244983</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1112,14 +1112,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461835</v>
+        <v>461652</v>
       </c>
       <c r="R5" t="n">
-        <v>7050524</v>
+        <v>7050519</v>
       </c>
       <c r="S5" t="n">
         <v>7</v>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1213,7 +1213,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124244983</v>
+        <v>124242084</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1249,14 +1249,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461652</v>
+        <v>461835</v>
       </c>
       <c r="R6" t="n">
-        <v>7050519</v>
+        <v>7050524</v>
       </c>
       <c r="S6" t="n">
         <v>7</v>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -4126,10 +4126,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124260115</v>
+        <v>124261793</v>
       </c>
       <c r="B28" t="n">
-        <v>100279</v>
+        <v>57529</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4138,46 +4138,46 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461636</v>
+        <v>461776</v>
       </c>
       <c r="R28" t="n">
-        <v>7050841</v>
+        <v>7050867</v>
       </c>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4216,7 +4216,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Letade efter hästmyra</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4227,31 +4232,26 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>August Nordin, Ludvig Nordin, Emil Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124261793</v>
+        <v>124262526</v>
       </c>
       <c r="B29" t="n">
-        <v>57529</v>
+        <v>79927</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4260,46 +4260,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461776</v>
+        <v>461665</v>
       </c>
       <c r="R29" t="n">
-        <v>7050867</v>
+        <v>7050738</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4328,7 +4323,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4338,12 +4333,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Letade efter hästmyra</t>
+          <t>På död rönn intill bäck</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4358,22 +4353,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>August Nordin, Ludvig Nordin, Emil Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124262526</v>
+        <v>124260468</v>
       </c>
       <c r="B30" t="n">
-        <v>79927</v>
+        <v>74901</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4382,25 +4377,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4410,10 +4405,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461665</v>
+        <v>461783</v>
       </c>
       <c r="R30" t="n">
-        <v>7050738</v>
+        <v>7050722</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4445,7 +4440,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4455,12 +4450,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På död rönn intill bäck</t>
+          <t>På bark på stam av levande gammal gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4475,22 +4470,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124260468</v>
+        <v>124260115</v>
       </c>
       <c r="B31" t="n">
-        <v>74901</v>
+        <v>100279</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4499,41 +4494,46 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461783</v>
+        <v>461636</v>
       </c>
       <c r="R31" t="n">
-        <v>7050722</v>
+        <v>7050841</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4572,12 +4572,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal fuktig granskog</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4588,16 +4583,21 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -6628,10 +6628,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124258944</v>
+        <v>124262686</v>
       </c>
       <c r="B48" t="n">
-        <v>57883</v>
+        <v>79920</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6644,41 +6644,27 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103015</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6687,13 +6673,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461559</v>
+        <v>461617</v>
       </c>
       <c r="R48" t="n">
-        <v>7050789</v>
+        <v>7050728</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6722,7 +6708,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6732,12 +6718,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6752,6 +6733,26 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6769,10 +6770,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124262686</v>
+        <v>124262725</v>
       </c>
       <c r="B49" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6781,46 +6782,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>461617</v>
+        <v>461642</v>
       </c>
       <c r="R49" t="n">
-        <v>7050728</v>
+        <v>7050696</v>
       </c>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6849,7 +6845,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6859,7 +6855,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal fuktig granskog nära bäck</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6870,51 +6871,26 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124262725</v>
+        <v>124260842</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6927,21 +6903,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6951,10 +6927,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>461642</v>
+        <v>461785</v>
       </c>
       <c r="R50" t="n">
-        <v>7050696</v>
+        <v>7050704</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6986,7 +6962,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6996,12 +6972,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal fuktig granskog nära bäck</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7028,10 +7004,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124260842</v>
+        <v>124259895</v>
       </c>
       <c r="B51" t="n">
-        <v>91012</v>
+        <v>74893</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7044,21 +7020,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -7068,10 +7044,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461785</v>
+        <v>461797</v>
       </c>
       <c r="R51" t="n">
-        <v>7050704</v>
+        <v>7050670</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7103,7 +7079,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7113,12 +7089,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>Rikligt på ved på basen av granhögstubbe i fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7145,10 +7121,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124259895</v>
+        <v>124263059</v>
       </c>
       <c r="B52" t="n">
-        <v>74893</v>
+        <v>74901</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7161,21 +7137,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>308</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -7185,10 +7161,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461797</v>
+        <v>461654</v>
       </c>
       <c r="R52" t="n">
-        <v>7050670</v>
+        <v>7050616</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7220,7 +7196,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7230,12 +7206,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Rikligt på ved på basen av granhögstubbe i fuktig gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7262,10 +7238,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124263059</v>
+        <v>124258944</v>
       </c>
       <c r="B53" t="n">
-        <v>74901</v>
+        <v>57883</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7274,41 +7250,60 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>103015</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461654</v>
+        <v>461559</v>
       </c>
       <c r="R53" t="n">
-        <v>7050616</v>
+        <v>7050789</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7337,7 +7332,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7347,12 +7342,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7363,16 +7358,21 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -7963,10 +7963,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124262878</v>
+        <v>124261626</v>
       </c>
       <c r="B59" t="n">
-        <v>74901</v>
+        <v>56714</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7979,37 +7979,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6440</v>
+        <v>102612</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461633</v>
+        <v>461768</v>
       </c>
       <c r="R59" t="n">
-        <v>7050666</v>
+        <v>7050794</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8038,7 +8043,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8048,12 +8053,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 170 år) i gammal granskog</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8064,16 +8064,21 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -8197,10 +8202,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124258987</v>
+        <v>124262878</v>
       </c>
       <c r="B61" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8213,21 +8218,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8237,10 +8242,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461689</v>
+        <v>461633</v>
       </c>
       <c r="R61" t="n">
-        <v>7050585</v>
+        <v>7050666</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8272,7 +8277,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8282,12 +8287,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 170 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8307,17 +8312,17 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124261626</v>
+        <v>124258987</v>
       </c>
       <c r="B62" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8330,42 +8335,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461768</v>
+        <v>461689</v>
       </c>
       <c r="R62" t="n">
-        <v>7050794</v>
+        <v>7050585</v>
       </c>
       <c r="S62" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8404,7 +8404,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8415,31 +8420,26 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124263802</v>
+        <v>124262760</v>
       </c>
       <c r="B63" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8448,41 +8448,50 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461536</v>
+        <v>461558</v>
       </c>
       <c r="R63" t="n">
-        <v>7050642</v>
+        <v>7050692</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8511,7 +8520,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8521,12 +8530,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ca 40 ex inom en kvadratmeter</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8541,22 +8545,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124261213</v>
+        <v>124263802</v>
       </c>
       <c r="B64" t="n">
-        <v>77743</v>
+        <v>98101</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8565,25 +8569,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8593,10 +8597,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461731</v>
+        <v>461536</v>
       </c>
       <c r="R64" t="n">
-        <v>7050704</v>
+        <v>7050642</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8628,7 +8632,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8638,12 +8642,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På gammal gran i gransumpskog</t>
+          <t>Ca 40 ex inom en kvadratmeter</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8663,17 +8667,17 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124262760</v>
+        <v>124261213</v>
       </c>
       <c r="B65" t="n">
-        <v>57883</v>
+        <v>77743</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8682,50 +8686,41 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103015</v>
+        <v>228579</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>461558</v>
+        <v>461731</v>
       </c>
       <c r="R65" t="n">
-        <v>7050692</v>
+        <v>7050704</v>
       </c>
       <c r="S65" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8754,7 +8749,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8764,7 +8759,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På gammal gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8779,12 +8779,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -9294,10 +9294,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124262970</v>
+        <v>124263683</v>
       </c>
       <c r="B70" t="n">
-        <v>79892</v>
+        <v>98101</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9306,38 +9306,57 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>461598</v>
+        <v>461584</v>
       </c>
       <c r="R70" t="n">
-        <v>7050665</v>
+        <v>7050644</v>
       </c>
       <c r="S70" t="n">
         <v>9</v>
@@ -9369,7 +9388,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9379,12 +9398,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Enstaka på en flerstammig sälg.</t>
+          <t>Minst 63 plantor inom ca 2 x 1 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9399,26 +9418,6 @@
       <c r="AH70" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9436,10 +9435,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124263250</v>
+        <v>124259967</v>
       </c>
       <c r="B71" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9452,34 +9451,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>461629</v>
+        <v>461623</v>
       </c>
       <c r="R71" t="n">
-        <v>7050621</v>
+        <v>7050871</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9511,7 +9515,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9521,12 +9525,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ett 100-tal bålar på ett 10-tal granar</t>
+          <t>Rikligt på en skadad rönn.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9537,26 +9541,51 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124260631</v>
+        <v>124261471</v>
       </c>
       <c r="B72" t="n">
-        <v>74901</v>
+        <v>78547</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9569,21 +9598,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9593,13 +9622,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>461864</v>
+        <v>461800</v>
       </c>
       <c r="R72" t="n">
-        <v>7050679</v>
+        <v>7050827</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9628,7 +9657,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9638,7 +9667,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På kolade tallstubbe.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9649,26 +9683,51 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Stump # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124263683</v>
+        <v>124262970</v>
       </c>
       <c r="B73" t="n">
-        <v>98101</v>
+        <v>79892</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9677,57 +9736,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>461584</v>
+        <v>461598</v>
       </c>
       <c r="R73" t="n">
-        <v>7050644</v>
+        <v>7050665</v>
       </c>
       <c r="S73" t="n">
         <v>9</v>
@@ -9759,7 +9799,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9769,12 +9809,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Minst 63 plantor inom ca 2 x 1 m2 i gammal granskog.</t>
+          <t>Enstaka på en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9789,6 +9829,26 @@
       <c r="AH73" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9806,10 +9866,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124259967</v>
+        <v>124263250</v>
       </c>
       <c r="B74" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9822,39 +9882,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>461623</v>
+        <v>461629</v>
       </c>
       <c r="R74" t="n">
-        <v>7050871</v>
+        <v>7050621</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9886,7 +9941,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9896,12 +9951,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Rikligt på en skadad rönn.</t>
+          <t>Ett 100-tal bålar på ett 10-tal granar</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9912,51 +9967,26 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124261471</v>
+        <v>124259169</v>
       </c>
       <c r="B75" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9969,34 +9999,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>461800</v>
+        <v>461539</v>
       </c>
       <c r="R75" t="n">
-        <v>7050827</v>
+        <v>7050804</v>
       </c>
       <c r="S75" t="n">
         <v>11</v>
@@ -10028,7 +10058,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10038,12 +10068,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>På kolade tallstubbe.</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10062,22 +10087,22 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Stump # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10095,10 +10120,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124259169</v>
+        <v>124260631</v>
       </c>
       <c r="B76" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10111,37 +10136,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>461539</v>
+        <v>461864</v>
       </c>
       <c r="R76" t="n">
-        <v>7050804</v>
+        <v>7050679</v>
       </c>
       <c r="S76" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -10170,7 +10195,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10180,7 +10205,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10191,51 +10216,26 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124260536</v>
+        <v>124262908</v>
       </c>
       <c r="B77" t="n">
-        <v>100279</v>
+        <v>77743</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10244,41 +10244,41 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222498</v>
+        <v>228579</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>461834</v>
+        <v>461633</v>
       </c>
       <c r="R77" t="n">
-        <v>7050707</v>
+        <v>7050666</v>
       </c>
       <c r="S77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10317,7 +10317,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran (ca 170 år gammal) i gammal granskog</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10332,22 +10337,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124263837</v>
+        <v>124259251</v>
       </c>
       <c r="B78" t="n">
-        <v>77743</v>
+        <v>98101</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10356,41 +10361,50 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>461549</v>
+        <v>461721</v>
       </c>
       <c r="R78" t="n">
-        <v>7050671</v>
+        <v>7050576</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10419,7 +10433,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10429,12 +10443,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Inom en yta på 3x7m</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10449,22 +10463,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124259877</v>
+        <v>124259184</v>
       </c>
       <c r="B79" t="n">
-        <v>79891</v>
+        <v>74901</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10477,42 +10491,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>461614</v>
+        <v>461677</v>
       </c>
       <c r="R79" t="n">
-        <v>7050862</v>
+        <v>7050616</v>
       </c>
       <c r="S79" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10541,7 +10550,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10551,12 +10560,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ymnig påväxt på en grov gammal sälg där vissa bålar är fertila med apothecier.</t>
+          <t>På död gran i sumpgranskog</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10567,48 +10576,23 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124262908</v>
+        <v>124263837</v>
       </c>
       <c r="B80" t="n">
         <v>77743</v>
@@ -10648,10 +10632,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>461633</v>
+        <v>461549</v>
       </c>
       <c r="R80" t="n">
-        <v>7050666</v>
+        <v>7050671</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10683,7 +10667,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10693,12 +10677,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (ca 170 år gammal) i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10718,17 +10702,17 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124259251</v>
+        <v>124259877</v>
       </c>
       <c r="B81" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10737,47 +10721,43 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>461721</v>
+        <v>461614</v>
       </c>
       <c r="R81" t="n">
-        <v>7050576</v>
+        <v>7050862</v>
       </c>
       <c r="S81" t="n">
         <v>9</v>
@@ -10809,7 +10789,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10819,12 +10799,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Inom en yta på 3x7m</t>
+          <t>Ymnig påväxt på en grov gammal sälg där vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10835,26 +10815,51 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124259184</v>
+        <v>124260536</v>
       </c>
       <c r="B82" t="n">
-        <v>74901</v>
+        <v>100279</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10863,41 +10868,41 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6440</v>
+        <v>222498</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>461677</v>
+        <v>461834</v>
       </c>
       <c r="R82" t="n">
-        <v>7050616</v>
+        <v>7050707</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10926,7 +10931,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10936,12 +10941,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>På död gran i sumpgranskog</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10956,12 +10956,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>

--- a/artfynd/A 12479-2025 artfynd.xlsx
+++ b/artfynd/A 12479-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124244491</v>
+        <v>124244322</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>100279</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461860</v>
+        <v>461935</v>
       </c>
       <c r="R2" t="n">
-        <v>7050631</v>
+        <v>7050570</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:46</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,26 +780,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -817,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124241219</v>
+        <v>124244983</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -857,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461671</v>
+        <v>461652</v>
       </c>
       <c r="R3" t="n">
-        <v>7050487</v>
+        <v>7050519</v>
       </c>
       <c r="S3" t="n">
         <v>7</v>
@@ -892,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -954,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124243782</v>
+        <v>124241219</v>
       </c>
       <c r="B4" t="n">
-        <v>95335</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -966,41 +946,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461757</v>
+        <v>461671</v>
       </c>
       <c r="R4" t="n">
-        <v>7050561</v>
+        <v>7050487</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1029,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1039,12 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Vid en bäck i gammal granskog.</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1059,6 +1034,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1076,7 +1071,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124244983</v>
+        <v>124244443</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1112,17 +1107,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461652</v>
+        <v>461867</v>
       </c>
       <c r="R5" t="n">
-        <v>7050519</v>
+        <v>7050617</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1151,7 +1146,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1161,7 +1156,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1213,10 +1213,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124242084</v>
+        <v>124244006</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1229,21 +1229,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461835</v>
+        <v>461840</v>
       </c>
       <c r="R6" t="n">
-        <v>7050524</v>
+        <v>7050563</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1298,7 +1298,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Enstaka på en grov sälglåga.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1317,22 +1322,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1350,10 +1355,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124244822</v>
+        <v>124244069</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1362,25 +1367,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1391,17 +1396,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461680</v>
+        <v>461842</v>
       </c>
       <c r="R7" t="n">
-        <v>7050615</v>
+        <v>7050570</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1430,7 +1435,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1440,7 +1445,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På en grov sälglåga.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1459,22 +1469,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1639,10 +1649,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124244006</v>
+        <v>124243782</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>95335</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1651,25 +1661,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1679,10 +1689,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461840</v>
+        <v>461757</v>
       </c>
       <c r="R9" t="n">
-        <v>7050563</v>
+        <v>7050561</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1714,7 +1724,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1724,12 +1734,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Enstaka på en grov sälglåga.</t>
+          <t>Vid en bäck i gammal granskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1744,26 +1754,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1781,10 +1771,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124244322</v>
+        <v>124243366</v>
       </c>
       <c r="B10" t="n">
-        <v>100279</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1793,46 +1783,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461935</v>
+        <v>461694</v>
       </c>
       <c r="R10" t="n">
-        <v>7050570</v>
+        <v>7050529</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1861,7 +1851,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1871,7 +1861,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i en murken granhögstubbe.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1886,6 +1881,26 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2039,7 +2054,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124244443</v>
+        <v>124242084</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -2079,13 +2094,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461867</v>
+        <v>461835</v>
       </c>
       <c r="R12" t="n">
-        <v>7050617</v>
+        <v>7050524</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2114,7 +2129,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2124,12 +2139,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:43</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2158,12 +2168,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2181,10 +2191,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124241982</v>
+        <v>124242253</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2197,21 +2207,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2221,13 +2231,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461758</v>
+        <v>461780</v>
       </c>
       <c r="R13" t="n">
-        <v>7050534</v>
+        <v>7050582</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2256,7 +2266,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2266,12 +2276,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:13</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På en sälglåga.</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2290,22 +2295,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2323,7 +2328,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124242253</v>
+        <v>124244822</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -2357,16 +2362,21 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461780</v>
+        <v>461680</v>
       </c>
       <c r="R14" t="n">
-        <v>7050582</v>
+        <v>7050615</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2398,7 +2408,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2408,7 +2418,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2460,10 +2470,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124243366</v>
+        <v>124244491</v>
       </c>
       <c r="B15" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2476,42 +2486,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461694</v>
+        <v>461860</v>
       </c>
       <c r="R15" t="n">
-        <v>7050529</v>
+        <v>7050631</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2540,7 +2545,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2550,12 +2555,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i en murken granhögstubbe.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2584,12 +2589,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2607,10 +2612,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124244069</v>
+        <v>124241982</v>
       </c>
       <c r="B16" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2619,46 +2624,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461842</v>
+        <v>461758</v>
       </c>
       <c r="R16" t="n">
-        <v>7050570</v>
+        <v>7050534</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På en grov sälglåga.</t>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2754,10 +2754,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124263649</v>
+        <v>124259895</v>
       </c>
       <c r="B17" t="n">
-        <v>79920</v>
+        <v>74893</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2766,25 +2766,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461556</v>
+        <v>461797</v>
       </c>
       <c r="R17" t="n">
-        <v>7050632</v>
+        <v>7050670</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gammal grov sälg i gammal granskog</t>
+          <t>Rikligt på ved på basen av granhögstubbe i fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2871,10 +2871,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124259946</v>
+        <v>124263225</v>
       </c>
       <c r="B18" t="n">
-        <v>78891</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2887,21 +2887,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>283</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2911,10 +2911,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461815</v>
+        <v>461603</v>
       </c>
       <c r="R18" t="n">
-        <v>7050652</v>
+        <v>7050578</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2956,12 +2956,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På tunn levande gren på gammal klen gran i gammal fuktig granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2988,10 +2988,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124259289</v>
+        <v>124259946</v>
       </c>
       <c r="B19" t="n">
-        <v>95347</v>
+        <v>78891</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3000,25 +3000,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2813</v>
+        <v>283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -3028,10 +3028,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461716</v>
+        <v>461815</v>
       </c>
       <c r="R19" t="n">
-        <v>7050630</v>
+        <v>7050652</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På marken i gammal sumpgranskog</t>
+          <t>På tunn levande gren på gammal klen gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3105,10 +3105,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124260090</v>
+        <v>124261248</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3121,34 +3121,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461642</v>
+        <v>461756</v>
       </c>
       <c r="R20" t="n">
-        <v>7050845</v>
+        <v>7050765</v>
       </c>
       <c r="S20" t="n">
         <v>12</v>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3201,48 +3201,23 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Emil Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124262595</v>
+        <v>124260947</v>
       </c>
       <c r="B21" t="n">
         <v>78810</v>
@@ -3282,13 +3257,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461615</v>
+        <v>461749</v>
       </c>
       <c r="R21" t="n">
-        <v>7050725</v>
+        <v>7050709</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3317,7 +3292,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3327,7 +3302,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3338,51 +3313,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124263001</v>
+        <v>124260115</v>
       </c>
       <c r="B22" t="n">
-        <v>79920</v>
+        <v>100279</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3395,42 +3345,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461597</v>
+        <v>461636</v>
       </c>
       <c r="R22" t="n">
-        <v>7050664</v>
+        <v>7050841</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3459,7 +3409,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3469,7 +3419,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3484,26 +3434,6 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3521,10 +3451,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124263852</v>
+        <v>124262970</v>
       </c>
       <c r="B23" t="n">
-        <v>74901</v>
+        <v>79892</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3537,37 +3467,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461549</v>
+        <v>461598</v>
       </c>
       <c r="R23" t="n">
-        <v>7050671</v>
+        <v>7050665</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3596,7 +3526,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3606,12 +3536,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>Enstaka på en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3622,26 +3552,51 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124261444</v>
+        <v>124259378</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3654,37 +3609,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461810</v>
+        <v>461603</v>
       </c>
       <c r="R24" t="n">
-        <v>7050829</v>
+        <v>7050832</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3713,7 +3673,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3723,12 +3683,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>Ymnigt med lunglav på en gammal grov sälg. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3739,26 +3699,51 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124259784</v>
+        <v>124262526</v>
       </c>
       <c r="B25" t="n">
-        <v>74901</v>
+        <v>79927</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3767,25 +3752,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3795,10 +3780,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461789</v>
+        <v>461665</v>
       </c>
       <c r="R25" t="n">
-        <v>7050616</v>
+        <v>7050738</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3830,7 +3815,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3840,12 +3825,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gammal gran ca 5m från bäck i äldre granskog</t>
+          <t>På död rönn intill bäck</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3872,10 +3857,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124262044</v>
+        <v>124264003</v>
       </c>
       <c r="B26" t="n">
-        <v>77743</v>
+        <v>98101</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3884,41 +3869,60 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461724</v>
+        <v>461546</v>
       </c>
       <c r="R26" t="n">
-        <v>7050772</v>
+        <v>7050666</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3947,7 +3951,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3957,12 +3961,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (28 cm dbh) i gammal granskog</t>
+          <t>Minst 51 plantor inom ca 2 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3973,26 +3977,31 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124264084</v>
+        <v>124263802</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4001,41 +4010,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461561</v>
+        <v>461536</v>
       </c>
       <c r="R27" t="n">
-        <v>7050657</v>
+        <v>7050642</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4064,7 +4073,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4074,7 +4083,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ca 40 ex inom en kvadratmeter</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4085,51 +4099,26 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124261793</v>
+        <v>124262198</v>
       </c>
       <c r="B28" t="n">
-        <v>57529</v>
+        <v>105102</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4138,46 +4127,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>221725</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461776</v>
+        <v>461687</v>
       </c>
       <c r="R28" t="n">
-        <v>7050867</v>
+        <v>7050752</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4206,7 +4190,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4216,12 +4200,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Letade efter hästmyra</t>
+          <t>På marken i fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4236,22 +4220,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>August Nordin, Ludvig Nordin, Emil Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124262526</v>
+        <v>124259289</v>
       </c>
       <c r="B29" t="n">
-        <v>79927</v>
+        <v>95347</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4264,21 +4248,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>2813</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4288,10 +4272,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461665</v>
+        <v>461716</v>
       </c>
       <c r="R29" t="n">
-        <v>7050738</v>
+        <v>7050630</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4323,7 +4307,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4333,12 +4317,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På död rönn intill bäck</t>
+          <t>På marken i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4353,22 +4337,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124260468</v>
+        <v>124241603</v>
       </c>
       <c r="B30" t="n">
-        <v>74901</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4377,38 +4361,52 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461783</v>
+        <v>461712</v>
       </c>
       <c r="R30" t="n">
-        <v>7050722</v>
+        <v>7050513</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4435,27 +4433,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal fuktig granskog</t>
+          <t>Minst 78 plantor och 3 vinterståndare inom ca 1 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4466,26 +4464,31 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124260115</v>
+        <v>124258944</v>
       </c>
       <c r="B31" t="n">
-        <v>100279</v>
+        <v>57883</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4498,27 +4501,41 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4527,13 +4544,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461636</v>
+        <v>461559</v>
       </c>
       <c r="R31" t="n">
-        <v>7050841</v>
+        <v>7050789</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4562,7 +4579,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4572,7 +4589,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4604,10 +4626,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124241603</v>
+        <v>124261471</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4616,55 +4638,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461712</v>
+        <v>461800</v>
       </c>
       <c r="R32" t="n">
-        <v>7050513</v>
+        <v>7050827</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4688,27 +4696,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Minst 78 plantor och 3 vinterståndare inom ca 1 m2 i gammal granskog.</t>
+          <t>På kolade tallstubbe.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4723,6 +4731,26 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stump # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4740,10 +4768,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124262932</v>
+        <v>124260536</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>100279</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4752,50 +4780,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461633</v>
+        <v>461834</v>
       </c>
       <c r="R33" t="n">
-        <v>7050666</v>
+        <v>7050707</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4824,7 +4843,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4834,12 +4853,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4854,22 +4868,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124262807</v>
+        <v>124263373</v>
       </c>
       <c r="B34" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4882,21 +4896,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4906,10 +4920,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461633</v>
+        <v>461587</v>
       </c>
       <c r="R34" t="n">
-        <v>7050701</v>
+        <v>7050582</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4941,7 +4955,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4951,12 +4965,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På gammal gran i gransumpskog</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4983,10 +4992,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124260479</v>
+        <v>124261167</v>
       </c>
       <c r="B35" t="n">
-        <v>79891</v>
+        <v>74901</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4999,42 +5008,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461666</v>
+        <v>461741</v>
       </c>
       <c r="R35" t="n">
-        <v>7050837</v>
+        <v>7050704</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5063,7 +5067,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5073,12 +5077,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns intill en bäck i gammal högväxt granskog.</t>
+          <t>På gammal gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5089,51 +5093,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin, Emil Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124262979</v>
+        <v>124259251</v>
       </c>
       <c r="B36" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5142,46 +5121,50 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461543</v>
+        <v>461721</v>
       </c>
       <c r="R36" t="n">
-        <v>7050645</v>
+        <v>7050576</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5210,7 +5193,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5220,12 +5203,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Inom en yta på 3x7m</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5245,17 +5228,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124263170</v>
+        <v>124260158</v>
       </c>
       <c r="B37" t="n">
-        <v>77743</v>
+        <v>79891</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5268,21 +5251,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5292,10 +5275,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461624</v>
+        <v>461793</v>
       </c>
       <c r="R37" t="n">
-        <v>7050624</v>
+        <v>7050683</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5327,7 +5310,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5337,12 +5320,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På gammal gran i fuktig äldre granskog</t>
+          <t>På bark på död rönnstubbe</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5357,22 +5340,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124261741</v>
+        <v>124263103</v>
       </c>
       <c r="B38" t="n">
-        <v>90977</v>
+        <v>79891</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5381,25 +5364,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5409,13 +5392,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461728</v>
+        <v>461643</v>
       </c>
       <c r="R38" t="n">
-        <v>7050768</v>
+        <v>7050590</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5444,7 +5427,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5454,12 +5437,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gammal rönn I gammal granskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5479,17 +5462,17 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124262454</v>
+        <v>124261444</v>
       </c>
       <c r="B39" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5502,21 +5485,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5526,10 +5509,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461608</v>
+        <v>461810</v>
       </c>
       <c r="R39" t="n">
-        <v>7050779</v>
+        <v>7050829</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5561,7 +5544,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5571,12 +5554,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en skadad rönn.</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5587,51 +5570,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124260873</v>
+        <v>124261741</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5640,25 +5598,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5668,13 +5626,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461744</v>
+        <v>461728</v>
       </c>
       <c r="R40" t="n">
-        <v>7050919</v>
+        <v>7050768</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5703,7 +5661,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5713,7 +5671,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5724,51 +5687,26 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124263675</v>
+        <v>124260993</v>
       </c>
       <c r="B41" t="n">
-        <v>79892</v>
+        <v>57529</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5781,37 +5719,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Småfloarna, Småfloarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461551</v>
+        <v>461776</v>
       </c>
       <c r="R41" t="n">
-        <v>7050634</v>
+        <v>7050859</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5840,7 +5783,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5850,12 +5793,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På sälg ca 60 cm i diameter</t>
+          <t>Rejäla hackspår.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5866,26 +5809,51 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124262198</v>
+        <v>124259877</v>
       </c>
       <c r="B42" t="n">
-        <v>105102</v>
+        <v>79891</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5894,41 +5862,46 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221725</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461687</v>
+        <v>461614</v>
       </c>
       <c r="R42" t="n">
-        <v>7050752</v>
+        <v>7050862</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5957,7 +5930,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5967,12 +5940,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På marken i fuktig gammal granskog</t>
+          <t>Ymnig påväxt på en grov gammal sälg där vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5983,26 +5956,51 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124260175</v>
+        <v>124261793</v>
       </c>
       <c r="B43" t="n">
-        <v>74885</v>
+        <v>57529</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6011,41 +6009,46 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6439</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461793</v>
+        <v>461776</v>
       </c>
       <c r="R43" t="n">
-        <v>7050683</v>
+        <v>7050867</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6074,7 +6077,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6084,12 +6087,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På ved på rönnhögstubbe i gammal fuktig granskog</t>
+          <t>Letade efter hästmyra</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6104,12 +6107,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>August Nordin, Ludvig Nordin, Emil Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -6233,10 +6236,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124260773</v>
+        <v>124261213</v>
       </c>
       <c r="B45" t="n">
-        <v>91673</v>
+        <v>77743</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6245,40 +6248,35 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>898</v>
+        <v>228579</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461785</v>
+        <v>461731</v>
       </c>
       <c r="R45" t="n">
         <v>7050704</v>
@@ -6313,7 +6311,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6323,12 +6321,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På gammal ullticka på granlåga i bördig, fuktig lågarik granskog</t>
+          <t>På gammal gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6339,41 +6337,26 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124264003</v>
+        <v>124260702</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6382,60 +6365,46 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461546</v>
+        <v>461678</v>
       </c>
       <c r="R46" t="n">
-        <v>7050666</v>
+        <v>7050823</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6464,7 +6433,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6474,12 +6443,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Minst 51 plantor inom ca 2 m2 i gammal granskog.</t>
+          <t>Både blåvioletta och vita blommor.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6511,10 +6480,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124263103</v>
+        <v>124263001</v>
       </c>
       <c r="B47" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6523,41 +6492,46 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461643</v>
+        <v>461597</v>
       </c>
       <c r="R47" t="n">
-        <v>7050590</v>
+        <v>7050664</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6586,7 +6560,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6596,12 +6570,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På gammal rönn I gammal granskog</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6612,26 +6581,51 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124262686</v>
+        <v>124263170</v>
       </c>
       <c r="B48" t="n">
-        <v>79920</v>
+        <v>77743</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6640,46 +6634,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>228579</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461617</v>
+        <v>461624</v>
       </c>
       <c r="R48" t="n">
-        <v>7050728</v>
+        <v>7050624</v>
       </c>
       <c r="S48" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6708,7 +6697,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6718,7 +6707,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På gammal gran i fuktig äldre granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6729,51 +6723,26 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124262725</v>
+        <v>124260205</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6782,25 +6751,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6810,10 +6779,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>461642</v>
+        <v>461793</v>
       </c>
       <c r="R49" t="n">
-        <v>7050696</v>
+        <v>7050683</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6845,7 +6814,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6855,12 +6824,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal fuktig granskog nära bäck</t>
+          <t>På bark på rönnhögststubbe i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6880,17 +6849,17 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124260842</v>
+        <v>124263132</v>
       </c>
       <c r="B50" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6903,37 +6872,51 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>461785</v>
+        <v>461570</v>
       </c>
       <c r="R50" t="n">
-        <v>7050704</v>
+        <v>7050652</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6962,7 +6945,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6972,12 +6955,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>Rikligt med fruktkroppar i en grov gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6988,26 +6971,51 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124259895</v>
+        <v>124259184</v>
       </c>
       <c r="B51" t="n">
-        <v>74893</v>
+        <v>74901</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7020,21 +7028,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>308</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -7044,10 +7052,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461797</v>
+        <v>461677</v>
       </c>
       <c r="R51" t="n">
-        <v>7050670</v>
+        <v>7050616</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7079,7 +7087,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7089,12 +7097,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Rikligt på ved på basen av granhögstubbe i fuktig gammal granskog</t>
+          <t>På död gran i sumpgranskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7109,22 +7117,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124263059</v>
+        <v>124262979</v>
       </c>
       <c r="B52" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7137,34 +7145,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461654</v>
+        <v>461543</v>
       </c>
       <c r="R52" t="n">
-        <v>7050616</v>
+        <v>7050645</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7196,7 +7209,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7206,12 +7219,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7226,22 +7239,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124258944</v>
+        <v>124262044</v>
       </c>
       <c r="B53" t="n">
-        <v>57883</v>
+        <v>77743</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7250,60 +7263,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103015</v>
+        <v>228579</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461559</v>
+        <v>461724</v>
       </c>
       <c r="R53" t="n">
-        <v>7050789</v>
+        <v>7050772</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7332,7 +7326,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7342,12 +7336,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>På bark på stam av levande gammal gran (28 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7358,31 +7352,26 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124261248</v>
+        <v>124260842</v>
       </c>
       <c r="B54" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7395,37 +7384,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>461756</v>
+        <v>461785</v>
       </c>
       <c r="R54" t="n">
-        <v>7050765</v>
+        <v>7050704</v>
       </c>
       <c r="S54" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7454,7 +7443,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7464,7 +7453,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7479,22 +7473,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Emil Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124260947</v>
+        <v>124261849</v>
       </c>
       <c r="B55" t="n">
-        <v>78810</v>
+        <v>78891</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7507,21 +7501,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7531,10 +7525,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>461749</v>
+        <v>461733</v>
       </c>
       <c r="R55" t="n">
-        <v>7050709</v>
+        <v>7050778</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7566,7 +7560,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7576,7 +7570,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ett ex på klen gran som saknar topp i äldre granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7591,22 +7590,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124261426</v>
+        <v>124259169</v>
       </c>
       <c r="B56" t="n">
-        <v>78891</v>
+        <v>78810</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7619,21 +7618,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7643,13 +7642,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461715</v>
+        <v>461539</v>
       </c>
       <c r="R56" t="n">
-        <v>7050700</v>
+        <v>7050804</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7678,7 +7677,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7688,12 +7687,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:56</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>På kvist på klen gran i gransumpskog</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7704,26 +7698,51 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124262035</v>
+        <v>124260175</v>
       </c>
       <c r="B57" t="n">
-        <v>79891</v>
+        <v>74885</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7732,50 +7751,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461712</v>
+        <v>461793</v>
       </c>
       <c r="R57" t="n">
-        <v>7050901</v>
+        <v>7050683</v>
       </c>
       <c r="S57" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7804,7 +7814,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7814,12 +7824,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>På ved på rönnhögstubbe i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7834,22 +7844,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124263066</v>
+        <v>124259784</v>
       </c>
       <c r="B58" t="n">
-        <v>77743</v>
+        <v>74901</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7862,21 +7872,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7886,7 +7896,7 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461654</v>
+        <v>461789</v>
       </c>
       <c r="R58" t="n">
         <v>7050616</v>
@@ -7921,7 +7931,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7931,12 +7941,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran ca 5m från bäck i äldre granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7951,22 +7961,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124261626</v>
+        <v>124262908</v>
       </c>
       <c r="B59" t="n">
-        <v>56714</v>
+        <v>77743</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7979,42 +7989,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>102612</v>
+        <v>228579</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461768</v>
+        <v>461633</v>
       </c>
       <c r="R59" t="n">
-        <v>7050794</v>
+        <v>7050666</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8043,7 +8048,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8053,7 +8058,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran (ca 170 år gammal) i gammal granskog</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8064,31 +8074,26 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124261167</v>
+        <v>124263250</v>
       </c>
       <c r="B60" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8101,21 +8106,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -8125,10 +8130,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461741</v>
+        <v>461629</v>
       </c>
       <c r="R60" t="n">
-        <v>7050704</v>
+        <v>7050621</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8160,7 +8165,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8170,12 +8175,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På gammal gran i gransumpskog</t>
+          <t>Ett 100-tal bålar på ett 10-tal granar</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8195,17 +8200,17 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Emil Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124262878</v>
+        <v>124259426</v>
       </c>
       <c r="B61" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8218,37 +8223,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461633</v>
+        <v>461787</v>
       </c>
       <c r="R61" t="n">
-        <v>7050666</v>
+        <v>7050628</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8277,7 +8282,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8287,12 +8292,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 170 år) i gammal granskog</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8307,19 +8307,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124258987</v>
+        <v>124262932</v>
       </c>
       <c r="B62" t="n">
         <v>78810</v>
@@ -8352,17 +8352,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461689</v>
+        <v>461633</v>
       </c>
       <c r="R62" t="n">
-        <v>7050585</v>
+        <v>7050666</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8394,7 +8403,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8404,12 +8413,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8429,17 +8438,17 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124262760</v>
+        <v>124262632</v>
       </c>
       <c r="B63" t="n">
-        <v>57883</v>
+        <v>79857</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8452,46 +8461,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103015</v>
+        <v>229748</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461558</v>
+        <v>461651</v>
       </c>
       <c r="R63" t="n">
-        <v>7050692</v>
+        <v>7050724</v>
       </c>
       <c r="S63" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8530,7 +8530,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>På rönn vid bäck i gammal granskog</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8545,22 +8550,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124263802</v>
+        <v>124263837</v>
       </c>
       <c r="B64" t="n">
-        <v>98101</v>
+        <v>77743</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8569,25 +8574,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8597,10 +8602,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461536</v>
+        <v>461549</v>
       </c>
       <c r="R64" t="n">
-        <v>7050642</v>
+        <v>7050671</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8632,7 +8637,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8642,12 +8647,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ca 40 ex inom en kvadratmeter</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8662,22 +8667,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124261213</v>
+        <v>124261426</v>
       </c>
       <c r="B65" t="n">
-        <v>77743</v>
+        <v>78891</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8690,21 +8695,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228579</v>
+        <v>283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8714,10 +8719,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>461731</v>
+        <v>461715</v>
       </c>
       <c r="R65" t="n">
-        <v>7050704</v>
+        <v>7050700</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8749,7 +8754,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8759,12 +8764,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På gammal gran i gransumpskog</t>
+          <t>På kvist på klen gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8791,10 +8796,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124260702</v>
+        <v>124262725</v>
       </c>
       <c r="B66" t="n">
-        <v>100279</v>
+        <v>78810</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8803,46 +8808,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>461678</v>
+        <v>461642</v>
       </c>
       <c r="R66" t="n">
-        <v>7050823</v>
+        <v>7050696</v>
       </c>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8871,7 +8871,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Både blåvioletta och vita blommor.</t>
+          <t>På gammal gran i gammal fuktig granskog nära bäck</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8897,31 +8897,26 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124261077</v>
+        <v>124261626</v>
       </c>
       <c r="B67" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8934,37 +8929,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461731</v>
+        <v>461768</v>
       </c>
       <c r="R67" t="n">
-        <v>7050711</v>
+        <v>7050794</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9003,12 +9003,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:44</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal fuktig granskog</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9019,23 +9014,28 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124259426</v>
+        <v>124263066</v>
       </c>
       <c r="B68" t="n">
         <v>77743</v>
@@ -9071,17 +9071,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>461787</v>
+        <v>461654</v>
       </c>
       <c r="R68" t="n">
-        <v>7050628</v>
+        <v>7050616</v>
       </c>
       <c r="S68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9120,7 +9120,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9135,22 +9140,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124259378</v>
+        <v>124259759</v>
       </c>
       <c r="B69" t="n">
-        <v>79891</v>
+        <v>77743</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9163,42 +9168,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>461603</v>
+        <v>461789</v>
       </c>
       <c r="R69" t="n">
-        <v>7050832</v>
+        <v>7050616</v>
       </c>
       <c r="S69" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglav på en gammal grov sälg. Vissa bålar är fertila med apothecier.</t>
+          <t>På gammal gran ca 5 m från bäck i äldre granskog</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9253,51 +9253,26 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124263683</v>
+        <v>124263675</v>
       </c>
       <c r="B70" t="n">
-        <v>98101</v>
+        <v>79892</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9306,60 +9281,41 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>461584</v>
+        <v>461551</v>
       </c>
       <c r="R70" t="n">
-        <v>7050644</v>
+        <v>7050634</v>
       </c>
       <c r="S70" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9388,7 +9344,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9398,12 +9354,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Minst 63 plantor inom ca 2 x 1 m2 i gammal granskog.</t>
+          <t>På sälg ca 60 cm i diameter</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9414,31 +9370,26 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124259967</v>
+        <v>124258793</v>
       </c>
       <c r="B71" t="n">
-        <v>79891</v>
+        <v>95335</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9447,43 +9398,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>461623</v>
+        <v>461641</v>
       </c>
       <c r="R71" t="n">
-        <v>7050871</v>
+        <v>7050551</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9515,7 +9461,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9525,12 +9471,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Rikligt på en skadad rönn.</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9541,51 +9487,26 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124261471</v>
+        <v>124258987</v>
       </c>
       <c r="B72" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9598,37 +9519,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>461800</v>
+        <v>461689</v>
       </c>
       <c r="R72" t="n">
-        <v>7050827</v>
+        <v>7050585</v>
       </c>
       <c r="S72" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9657,7 +9578,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9667,12 +9588,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På kolade tallstubbe.</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9683,51 +9604,26 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Stump # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124262970</v>
+        <v>124260479</v>
       </c>
       <c r="B73" t="n">
-        <v>79892</v>
+        <v>79891</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9740,34 +9636,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>461598</v>
+        <v>461666</v>
       </c>
       <c r="R73" t="n">
-        <v>7050665</v>
+        <v>7050837</v>
       </c>
       <c r="S73" t="n">
         <v>9</v>
@@ -9799,7 +9700,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9809,12 +9710,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Enstaka på en flerstammig sälg.</t>
+          <t>Fyndplatsen finns intill en bäck i gammal högväxt granskog.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9833,12 +9734,12 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
@@ -9848,7 +9749,7 @@
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9866,10 +9767,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124263250</v>
+        <v>124260468</v>
       </c>
       <c r="B74" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9882,21 +9783,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9906,10 +9807,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>461629</v>
+        <v>461783</v>
       </c>
       <c r="R74" t="n">
-        <v>7050621</v>
+        <v>7050722</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9941,7 +9842,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9951,12 +9852,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ett 100-tal bålar på ett 10-tal granar</t>
+          <t>På bark på stam av levande gammal gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9971,22 +9872,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124259169</v>
+        <v>124262348</v>
       </c>
       <c r="B75" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9995,25 +9896,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -10023,13 +9924,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>461539</v>
+        <v>461656</v>
       </c>
       <c r="R75" t="n">
-        <v>7050804</v>
+        <v>7050743</v>
       </c>
       <c r="S75" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10058,7 +9959,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10068,7 +9969,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>På rönn vid bäck</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10079,51 +9985,26 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124260631</v>
+        <v>124261077</v>
       </c>
       <c r="B76" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10136,34 +10017,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>461864</v>
+        <v>461731</v>
       </c>
       <c r="R76" t="n">
-        <v>7050679</v>
+        <v>7050711</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10195,7 +10076,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10205,7 +10086,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10220,22 +10106,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124262908</v>
+        <v>124263257</v>
       </c>
       <c r="B77" t="n">
-        <v>77743</v>
+        <v>57529</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10248,37 +10134,46 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228579</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>461633</v>
+        <v>461584</v>
       </c>
       <c r="R77" t="n">
-        <v>7050666</v>
+        <v>7050588</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10307,7 +10202,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10317,12 +10212,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran (ca 170 år gammal) i gammal granskog</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10349,7 +10239,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124259251</v>
+        <v>124263683</v>
       </c>
       <c r="B78" t="n">
         <v>98101</v>
@@ -10384,7 +10274,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>63</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -10392,16 +10282,26 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>461721</v>
+        <v>461584</v>
       </c>
       <c r="R78" t="n">
-        <v>7050576</v>
+        <v>7050644</v>
       </c>
       <c r="S78" t="n">
         <v>9</v>
@@ -10433,7 +10333,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10443,12 +10343,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Inom en yta på 3x7m</t>
+          <t>Minst 63 plantor inom ca 2 x 1 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10459,26 +10359,31 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124259184</v>
+        <v>124260773</v>
       </c>
       <c r="B79" t="n">
-        <v>74901</v>
+        <v>91673</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10487,38 +10392,43 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6440</v>
+        <v>898</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>461677</v>
+        <v>461785</v>
       </c>
       <c r="R79" t="n">
-        <v>7050616</v>
+        <v>7050704</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10550,7 +10460,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10560,12 +10470,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>På död gran i sumpgranskog</t>
+          <t>På gammal ullticka på granlåga i bördig, fuktig lågarik granskog</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10576,26 +10486,41 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124263837</v>
+        <v>124260090</v>
       </c>
       <c r="B80" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10608,21 +10533,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10632,13 +10557,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>461549</v>
+        <v>461642</v>
       </c>
       <c r="R80" t="n">
-        <v>7050671</v>
+        <v>7050845</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10667,7 +10592,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10677,12 +10602,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:16</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10693,26 +10613,51 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124259877</v>
+        <v>124262595</v>
       </c>
       <c r="B81" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10725,42 +10670,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>461614</v>
+        <v>461615</v>
       </c>
       <c r="R81" t="n">
-        <v>7050862</v>
+        <v>7050725</v>
       </c>
       <c r="S81" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10789,7 +10729,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10799,12 +10739,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ymnig påväxt på en grov gammal sälg där vissa bålar är fertila med apothecier.</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10823,22 +10758,22 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10856,10 +10791,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124260536</v>
+        <v>124262035</v>
       </c>
       <c r="B82" t="n">
-        <v>100279</v>
+        <v>79891</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10868,41 +10803,50 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>461834</v>
+        <v>461712</v>
       </c>
       <c r="R82" t="n">
-        <v>7050707</v>
+        <v>7050901</v>
       </c>
       <c r="S82" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10931,7 +10875,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10941,7 +10885,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10956,22 +10905,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124261849</v>
+        <v>124260873</v>
       </c>
       <c r="B83" t="n">
-        <v>78891</v>
+        <v>78810</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10984,21 +10933,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -11008,13 +10957,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>461733</v>
+        <v>461744</v>
       </c>
       <c r="R83" t="n">
-        <v>7050778</v>
+        <v>7050919</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -11043,7 +10992,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11053,12 +11002,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:08</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ett ex på klen gran som saknar topp i äldre granskog</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11069,26 +11013,51 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124263132</v>
+        <v>124259967</v>
       </c>
       <c r="B84" t="n">
-        <v>91030</v>
+        <v>79891</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11101,51 +11070,42 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>461570</v>
+        <v>461623</v>
       </c>
       <c r="R84" t="n">
-        <v>7050652</v>
+        <v>7050871</v>
       </c>
       <c r="S84" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11174,7 +11134,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11184,12 +11144,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i en grov gran.</t>
+          <t>Rikligt på en skadad rönn.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11208,22 +11168,22 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -11241,10 +11201,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124262632</v>
+        <v>124263852</v>
       </c>
       <c r="B85" t="n">
-        <v>79857</v>
+        <v>74901</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11253,25 +11213,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>229748</v>
+        <v>6440</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -11281,10 +11241,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>461651</v>
+        <v>461549</v>
       </c>
       <c r="R85" t="n">
-        <v>7050724</v>
+        <v>7050671</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11316,7 +11276,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11326,12 +11286,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>På rönn vid bäck i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11351,17 +11311,17 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124263373</v>
+        <v>124262760</v>
       </c>
       <c r="B86" t="n">
-        <v>77743</v>
+        <v>57883</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11370,41 +11330,50 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228579</v>
+        <v>103015</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>461587</v>
+        <v>461558</v>
       </c>
       <c r="R86" t="n">
-        <v>7050582</v>
+        <v>7050692</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -11433,7 +11402,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11443,7 +11412,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11458,22 +11427,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124260993</v>
+        <v>124260054</v>
       </c>
       <c r="B87" t="n">
-        <v>57529</v>
+        <v>96979</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11482,46 +11451,41 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Småfloarna, Småfloarna, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>461776</v>
+        <v>461843</v>
       </c>
       <c r="R87" t="n">
-        <v>7050859</v>
+        <v>7050661</v>
       </c>
       <c r="S87" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11550,7 +11514,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11560,12 +11524,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:41</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår.</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11576,48 +11535,23 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Emil Nordin</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124260205</v>
+        <v>124263649</v>
       </c>
       <c r="B88" t="n">
         <v>79920</v>
@@ -11657,10 +11591,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>461793</v>
+        <v>461556</v>
       </c>
       <c r="R88" t="n">
-        <v>7050683</v>
+        <v>7050632</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11692,7 +11626,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11702,12 +11636,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På bark på rönnhögststubbe i gammal fuktig granskog</t>
+          <t>På gammal grov sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11734,10 +11668,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124263257</v>
+        <v>124260631</v>
       </c>
       <c r="B89" t="n">
-        <v>57529</v>
+        <v>74901</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11750,46 +11684,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>461584</v>
+        <v>461864</v>
       </c>
       <c r="R89" t="n">
-        <v>7050588</v>
+        <v>7050679</v>
       </c>
       <c r="S89" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11818,7 +11743,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11828,7 +11753,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11843,22 +11768,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124260054</v>
+        <v>124262878</v>
       </c>
       <c r="B90" t="n">
-        <v>96979</v>
+        <v>74901</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11867,41 +11792,41 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221945</v>
+        <v>6440</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>461843</v>
+        <v>461633</v>
       </c>
       <c r="R90" t="n">
-        <v>7050661</v>
+        <v>7050666</v>
       </c>
       <c r="S90" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11930,7 +11855,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11940,7 +11865,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 170 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11955,22 +11885,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Emil Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124260158</v>
+        <v>124263059</v>
       </c>
       <c r="B91" t="n">
-        <v>79891</v>
+        <v>74901</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11983,21 +11913,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -12007,10 +11937,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>461793</v>
+        <v>461654</v>
       </c>
       <c r="R91" t="n">
-        <v>7050683</v>
+        <v>7050616</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12042,7 +11972,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -12052,12 +11982,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>På bark på död rönnstubbe</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12077,17 +12007,17 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124259759</v>
+        <v>124262454</v>
       </c>
       <c r="B92" t="n">
-        <v>77743</v>
+        <v>79891</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12100,21 +12030,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -12124,10 +12054,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>461789</v>
+        <v>461608</v>
       </c>
       <c r="R92" t="n">
-        <v>7050616</v>
+        <v>7050779</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12159,7 +12089,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -12169,12 +12099,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>På gammal gran ca 5 m från bäck i äldre granskog</t>
+          <t>Enstaka bålar på en skadad rönn.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12185,26 +12115,51 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM92" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124263225</v>
+        <v>124262807</v>
       </c>
       <c r="B93" t="n">
-        <v>91012</v>
+        <v>74901</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -12217,21 +12172,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -12241,10 +12196,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>461603</v>
+        <v>461633</v>
       </c>
       <c r="R93" t="n">
-        <v>7050578</v>
+        <v>7050701</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12276,7 +12231,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -12286,12 +12241,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gammal gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12306,22 +12261,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124258793</v>
+        <v>124262686</v>
       </c>
       <c r="B94" t="n">
-        <v>95335</v>
+        <v>79920</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12334,37 +12289,42 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2809</v>
+        <v>6462</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>461641</v>
+        <v>461617</v>
       </c>
       <c r="R94" t="n">
-        <v>7050551</v>
+        <v>7050728</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -12393,7 +12353,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12403,12 +12363,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:41</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12419,26 +12374,51 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM94" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124262348</v>
+        <v>124264084</v>
       </c>
       <c r="B95" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12447,41 +12427,41 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>461656</v>
+        <v>461561</v>
       </c>
       <c r="R95" t="n">
-        <v>7050743</v>
+        <v>7050657</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -12510,7 +12490,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12520,12 +12500,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:26</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>På rönn vid bäck</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12536,16 +12511,41 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM95" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>

--- a/artfynd/A 12479-2025 artfynd.xlsx
+++ b/artfynd/A 12479-2025 artfynd.xlsx
@@ -3451,10 +3451,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124262970</v>
+        <v>124262526</v>
       </c>
       <c r="B23" t="n">
-        <v>79892</v>
+        <v>79927</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3463,41 +3463,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461598</v>
+        <v>461665</v>
       </c>
       <c r="R23" t="n">
-        <v>7050665</v>
+        <v>7050738</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Enstaka på en flerstammig sälg.</t>
+          <t>På död rönn intill bäck</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3552,51 +3552,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124259378</v>
+        <v>124262970</v>
       </c>
       <c r="B24" t="n">
-        <v>79891</v>
+        <v>79892</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3609,39 +3584,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461603</v>
+        <v>461598</v>
       </c>
       <c r="R24" t="n">
-        <v>7050832</v>
+        <v>7050665</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3673,7 +3643,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3683,12 +3653,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglav på en gammal grov sälg. Vissa bålar är fertila med apothecier.</t>
+          <t>Enstaka på en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3740,10 +3710,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124262526</v>
+        <v>124259378</v>
       </c>
       <c r="B25" t="n">
-        <v>79927</v>
+        <v>79891</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3752,41 +3722,46 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461665</v>
+        <v>461603</v>
       </c>
       <c r="R25" t="n">
-        <v>7050738</v>
+        <v>7050832</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3815,7 +3790,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3825,12 +3800,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På död rönn intill bäck</t>
+          <t>Ymnigt med lunglav på en gammal grov sälg. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3841,16 +3816,41 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -4626,10 +4626,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124261471</v>
+        <v>124261167</v>
       </c>
       <c r="B32" t="n">
-        <v>78547</v>
+        <v>74901</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4642,37 +4642,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461800</v>
+        <v>461741</v>
       </c>
       <c r="R32" t="n">
-        <v>7050827</v>
+        <v>7050704</v>
       </c>
       <c r="S32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På kolade tallstubbe.</t>
+          <t>På gammal gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4727,51 +4727,26 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Stump # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin, Emil Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124260536</v>
+        <v>124259251</v>
       </c>
       <c r="B33" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4780,38 +4755,47 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461834</v>
+        <v>461721</v>
       </c>
       <c r="R33" t="n">
-        <v>7050707</v>
+        <v>7050576</v>
       </c>
       <c r="S33" t="n">
         <v>9</v>
@@ -4843,7 +4827,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4853,7 +4837,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Inom en yta på 3x7m</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4868,22 +4857,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124263373</v>
+        <v>124261471</v>
       </c>
       <c r="B34" t="n">
-        <v>77743</v>
+        <v>78547</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4896,37 +4885,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228579</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461587</v>
+        <v>461800</v>
       </c>
       <c r="R34" t="n">
-        <v>7050582</v>
+        <v>7050827</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4955,7 +4944,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4965,7 +4954,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På kolade tallstubbe.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4976,26 +4970,51 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Stump # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124261167</v>
+        <v>124260536</v>
       </c>
       <c r="B35" t="n">
-        <v>74901</v>
+        <v>100279</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5004,41 +5023,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461741</v>
+        <v>461834</v>
       </c>
       <c r="R35" t="n">
-        <v>7050704</v>
+        <v>7050707</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5067,7 +5086,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5077,12 +5096,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:48</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På gammal gran i gransumpskog</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5097,22 +5111,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Emil Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124259251</v>
+        <v>124263373</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>77743</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5121,50 +5135,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461721</v>
+        <v>461587</v>
       </c>
       <c r="R36" t="n">
-        <v>7050576</v>
+        <v>7050582</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5193,7 +5198,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5203,12 +5208,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Inom en yta på 3x7m</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5223,12 +5223,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -11054,10 +11054,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124259967</v>
+        <v>124262760</v>
       </c>
       <c r="B84" t="n">
-        <v>79891</v>
+        <v>57883</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11066,31 +11066,35 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -11099,13 +11103,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>461623</v>
+        <v>461558</v>
       </c>
       <c r="R84" t="n">
-        <v>7050871</v>
+        <v>7050692</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11134,7 +11138,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11144,12 +11148,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Rikligt på en skadad rönn.</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11160,51 +11159,26 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124263852</v>
+        <v>124259967</v>
       </c>
       <c r="B85" t="n">
-        <v>74901</v>
+        <v>79891</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11217,34 +11191,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>461549</v>
+        <v>461623</v>
       </c>
       <c r="R85" t="n">
-        <v>7050671</v>
+        <v>7050871</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11276,7 +11255,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11286,12 +11265,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>Rikligt på en skadad rönn.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11302,26 +11281,51 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124262760</v>
+        <v>124263852</v>
       </c>
       <c r="B86" t="n">
-        <v>57883</v>
+        <v>74901</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11330,50 +11334,41 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>103015</v>
+        <v>6440</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>461558</v>
+        <v>461549</v>
       </c>
       <c r="R86" t="n">
-        <v>7050692</v>
+        <v>7050671</v>
       </c>
       <c r="S86" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -11402,7 +11397,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11412,7 +11407,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11427,12 +11427,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>

--- a/artfynd/A 12479-2025 artfynd.xlsx
+++ b/artfynd/A 12479-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124244322</v>
+        <v>124241219</v>
       </c>
       <c r="B2" t="n">
-        <v>100279</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461935</v>
+        <v>461671</v>
       </c>
       <c r="R2" t="n">
-        <v>7050570</v>
+        <v>7050487</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,6 +775,26 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124244983</v>
+        <v>124244322</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>100279</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,41 +824,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461652</v>
+        <v>461935</v>
       </c>
       <c r="R3" t="n">
-        <v>7050519</v>
+        <v>7050570</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +902,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,26 +917,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -934,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124241219</v>
+        <v>124243996</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,38 +946,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461671</v>
+        <v>461837</v>
       </c>
       <c r="R4" t="n">
-        <v>7050487</v>
+        <v>7050572</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
@@ -1009,7 +1014,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1024,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På en grov sälglåga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,22 +1048,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1071,7 +1081,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124244443</v>
+        <v>124242253</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1111,10 +1121,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461867</v>
+        <v>461780</v>
       </c>
       <c r="R5" t="n">
-        <v>7050617</v>
+        <v>7050582</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1146,7 +1156,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1156,12 +1166,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:43</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1190,12 +1195,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1355,10 +1360,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124244069</v>
+        <v>124243782</v>
       </c>
       <c r="B7" t="n">
-        <v>79920</v>
+        <v>95335</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1371,42 +1376,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>2809</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461842</v>
+        <v>461757</v>
       </c>
       <c r="R7" t="n">
-        <v>7050570</v>
+        <v>7050561</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1445,12 +1445,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På en grov sälglåga.</t>
+          <t>Vid en bäck i gammal granskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1465,26 +1465,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1502,10 +1482,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124243996</v>
+        <v>124241982</v>
       </c>
       <c r="B8" t="n">
-        <v>79927</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1514,46 +1494,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461837</v>
+        <v>461758</v>
       </c>
       <c r="R8" t="n">
-        <v>7050572</v>
+        <v>7050534</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1582,7 +1557,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1592,12 +1567,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På en grov sälglåga.</t>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1649,10 +1624,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124243782</v>
+        <v>124244357</v>
       </c>
       <c r="B9" t="n">
-        <v>95335</v>
+        <v>57883</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1665,37 +1640,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2809</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461757</v>
+        <v>461909</v>
       </c>
       <c r="R9" t="n">
-        <v>7050561</v>
+        <v>7050579</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1724,7 +1713,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1734,12 +1723,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Vid en bäck i gammal granskog.</t>
+          <t>I flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1771,10 +1760,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124243366</v>
+        <v>124242084</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1787,39 +1776,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461694</v>
+        <v>461835</v>
       </c>
       <c r="R10" t="n">
-        <v>7050529</v>
+        <v>7050524</v>
       </c>
       <c r="S10" t="n">
         <v>7</v>
@@ -1851,7 +1835,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1861,12 +1845,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:57</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i en murken granhögstubbe.</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1895,12 +1874,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1918,10 +1897,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124244357</v>
+        <v>124244443</v>
       </c>
       <c r="B11" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1930,52 +1909,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461909</v>
+        <v>461867</v>
       </c>
       <c r="R11" t="n">
-        <v>7050579</v>
+        <v>7050617</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -2007,7 +1972,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2017,12 +1982,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>I flerskiktad äldre granskog.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2037,6 +2002,26 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2054,10 +2039,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124242084</v>
+        <v>124243366</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2070,34 +2055,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461835</v>
+        <v>461694</v>
       </c>
       <c r="R12" t="n">
-        <v>7050524</v>
+        <v>7050529</v>
       </c>
       <c r="S12" t="n">
         <v>7</v>
@@ -2129,7 +2119,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2139,7 +2129,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i en murken granhögstubbe.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2168,12 +2163,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2191,7 +2186,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124242253</v>
+        <v>124244491</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -2231,13 +2226,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461780</v>
+        <v>461860</v>
       </c>
       <c r="R13" t="n">
-        <v>7050582</v>
+        <v>7050631</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2266,7 +2261,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2276,7 +2271,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2328,7 +2328,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124244822</v>
+        <v>124244983</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -2362,24 +2362,19 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461680</v>
+        <v>461652</v>
       </c>
       <c r="R14" t="n">
-        <v>7050615</v>
+        <v>7050519</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2408,7 +2403,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2418,7 +2413,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2470,10 +2465,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124244491</v>
+        <v>124244069</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2482,38 +2477,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461860</v>
+        <v>461842</v>
       </c>
       <c r="R15" t="n">
-        <v>7050631</v>
+        <v>7050570</v>
       </c>
       <c r="S15" t="n">
         <v>8</v>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På en grov sälglåga.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2579,22 +2579,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2612,10 +2612,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124241982</v>
+        <v>124244822</v>
       </c>
       <c r="B16" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2628,37 +2628,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461758</v>
+        <v>461680</v>
       </c>
       <c r="R16" t="n">
-        <v>7050534</v>
+        <v>7050615</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2687,7 +2692,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2697,12 +2702,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:13</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På en sälglåga.</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2721,22 +2721,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2754,10 +2754,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124259895</v>
+        <v>124260158</v>
       </c>
       <c r="B17" t="n">
-        <v>74893</v>
+        <v>79891</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2770,21 +2770,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461797</v>
+        <v>461793</v>
       </c>
       <c r="R17" t="n">
-        <v>7050670</v>
+        <v>7050683</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt på ved på basen av granhögstubbe i fuktig gammal granskog</t>
+          <t>På bark på död rönnstubbe</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2871,10 +2871,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124263225</v>
+        <v>124260479</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2887,37 +2887,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461603</v>
+        <v>461666</v>
       </c>
       <c r="R18" t="n">
-        <v>7050578</v>
+        <v>7050837</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2946,7 +2951,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2956,12 +2961,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>Fyndplatsen finns intill en bäck i gammal högväxt granskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2972,26 +2977,51 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124259946</v>
+        <v>124262686</v>
       </c>
       <c r="B19" t="n">
-        <v>78891</v>
+        <v>79920</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3000,41 +3030,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>283</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461815</v>
+        <v>461617</v>
       </c>
       <c r="R19" t="n">
-        <v>7050652</v>
+        <v>7050728</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3063,7 +3098,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3073,12 +3108,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På tunn levande gren på gammal klen gran i gammal fuktig granskog</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3089,26 +3119,51 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124261248</v>
+        <v>124263649</v>
       </c>
       <c r="B20" t="n">
-        <v>91030</v>
+        <v>79920</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3117,41 +3172,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461756</v>
+        <v>461556</v>
       </c>
       <c r="R20" t="n">
-        <v>7050765</v>
+        <v>7050632</v>
       </c>
       <c r="S20" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3180,7 +3235,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3190,7 +3245,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På gammal grov sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3205,22 +3265,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Emil Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124260947</v>
+        <v>124261849</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>78891</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3233,21 +3293,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3257,10 +3317,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461749</v>
+        <v>461733</v>
       </c>
       <c r="R21" t="n">
-        <v>7050709</v>
+        <v>7050778</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3292,7 +3352,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3302,7 +3362,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ett ex på klen gran som saknar topp i äldre granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3317,22 +3382,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124260115</v>
+        <v>124260842</v>
       </c>
       <c r="B22" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3341,46 +3406,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461636</v>
+        <v>461785</v>
       </c>
       <c r="R22" t="n">
-        <v>7050841</v>
+        <v>7050704</v>
       </c>
       <c r="S22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3409,7 +3469,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3419,7 +3479,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3430,31 +3495,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124262526</v>
+        <v>124259895</v>
       </c>
       <c r="B23" t="n">
-        <v>79927</v>
+        <v>74893</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3463,25 +3523,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3491,10 +3551,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461665</v>
+        <v>461797</v>
       </c>
       <c r="R23" t="n">
-        <v>7050738</v>
+        <v>7050670</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3526,7 +3586,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3536,12 +3596,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På död rönn intill bäck</t>
+          <t>Rikligt på ved på basen av granhögstubbe i fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3556,22 +3616,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124262970</v>
+        <v>124263257</v>
       </c>
       <c r="B24" t="n">
-        <v>79892</v>
+        <v>57529</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3584,37 +3644,46 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461598</v>
+        <v>461584</v>
       </c>
       <c r="R24" t="n">
-        <v>7050665</v>
+        <v>7050588</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3643,7 +3712,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3653,12 +3722,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Enstaka på en flerstammig sälg.</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3669,51 +3733,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124259378</v>
+        <v>124264084</v>
       </c>
       <c r="B25" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3726,42 +3765,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461603</v>
+        <v>461561</v>
       </c>
       <c r="R25" t="n">
-        <v>7050832</v>
+        <v>7050657</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3790,7 +3824,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3800,12 +3834,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ymnigt med lunglav på en gammal grov sälg. Vissa bålar är fertila med apothecier.</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3824,22 +3853,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3857,10 +3886,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124264003</v>
+        <v>124262035</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3869,60 +3898,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461546</v>
+        <v>461712</v>
       </c>
       <c r="R26" t="n">
-        <v>7050666</v>
+        <v>7050901</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3951,7 +3970,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3961,12 +3980,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Minst 51 plantor inom ca 2 m2 i gammal granskog.</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3977,31 +3996,26 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124263802</v>
+        <v>124261741</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4010,25 +4024,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -4038,10 +4052,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461536</v>
+        <v>461728</v>
       </c>
       <c r="R27" t="n">
-        <v>7050642</v>
+        <v>7050768</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4073,7 +4087,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4083,12 +4097,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ca 40 ex inom en kvadratmeter</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4103,22 +4117,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124262198</v>
+        <v>124259378</v>
       </c>
       <c r="B28" t="n">
-        <v>105102</v>
+        <v>79891</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4127,41 +4141,46 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221725</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461687</v>
+        <v>461603</v>
       </c>
       <c r="R28" t="n">
-        <v>7050752</v>
+        <v>7050832</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4190,7 +4209,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4200,12 +4219,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På marken i fuktig gammal granskog</t>
+          <t>Ymnigt med lunglav på en gammal grov sälg. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4216,26 +4235,51 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124259289</v>
+        <v>124263852</v>
       </c>
       <c r="B29" t="n">
-        <v>95347</v>
+        <v>74901</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4244,25 +4288,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2813</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4272,10 +4316,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461716</v>
+        <v>461549</v>
       </c>
       <c r="R29" t="n">
-        <v>7050630</v>
+        <v>7050671</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4307,7 +4351,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4317,12 +4361,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På marken i gammal sumpgranskog</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4342,17 +4386,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124241603</v>
+        <v>124262878</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>74901</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4361,52 +4405,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461712</v>
+        <v>461633</v>
       </c>
       <c r="R30" t="n">
-        <v>7050513</v>
+        <v>7050666</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4433,27 +4463,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Minst 78 plantor och 3 vinterståndare inom ca 1 m2 i gammal granskog.</t>
+          <t>På bark på stam av levande gammal gran (25 cm dbh, ca 170 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4464,31 +4494,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124258944</v>
+        <v>124259946</v>
       </c>
       <c r="B31" t="n">
-        <v>57883</v>
+        <v>78891</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4497,60 +4522,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103015</v>
+        <v>283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461559</v>
+        <v>461815</v>
       </c>
       <c r="R31" t="n">
-        <v>7050789</v>
+        <v>7050652</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4579,7 +4585,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4589,12 +4595,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>På tunn levande gren på gammal klen gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4605,28 +4611,23 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124261167</v>
+        <v>124262807</v>
       </c>
       <c r="B32" t="n">
         <v>74901</v>
@@ -4666,10 +4667,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461741</v>
+        <v>461633</v>
       </c>
       <c r="R32" t="n">
-        <v>7050704</v>
+        <v>7050701</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4701,7 +4702,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4711,7 +4712,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4736,17 +4737,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Emil Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124259251</v>
+        <v>124262932</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4755,50 +4756,50 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461721</v>
+        <v>461633</v>
       </c>
       <c r="R33" t="n">
-        <v>7050576</v>
+        <v>7050666</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4827,7 +4828,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4837,12 +4838,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Inom en yta på 3x7m</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4857,22 +4858,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124261471</v>
+        <v>124262526</v>
       </c>
       <c r="B34" t="n">
-        <v>78547</v>
+        <v>79927</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4881,41 +4882,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6464</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461800</v>
+        <v>461665</v>
       </c>
       <c r="R34" t="n">
-        <v>7050827</v>
+        <v>7050738</v>
       </c>
       <c r="S34" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4944,7 +4945,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4954,12 +4955,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På kolade tallstubbe.</t>
+          <t>På död rönn intill bäck</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4970,51 +4971,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Stump # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124260536</v>
+        <v>124263802</v>
       </c>
       <c r="B35" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5023,41 +4999,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461834</v>
+        <v>461536</v>
       </c>
       <c r="R35" t="n">
-        <v>7050707</v>
+        <v>7050642</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5086,7 +5062,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5096,7 +5072,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ca 40 ex inom en kvadratmeter</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5111,19 +5092,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124263373</v>
+        <v>124259426</v>
       </c>
       <c r="B36" t="n">
         <v>77743</v>
@@ -5159,17 +5140,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461587</v>
+        <v>461787</v>
       </c>
       <c r="R36" t="n">
-        <v>7050582</v>
+        <v>7050628</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5198,7 +5179,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5208,7 +5189,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5223,22 +5204,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124260158</v>
+        <v>124263170</v>
       </c>
       <c r="B37" t="n">
-        <v>79891</v>
+        <v>77743</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5251,21 +5232,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5275,10 +5256,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461793</v>
+        <v>461624</v>
       </c>
       <c r="R37" t="n">
-        <v>7050683</v>
+        <v>7050624</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5310,7 +5291,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5320,12 +5301,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På bark på död rönnstubbe</t>
+          <t>På gammal gran i fuktig äldre granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5340,22 +5321,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124263103</v>
+        <v>124263059</v>
       </c>
       <c r="B38" t="n">
-        <v>79891</v>
+        <v>74901</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5368,21 +5349,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5392,13 +5373,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461643</v>
+        <v>461654</v>
       </c>
       <c r="R38" t="n">
-        <v>7050590</v>
+        <v>7050616</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5427,7 +5408,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5437,12 +5418,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gammal rönn I gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5462,14 +5443,14 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124261444</v>
+        <v>124258987</v>
       </c>
       <c r="B39" t="n">
         <v>78810</v>
@@ -5509,10 +5490,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461810</v>
+        <v>461689</v>
       </c>
       <c r="R39" t="n">
-        <v>7050829</v>
+        <v>7050585</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5544,7 +5525,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5554,12 +5535,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5579,17 +5560,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124261741</v>
+        <v>124260631</v>
       </c>
       <c r="B40" t="n">
-        <v>90977</v>
+        <v>74901</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5598,38 +5579,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461728</v>
+        <v>461864</v>
       </c>
       <c r="R40" t="n">
-        <v>7050768</v>
+        <v>7050679</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5661,7 +5642,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5671,12 +5652,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5691,22 +5667,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124260993</v>
+        <v>124261213</v>
       </c>
       <c r="B41" t="n">
-        <v>57529</v>
+        <v>77743</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5719,42 +5695,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>228579</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Småfloarna, Småfloarna, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461776</v>
+        <v>461731</v>
       </c>
       <c r="R41" t="n">
-        <v>7050859</v>
+        <v>7050704</v>
       </c>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5783,7 +5754,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5793,12 +5764,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Rejäla hackspår.</t>
+          <t>På gammal gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5809,51 +5780,26 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124259877</v>
+        <v>124261167</v>
       </c>
       <c r="B42" t="n">
-        <v>79891</v>
+        <v>74901</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5866,42 +5812,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461614</v>
+        <v>461741</v>
       </c>
       <c r="R42" t="n">
-        <v>7050862</v>
+        <v>7050704</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5930,7 +5871,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5940,12 +5881,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ymnig påväxt på en grov gammal sälg där vissa bålar är fertila med apothecier.</t>
+          <t>På gammal gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5956,51 +5897,26 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin, Emil Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124261793</v>
+        <v>124259877</v>
       </c>
       <c r="B43" t="n">
-        <v>57529</v>
+        <v>79891</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6013,42 +5929,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461776</v>
+        <v>461614</v>
       </c>
       <c r="R43" t="n">
-        <v>7050867</v>
+        <v>7050862</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6077,7 +5993,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6087,12 +6003,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Letade efter hästmyra</t>
+          <t>Ymnig påväxt på en grov gammal sälg där vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6103,26 +6019,51 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>August Nordin, Ludvig Nordin, Emil Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124262353</v>
+        <v>124260115</v>
       </c>
       <c r="B44" t="n">
-        <v>77743</v>
+        <v>100279</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6131,41 +6072,46 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228579</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461655</v>
+        <v>461636</v>
       </c>
       <c r="R44" t="n">
-        <v>7050759</v>
+        <v>7050841</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6194,7 +6140,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6204,12 +6150,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På gran ca 40 cm i diameter intill bäck</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6220,23 +6161,28 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124261213</v>
+        <v>124262908</v>
       </c>
       <c r="B45" t="n">
         <v>77743</v>
@@ -6276,10 +6222,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461731</v>
+        <v>461633</v>
       </c>
       <c r="R45" t="n">
-        <v>7050704</v>
+        <v>7050666</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6311,7 +6257,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6321,12 +6267,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På gammal gran i gransumpskog</t>
+          <t>På bark på stam av levande gammal gran (ca 170 år gammal) i gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6341,22 +6287,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124260702</v>
+        <v>124262979</v>
       </c>
       <c r="B46" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6365,46 +6311,46 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461678</v>
+        <v>461543</v>
       </c>
       <c r="R46" t="n">
-        <v>7050823</v>
+        <v>7050645</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6433,7 +6379,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6443,12 +6389,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Både blåvioletta och vita blommor.</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6459,31 +6405,26 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124263001</v>
+        <v>124260773</v>
       </c>
       <c r="B47" t="n">
-        <v>79920</v>
+        <v>91673</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6492,43 +6433,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>898</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461597</v>
+        <v>461785</v>
       </c>
       <c r="R47" t="n">
-        <v>7050664</v>
+        <v>7050704</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6560,7 +6501,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6570,7 +6511,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På gammal ullticka på granlåga i bördig, fuktig lågarik granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6582,50 +6528,40 @@
       <c r="AG47" t="b">
         <v>0</v>
       </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>ullticka</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124263170</v>
+        <v>124259289</v>
       </c>
       <c r="B48" t="n">
-        <v>77743</v>
+        <v>95347</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6634,25 +6570,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228579</v>
+        <v>2813</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6662,10 +6598,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461624</v>
+        <v>461716</v>
       </c>
       <c r="R48" t="n">
-        <v>7050624</v>
+        <v>7050630</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6697,7 +6633,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6707,12 +6643,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På gammal gran i fuktig äldre granskog</t>
+          <t>På marken i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6727,22 +6663,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124260205</v>
+        <v>124260873</v>
       </c>
       <c r="B49" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6751,25 +6687,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6779,13 +6715,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>461793</v>
+        <v>461744</v>
       </c>
       <c r="R49" t="n">
-        <v>7050683</v>
+        <v>7050919</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6814,7 +6750,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6824,12 +6760,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På bark på rönnhögststubbe i gammal fuktig granskog</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6840,26 +6771,51 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124263132</v>
+        <v>124263683</v>
       </c>
       <c r="B50" t="n">
-        <v>91030</v>
+        <v>98101</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6868,40 +6824,45 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>63</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6910,13 +6871,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>461570</v>
+        <v>461584</v>
       </c>
       <c r="R50" t="n">
-        <v>7050652</v>
+        <v>7050644</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6945,7 +6906,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6955,12 +6916,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i en grov gran.</t>
+          <t>Minst 63 plantor inom ca 2 x 1 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6975,26 +6936,6 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7012,10 +6953,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124259184</v>
+        <v>124262632</v>
       </c>
       <c r="B51" t="n">
-        <v>74901</v>
+        <v>79857</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7024,25 +6965,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>229748</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -7052,10 +6993,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461677</v>
+        <v>461651</v>
       </c>
       <c r="R51" t="n">
-        <v>7050616</v>
+        <v>7050724</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7087,7 +7028,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7097,12 +7038,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På död gran i sumpgranskog</t>
+          <t>På rönn vid bäck i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7117,22 +7058,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124262979</v>
+        <v>124262970</v>
       </c>
       <c r="B52" t="n">
-        <v>91012</v>
+        <v>79892</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7145,42 +7086,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461543</v>
+        <v>461598</v>
       </c>
       <c r="R52" t="n">
-        <v>7050645</v>
+        <v>7050665</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7209,7 +7145,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7219,12 +7155,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Enstaka på en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7235,26 +7171,51 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124262044</v>
+        <v>124260468</v>
       </c>
       <c r="B53" t="n">
-        <v>77743</v>
+        <v>74901</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7267,21 +7228,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7291,10 +7252,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461724</v>
+        <v>461783</v>
       </c>
       <c r="R53" t="n">
-        <v>7050772</v>
+        <v>7050722</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7326,7 +7287,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7336,12 +7297,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (28 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7368,10 +7329,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124260842</v>
+        <v>124260993</v>
       </c>
       <c r="B54" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7384,37 +7345,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Småfloarna, Småfloarna, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>461785</v>
+        <v>461776</v>
       </c>
       <c r="R54" t="n">
-        <v>7050704</v>
+        <v>7050859</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7443,7 +7409,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7453,12 +7419,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>Rejäla hackspår.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7469,26 +7435,51 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124261849</v>
+        <v>124263001</v>
       </c>
       <c r="B55" t="n">
-        <v>78891</v>
+        <v>79920</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7497,38 +7488,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>283</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>461733</v>
+        <v>461597</v>
       </c>
       <c r="R55" t="n">
-        <v>7050778</v>
+        <v>7050664</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7560,7 +7556,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7570,12 +7566,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:08</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ett ex på klen gran som saknar topp i äldre granskog</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7586,26 +7577,51 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124259169</v>
+        <v>124259784</v>
       </c>
       <c r="B56" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7618,21 +7634,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7642,13 +7658,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461539</v>
+        <v>461789</v>
       </c>
       <c r="R56" t="n">
-        <v>7050804</v>
+        <v>7050616</v>
       </c>
       <c r="S56" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7677,7 +7693,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7687,7 +7703,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På gammal gran ca 5m från bäck i äldre granskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7698,51 +7719,26 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124260175</v>
+        <v>124262198</v>
       </c>
       <c r="B57" t="n">
-        <v>74885</v>
+        <v>105102</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7755,21 +7751,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6439</v>
+        <v>221725</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7779,13 +7775,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461793</v>
+        <v>461687</v>
       </c>
       <c r="R57" t="n">
-        <v>7050683</v>
+        <v>7050752</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7814,7 +7810,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7824,12 +7820,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På ved på rönnhögstubbe i gammal fuktig granskog</t>
+          <t>På marken i fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7849,17 +7845,17 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124259784</v>
+        <v>124259759</v>
       </c>
       <c r="B58" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7872,21 +7868,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7931,7 +7927,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7941,12 +7937,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På gammal gran ca 5m från bäck i äldre granskog</t>
+          <t>På gammal gran ca 5 m från bäck i äldre granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7973,10 +7969,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124262908</v>
+        <v>124262595</v>
       </c>
       <c r="B59" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7989,21 +7985,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -8013,13 +8009,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461633</v>
+        <v>461615</v>
       </c>
       <c r="R59" t="n">
-        <v>7050666</v>
+        <v>7050725</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8048,7 +8044,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8058,12 +8054,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran (ca 170 år gammal) i gammal granskog</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8074,23 +8065,48 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124263250</v>
+        <v>124261444</v>
       </c>
       <c r="B60" t="n">
         <v>78810</v>
@@ -8130,10 +8146,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461629</v>
+        <v>461810</v>
       </c>
       <c r="R60" t="n">
-        <v>7050621</v>
+        <v>7050829</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8165,7 +8181,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8175,12 +8191,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ett 100-tal bålar på ett 10-tal granar</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8195,22 +8211,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124259426</v>
+        <v>124262454</v>
       </c>
       <c r="B61" t="n">
-        <v>77743</v>
+        <v>79891</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8223,37 +8239,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461787</v>
+        <v>461608</v>
       </c>
       <c r="R61" t="n">
-        <v>7050628</v>
+        <v>7050779</v>
       </c>
       <c r="S61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8282,7 +8298,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8292,7 +8308,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på en skadad rönn.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8303,26 +8324,51 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124262932</v>
+        <v>124261793</v>
       </c>
       <c r="B62" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8335,46 +8381,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461633</v>
+        <v>461776</v>
       </c>
       <c r="R62" t="n">
-        <v>7050666</v>
+        <v>7050867</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8403,7 +8445,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8413,12 +8455,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>Letade efter hästmyra</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8433,22 +8475,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>August Nordin, Ludvig Nordin, Emil Nordin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124262632</v>
+        <v>124263225</v>
       </c>
       <c r="B63" t="n">
-        <v>79857</v>
+        <v>91012</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8457,25 +8499,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229748</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8485,10 +8527,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461651</v>
+        <v>461603</v>
       </c>
       <c r="R63" t="n">
-        <v>7050724</v>
+        <v>7050578</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8520,7 +8562,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8530,12 +8572,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På rönn vid bäck i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8562,10 +8604,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124263837</v>
+        <v>124260702</v>
       </c>
       <c r="B64" t="n">
-        <v>77743</v>
+        <v>100279</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8574,41 +8616,46 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228579</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461549</v>
+        <v>461678</v>
       </c>
       <c r="R64" t="n">
-        <v>7050671</v>
+        <v>7050823</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8637,7 +8684,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8647,12 +8694,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Både blåvioletta och vita blommor.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8663,26 +8710,31 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124261426</v>
+        <v>124260175</v>
       </c>
       <c r="B65" t="n">
-        <v>78891</v>
+        <v>74885</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8691,25 +8743,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>283</v>
+        <v>6439</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8719,10 +8771,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>461715</v>
+        <v>461793</v>
       </c>
       <c r="R65" t="n">
-        <v>7050700</v>
+        <v>7050683</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8754,7 +8806,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8764,12 +8816,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På kvist på klen gran i gransumpskog</t>
+          <t>På ved på rönnhögstubbe i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8784,22 +8836,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124262725</v>
+        <v>124262760</v>
       </c>
       <c r="B66" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8808,41 +8860,50 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>461642</v>
+        <v>461558</v>
       </c>
       <c r="R66" t="n">
-        <v>7050696</v>
+        <v>7050692</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8871,7 +8932,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8881,12 +8942,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal fuktig granskog nära bäck</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8901,22 +8957,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124261626</v>
+        <v>124264003</v>
       </c>
       <c r="B67" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8925,43 +8981,57 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461768</v>
+        <v>461546</v>
       </c>
       <c r="R67" t="n">
-        <v>7050794</v>
+        <v>7050666</v>
       </c>
       <c r="S67" t="n">
         <v>8</v>
@@ -8993,7 +9063,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9003,7 +9073,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Minst 51 plantor inom ca 2 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9035,10 +9110,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124263066</v>
+        <v>124259169</v>
       </c>
       <c r="B68" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9051,21 +9126,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -9075,13 +9150,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>461654</v>
+        <v>461539</v>
       </c>
       <c r="R68" t="n">
-        <v>7050616</v>
+        <v>7050804</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9110,7 +9185,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9120,12 +9195,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9136,26 +9206,51 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124259759</v>
+        <v>124261077</v>
       </c>
       <c r="B69" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9168,21 +9263,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9192,10 +9287,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>461789</v>
+        <v>461731</v>
       </c>
       <c r="R69" t="n">
-        <v>7050616</v>
+        <v>7050711</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9227,7 +9322,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9237,12 +9332,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På gammal gran ca 5 m från bäck i äldre granskog</t>
+          <t>På gammal gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9257,22 +9352,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124263675</v>
+        <v>124263837</v>
       </c>
       <c r="B70" t="n">
-        <v>79892</v>
+        <v>77743</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9285,21 +9380,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9309,10 +9404,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>461551</v>
+        <v>461549</v>
       </c>
       <c r="R70" t="n">
-        <v>7050634</v>
+        <v>7050671</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9344,7 +9439,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9354,12 +9449,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På sälg ca 60 cm i diameter</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9374,22 +9469,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124258793</v>
+        <v>124241603</v>
       </c>
       <c r="B71" t="n">
-        <v>95335</v>
+        <v>98101</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9398,38 +9493,52 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>461641</v>
+        <v>461712</v>
       </c>
       <c r="R71" t="n">
-        <v>7050551</v>
+        <v>7050513</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9456,27 +9565,27 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>Minst 78 plantor och 3 vinterståndare inom ca 1 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9487,26 +9596,31 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Emil Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124258987</v>
+        <v>124260054</v>
       </c>
       <c r="B72" t="n">
-        <v>78810</v>
+        <v>96979</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9515,41 +9629,41 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>461689</v>
+        <v>461843</v>
       </c>
       <c r="R72" t="n">
-        <v>7050585</v>
+        <v>7050661</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9578,7 +9692,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9588,12 +9702,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9608,22 +9717,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Emil Nordin, August Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Emil Nordin</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124260479</v>
+        <v>124263250</v>
       </c>
       <c r="B73" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9636,42 +9745,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>461666</v>
+        <v>461629</v>
       </c>
       <c r="R73" t="n">
-        <v>7050837</v>
+        <v>7050621</v>
       </c>
       <c r="S73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9700,7 +9804,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9710,12 +9814,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns intill en bäck i gammal högväxt granskog.</t>
+          <t>Ett 100-tal bålar på ett 10-tal granar</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9726,51 +9830,26 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124260468</v>
+        <v>124261626</v>
       </c>
       <c r="B74" t="n">
-        <v>74901</v>
+        <v>56714</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9783,37 +9862,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6440</v>
+        <v>102612</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>461783</v>
+        <v>461768</v>
       </c>
       <c r="R74" t="n">
-        <v>7050722</v>
+        <v>7050794</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9842,7 +9926,7